--- a/04_Figures/F06_prediction/modules/training/enet/c_data/results.xlsx
+++ b/04_Figures/F06_prediction/modules/training/enet/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -143,16 +143,10 @@
     <t xml:space="preserve">freq</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_black</t>
-  </si>
-  <si>
     <t xml:space="preserve">ME_blue</t>
   </si>
   <si>
     <t xml:space="preserve">ME_brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_green</t>
   </si>
   <si>
     <t xml:space="preserve">ME_greenyellow</t>
@@ -164,22 +158,22 @@
     <t xml:space="preserve">ME_pink</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_purple</t>
+    <t xml:space="preserve">ME_black</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_salmon</t>
+    <t xml:space="preserve">ME_green</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_tan</t>
+    <t xml:space="preserve">ME_turquoise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_purple</t>
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
   </si>
   <si>
     <t xml:space="preserve">ME_yellow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_turquoise</t>
   </si>
 </sst>
 </file>
@@ -566,7 +560,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -599,7 +593,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
         <v>200</v>
@@ -611,16 +605,16 @@
         <v>-1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.218905472636816</v>
+        <v>0.18407960199005</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.300829879229128</v>
+        <v>-0.494281883532849</v>
       </c>
       <c r="M3" t="n">
-        <v>0.336043928222507</v>
+        <v>0.722731075962217</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +634,7 @@
         <v>14</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -673,7 +667,7 @@
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>200</v>
@@ -685,16 +679,16 @@
         <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.353233830845771</v>
+        <v>0.288557213930348</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.37243347952274</v>
+        <v>-0.512114607459116</v>
       </c>
       <c r="M5" t="n">
-        <v>0.443945747074083</v>
+        <v>0.57885706130026</v>
       </c>
     </row>
     <row r="6">
@@ -714,13 +708,13 @@
         <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.828860503742606</v>
+        <v>-0.385379546371285</v>
       </c>
       <c r="I6" t="n">
         <v>-0.986813186813187</v>
@@ -747,28 +741,28 @@
         <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.828860503742606</v>
+        <v>-0.385379546371285</v>
       </c>
       <c r="I7" t="n">
         <v>-0.986813186813187</v>
       </c>
       <c r="J7" t="n">
-        <v>0.865671641791045</v>
+        <v>0.512437810945274</v>
       </c>
       <c r="K7" t="n">
-        <v>0.482587064676617</v>
+        <v>0.572139303482587</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.420792899117847</v>
+        <v>-0.554568548526201</v>
       </c>
       <c r="M7" t="n">
-        <v>0.491789576619852</v>
+        <v>0.63944141084147</v>
       </c>
     </row>
     <row r="8">
@@ -788,13 +782,13 @@
         <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.219708630258544</v>
+        <v>-0.159763313609467</v>
       </c>
       <c r="I8" t="n">
         <v>-1</v>
@@ -821,28 +815,28 @@
         <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
         <v>200</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.219708630258544</v>
+        <v>-0.159763313609467</v>
       </c>
       <c r="I9" t="n">
         <v>-1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.606965174129353</v>
+        <v>0.283582089552239</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.324965880188836</v>
+        <v>-0.52864735184952</v>
       </c>
       <c r="M9" t="n">
-        <v>0.43011726469739</v>
+        <v>0.895837226753899</v>
       </c>
     </row>
     <row r="10">
@@ -862,16 +856,16 @@
         <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.999241616869639</v>
+        <v>-1.09379435623788</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.977934475965884</v>
+        <v>-0.974590990105923</v>
       </c>
       <c r="J10"/>
       <c r="K10"/>
@@ -895,28 +889,28 @@
         <v>14</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>200</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.999241616869639</v>
+        <v>-1.09379435623788</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.977934475965884</v>
+        <v>-0.974590990105923</v>
       </c>
       <c r="J11" t="n">
-        <v>0.925373134328358</v>
+        <v>0.885572139303483</v>
       </c>
       <c r="K11" t="n">
-        <v>0.507462686567164</v>
+        <v>0.532338308457711</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.375444785490261</v>
+        <v>-0.599669544034898</v>
       </c>
       <c r="M11" t="n">
-        <v>0.592135366984162</v>
+        <v>1.15388993149839</v>
       </c>
     </row>
     <row r="12">
@@ -936,16 +930,16 @@
         <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.267545372374846</v>
+        <v>-0.638290238571273</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.915862940179192</v>
+        <v>-0.69241445176198</v>
       </c>
       <c r="J12"/>
       <c r="K12"/>
@@ -969,28 +963,28 @@
         <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>200</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.267545372374846</v>
+        <v>-0.638290238571273</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.915862940179192</v>
+        <v>-0.69241445176198</v>
       </c>
       <c r="J13" t="n">
-        <v>0.592039800995025</v>
+        <v>0.766169154228856</v>
       </c>
       <c r="K13" t="n">
-        <v>0.308457711442786</v>
+        <v>0.27363184079602</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.338949214901887</v>
+        <v>-0.485102805987823</v>
       </c>
       <c r="M13" t="n">
-        <v>0.331685323669095</v>
+        <v>0.678512154142582</v>
       </c>
     </row>
   </sheetData>
@@ -1034,7 +1028,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.4391350592129</v>
       </c>
     </row>
     <row r="4">
@@ -1045,7 +1039,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.718465168865286</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="5">
@@ -1067,7 +1061,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.441580543072956</v>
+        <v>-0.770441159457478</v>
       </c>
     </row>
     <row r="7">
@@ -1078,7 +1072,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>0.132939417693749</v>
+        <v>0.653055358517104</v>
       </c>
     </row>
     <row r="8">
@@ -1089,7 +1083,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.283327483696527</v>
       </c>
     </row>
     <row r="9">
@@ -1111,7 +1105,7 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.446929516774339</v>
+        <v>-0.386813243121542</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1116,7 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.226961129267581</v>
+        <v>-0.232667251784306</v>
       </c>
     </row>
     <row r="12">
@@ -1133,7 +1127,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.647597647526729</v>
+        <v>-0.132079789884757</v>
       </c>
     </row>
     <row r="13">
@@ -1144,7 +1138,7 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>0.531583009421658</v>
+        <v>-0.154126103354177</v>
       </c>
     </row>
     <row r="14">
@@ -1155,7 +1149,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.977008775213075</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="15">
@@ -1166,7 +1160,7 @@
         <v>16</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.180970606226683</v>
       </c>
     </row>
     <row r="16">
@@ -1177,7 +1171,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.294563132666078</v>
+        <v>-0.7020172349638</v>
       </c>
     </row>
     <row r="17">
@@ -1210,7 +1204,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.159763313609468</v>
+        <v>-3.20111103634908</v>
       </c>
     </row>
     <row r="20">
@@ -1232,7 +1226,7 @@
         <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.172357506155636</v>
+        <v>-0.16774181019572</v>
       </c>
     </row>
     <row r="22">
@@ -1254,7 +1248,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.686755600098654</v>
+        <v>-0.412341626951171</v>
       </c>
     </row>
     <row r="24">
@@ -1276,7 +1270,7 @@
         <v>16</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.94582265640431</v>
+        <v>-0.882374851168406</v>
       </c>
     </row>
     <row r="26">
@@ -1287,7 +1281,7 @@
         <v>16</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.42091870289515</v>
+        <v>-0.398456373489002</v>
       </c>
     </row>
     <row r="27">
@@ -1298,7 +1292,7 @@
         <v>16</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.646057539134805</v>
       </c>
     </row>
     <row r="28">
@@ -1309,7 +1303,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.197901565300745</v>
+        <v>-0.430023572453902</v>
       </c>
     </row>
     <row r="29">
@@ -1320,7 +1314,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.277344823223547</v>
+        <v>-0.242949705521881</v>
       </c>
     </row>
     <row r="30">
@@ -1353,7 +1347,7 @@
         <v>16</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.209981952978467</v>
+        <v>-0.727639029522458</v>
       </c>
     </row>
     <row r="33">
@@ -1364,7 +1358,7 @@
         <v>16</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.292203549185331</v>
+        <v>-0.294519872583181</v>
       </c>
     </row>
     <row r="34">
@@ -1375,7 +1369,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.125835414924885</v>
+        <v>-0.103533125478658</v>
       </c>
     </row>
     <row r="35">
@@ -1386,7 +1380,7 @@
         <v>16</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.368461879170476</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="36">
@@ -1397,7 +1391,7 @@
         <v>16</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.05490398887546</v>
       </c>
     </row>
     <row r="37">
@@ -1408,7 +1402,7 @@
         <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.353232191483148</v>
+        <v>-0.406240129862</v>
       </c>
     </row>
     <row r="38">
@@ -1419,7 +1413,7 @@
         <v>16</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.0175871154387317</v>
       </c>
     </row>
     <row r="39">
@@ -1430,7 +1424,7 @@
         <v>16</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.500968439826841</v>
+        <v>-0.873928318417741</v>
       </c>
     </row>
     <row r="40">
@@ -1441,7 +1435,7 @@
         <v>16</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.570835352051907</v>
+        <v>-0.782255651294685</v>
       </c>
     </row>
     <row r="41">
@@ -1452,7 +1446,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.408301229420909</v>
+        <v>0.272203501492787</v>
       </c>
     </row>
     <row r="42">
@@ -1463,7 +1457,7 @@
         <v>16</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.18904153610382</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="43">
@@ -1474,7 +1468,7 @@
         <v>16</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.309531916784623</v>
       </c>
     </row>
     <row r="44">
@@ -1485,7 +1479,7 @@
         <v>16</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.206223022065292</v>
+        <v>-0.191563737838015</v>
       </c>
     </row>
     <row r="45">
@@ -1496,7 +1490,7 @@
         <v>16</v>
       </c>
       <c r="C45" t="n">
-        <v>-1.37052738082241</v>
+        <v>-0.214902161473447</v>
       </c>
     </row>
     <row r="46">
@@ -1507,7 +1501,7 @@
         <v>16</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.333233813359288</v>
+        <v>-0.362364296919099</v>
       </c>
     </row>
     <row r="47">
@@ -1529,7 +1523,7 @@
         <v>16</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.159763313609468</v>
+        <v>-2.50113158765242</v>
       </c>
     </row>
     <row r="49">
@@ -1540,7 +1534,7 @@
         <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.353479727695274</v>
+        <v>-0.297548676875425</v>
       </c>
     </row>
     <row r="50">
@@ -1551,7 +1545,7 @@
         <v>16</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.16917266332395</v>
       </c>
     </row>
     <row r="51">
@@ -1562,7 +1556,7 @@
         <v>16</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.684761624880653</v>
+        <v>0.654451152498751</v>
       </c>
     </row>
     <row r="52">
@@ -1573,7 +1567,7 @@
         <v>16</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.425260831304655</v>
+        <v>-0.597558457869649</v>
       </c>
     </row>
     <row r="53">
@@ -1584,7 +1578,7 @@
         <v>16</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.562371624448503</v>
+        <v>-0.107900680152819</v>
       </c>
     </row>
     <row r="54">
@@ -1606,7 +1600,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.528577465933972</v>
+        <v>-0.350009078238519</v>
       </c>
     </row>
     <row r="56">
@@ -1628,7 +1622,7 @@
         <v>16</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.37520740115078</v>
       </c>
     </row>
     <row r="58">
@@ -1639,7 +1633,7 @@
         <v>16</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.441347782153063</v>
+        <v>-0.631326005085986</v>
       </c>
     </row>
     <row r="59">
@@ -1650,7 +1644,7 @@
         <v>16</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.381267273741646</v>
+        <v>-0.329382357678199</v>
       </c>
     </row>
     <row r="60">
@@ -1661,7 +1655,7 @@
         <v>16</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.100609853388728</v>
+        <v>-0.463833613763123</v>
       </c>
     </row>
     <row r="61">
@@ -1672,7 +1666,7 @@
         <v>16</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.340507212339724</v>
+        <v>-0.247746461190572</v>
       </c>
     </row>
     <row r="62">
@@ -1683,7 +1677,7 @@
         <v>16</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.290578415100615</v>
+        <v>-3.73928713129714</v>
       </c>
     </row>
     <row r="63">
@@ -1694,7 +1688,7 @@
         <v>16</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.21367698441019</v>
+        <v>-0.319377681814776</v>
       </c>
     </row>
     <row r="64">
@@ -1705,7 +1699,7 @@
         <v>16</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.918948099109892</v>
+        <v>-0.417245685600035</v>
       </c>
     </row>
     <row r="65">
@@ -1716,7 +1710,7 @@
         <v>16</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.493168726466863</v>
       </c>
     </row>
     <row r="66">
@@ -1727,7 +1721,7 @@
         <v>16</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.220525045409945</v>
+        <v>0.052127095655718</v>
       </c>
     </row>
     <row r="67">
@@ -1738,7 +1732,7 @@
         <v>16</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.119817573017935</v>
+        <v>-0.134729055024427</v>
       </c>
     </row>
     <row r="68">
@@ -1749,7 +1743,7 @@
         <v>16</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.299809368322073</v>
+        <v>-2.42030375052014</v>
       </c>
     </row>
     <row r="69">
@@ -1771,7 +1765,7 @@
         <v>16</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.701252447262075</v>
       </c>
     </row>
     <row r="71">
@@ -1782,7 +1776,7 @@
         <v>16</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.469592115165498</v>
+        <v>-3.52604486661767</v>
       </c>
     </row>
     <row r="72">
@@ -1793,7 +1787,7 @@
         <v>16</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.333560225626865</v>
+        <v>-0.528234167691131</v>
       </c>
     </row>
     <row r="73">
@@ -1804,7 +1798,7 @@
         <v>16</v>
       </c>
       <c r="C73" t="n">
-        <v>0.285698268455886</v>
+        <v>-4.15228198097839</v>
       </c>
     </row>
     <row r="74">
@@ -1815,7 +1809,7 @@
         <v>16</v>
       </c>
       <c r="C74" t="n">
-        <v>-1.12727092619218</v>
+        <v>-1.3028876215352</v>
       </c>
     </row>
     <row r="75">
@@ -1859,7 +1853,7 @@
         <v>16</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.158083415419848</v>
       </c>
     </row>
     <row r="79">
@@ -1870,7 +1864,7 @@
         <v>16</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.276075490411867</v>
+        <v>-0.21936628028048</v>
       </c>
     </row>
     <row r="80">
@@ -1892,7 +1886,7 @@
         <v>16</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.228610022279399</v>
+        <v>-0.461653665683725</v>
       </c>
     </row>
     <row r="82">
@@ -1903,7 +1897,7 @@
         <v>16</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.364121408171145</v>
+        <v>-0.186218353099781</v>
       </c>
     </row>
     <row r="83">
@@ -1914,7 +1908,7 @@
         <v>16</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.622420072743497</v>
+        <v>-0.323623002670361</v>
       </c>
     </row>
     <row r="84">
@@ -1925,7 +1919,7 @@
         <v>16</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.397109112286125</v>
+        <v>-0.512376263263015</v>
       </c>
     </row>
     <row r="85">
@@ -1936,7 +1930,7 @@
         <v>16</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.30402595524243</v>
+        <v>-0.48707297182304</v>
       </c>
     </row>
     <row r="86">
@@ -1947,7 +1941,7 @@
         <v>16</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.179586991844586</v>
       </c>
     </row>
     <row r="87">
@@ -1958,7 +1952,7 @@
         <v>16</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.57626624696985</v>
       </c>
     </row>
     <row r="88">
@@ -1969,7 +1963,7 @@
         <v>16</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.297082305467709</v>
+        <v>-0.116016736691324</v>
       </c>
     </row>
     <row r="89">
@@ -1980,7 +1974,7 @@
         <v>16</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.67713267013735</v>
+        <v>-0.133154055959298</v>
       </c>
     </row>
     <row r="90">
@@ -1991,7 +1985,7 @@
         <v>16</v>
       </c>
       <c r="C90" t="n">
-        <v>0.00376230126179933</v>
+        <v>-0.499892116662476</v>
       </c>
     </row>
     <row r="91">
@@ -2002,7 +1996,7 @@
         <v>16</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.695623608019752</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="92">
@@ -2013,7 +2007,7 @@
         <v>16</v>
       </c>
       <c r="C92" t="n">
-        <v>0.266218052729044</v>
+        <v>-1.54573782936196</v>
       </c>
     </row>
     <row r="93">
@@ -2035,7 +2029,7 @@
         <v>16</v>
       </c>
       <c r="C94" t="n">
-        <v>-1.0754924478138</v>
+        <v>-0.0357438523126559</v>
       </c>
     </row>
     <row r="95">
@@ -2057,7 +2051,7 @@
         <v>16</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.633680102473439</v>
+        <v>-1.11746255325944</v>
       </c>
     </row>
     <row r="97">
@@ -2068,7 +2062,7 @@
         <v>16</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.0972431270929828</v>
+        <v>-0.0681762754009592</v>
       </c>
     </row>
     <row r="98">
@@ -2079,7 +2073,7 @@
         <v>16</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.290054150549526</v>
       </c>
     </row>
     <row r="99">
@@ -2090,7 +2084,7 @@
         <v>16</v>
       </c>
       <c r="C99" t="n">
-        <v>-1.49020319204319</v>
+        <v>-0.282124231778972</v>
       </c>
     </row>
     <row r="100">
@@ -2101,7 +2095,7 @@
         <v>16</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.447000760063926</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="101">
@@ -2123,7 +2117,7 @@
         <v>16</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.19633132092569</v>
       </c>
     </row>
     <row r="103">
@@ -2134,7 +2128,7 @@
         <v>16</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.503125335220302</v>
       </c>
     </row>
     <row r="104">
@@ -2145,7 +2139,7 @@
         <v>16</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.405954239185198</v>
       </c>
     </row>
     <row r="105">
@@ -2156,7 +2150,7 @@
         <v>16</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.165913941607362</v>
+        <v>-1.37938662907539</v>
       </c>
     </row>
     <row r="106">
@@ -2167,7 +2161,7 @@
         <v>16</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.538822269868463</v>
+        <v>-0.510231885439598</v>
       </c>
     </row>
     <row r="107">
@@ -2178,7 +2172,7 @@
         <v>16</v>
       </c>
       <c r="C107" t="n">
-        <v>-1.03790140460968</v>
+        <v>-1.33143039669242</v>
       </c>
     </row>
     <row r="108">
@@ -2189,7 +2183,7 @@
         <v>16</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.196398664214392</v>
+        <v>-0.222203579304129</v>
       </c>
     </row>
     <row r="109">
@@ -2200,7 +2194,7 @@
         <v>16</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.263698265962959</v>
       </c>
     </row>
     <row r="110">
@@ -2211,7 +2205,7 @@
         <v>16</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.40174355758974</v>
+        <v>-0.464161676365544</v>
       </c>
     </row>
     <row r="111">
@@ -2222,7 +2216,7 @@
         <v>16</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.319524815617948</v>
+        <v>-0.875004055067284</v>
       </c>
     </row>
     <row r="112">
@@ -2244,7 +2238,7 @@
         <v>16</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.849355414995621</v>
       </c>
     </row>
     <row r="114">
@@ -2255,7 +2249,7 @@
         <v>16</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.249568737547298</v>
+        <v>-1.28957347189089</v>
       </c>
     </row>
     <row r="115">
@@ -2266,7 +2260,7 @@
         <v>16</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.202232978338337</v>
+        <v>-0.187476398264107</v>
       </c>
     </row>
     <row r="116">
@@ -2288,7 +2282,7 @@
         <v>16</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.17016250464278</v>
+        <v>-0.234381209089484</v>
       </c>
     </row>
     <row r="118">
@@ -2310,7 +2304,7 @@
         <v>16</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.563282792922007</v>
+        <v>-0.822789400503265</v>
       </c>
     </row>
     <row r="120">
@@ -2321,7 +2315,7 @@
         <v>16</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.706055766952405</v>
+        <v>-0.251192438287619</v>
       </c>
     </row>
     <row r="121">
@@ -2332,7 +2326,7 @@
         <v>16</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.25038643005601</v>
+        <v>-0.347676999717578</v>
       </c>
     </row>
     <row r="122">
@@ -2354,7 +2348,7 @@
         <v>16</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.0320706701997406</v>
+        <v>-0.211027800416115</v>
       </c>
     </row>
     <row r="124">
@@ -2365,7 +2359,7 @@
         <v>16</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.323565763745681</v>
+        <v>-0.36325346949197</v>
       </c>
     </row>
     <row r="125">
@@ -2376,7 +2370,7 @@
         <v>16</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.706267915507461</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="126">
@@ -2387,7 +2381,7 @@
         <v>16</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.196432200260609</v>
+        <v>-0.193594343783017</v>
       </c>
     </row>
     <row r="127">
@@ -2398,7 +2392,7 @@
         <v>16</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.456442552773795</v>
+        <v>-0.206934331879398</v>
       </c>
     </row>
     <row r="128">
@@ -2409,7 +2403,7 @@
         <v>16</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.92496239066537</v>
       </c>
     </row>
     <row r="129">
@@ -2420,7 +2414,7 @@
         <v>16</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.481396821604362</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="130">
@@ -2431,7 +2425,7 @@
         <v>16</v>
       </c>
       <c r="C130" t="n">
-        <v>-1.2556526125425</v>
+        <v>0.527715925895922</v>
       </c>
     </row>
     <row r="131">
@@ -2442,7 +2436,7 @@
         <v>16</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.19378105708032</v>
+        <v>-0.204300968828279</v>
       </c>
     </row>
     <row r="132">
@@ -2453,7 +2447,7 @@
         <v>16</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.527897097655765</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="133">
@@ -2464,7 +2458,7 @@
         <v>16</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.613328353509478</v>
+        <v>-0.965556768494592</v>
       </c>
     </row>
     <row r="134">
@@ -2475,7 +2469,7 @@
         <v>16</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.313031818772543</v>
+        <v>-0.245337887396552</v>
       </c>
     </row>
     <row r="135">
@@ -2486,7 +2480,7 @@
         <v>16</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.324500226347239</v>
+        <v>-1.21948517939853</v>
       </c>
     </row>
     <row r="136">
@@ -2497,7 +2491,7 @@
         <v>16</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.486025789482865</v>
       </c>
     </row>
     <row r="137">
@@ -2508,7 +2502,7 @@
         <v>16</v>
       </c>
       <c r="C137" t="n">
-        <v>0.140045414284037</v>
+        <v>-0.560095277957456</v>
       </c>
     </row>
     <row r="138">
@@ -2530,7 +2524,7 @@
         <v>16</v>
       </c>
       <c r="C139" t="n">
-        <v>0.142101586947413</v>
+        <v>-0.62017404473379</v>
       </c>
     </row>
     <row r="140">
@@ -2541,7 +2535,7 @@
         <v>16</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.232637626103065</v>
+        <v>-0.180316034781935</v>
       </c>
     </row>
     <row r="141">
@@ -2552,7 +2546,7 @@
         <v>16</v>
       </c>
       <c r="C141" t="n">
-        <v>0.0417894624472832</v>
+        <v>-0.0189246100977294</v>
       </c>
     </row>
     <row r="142">
@@ -2563,7 +2557,7 @@
         <v>16</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.229843398746404</v>
+        <v>-1.00369217731305</v>
       </c>
     </row>
     <row r="143">
@@ -2574,7 +2568,7 @@
         <v>16</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.17044345274079</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="144">
@@ -2585,7 +2579,7 @@
         <v>16</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.157578351251149</v>
       </c>
     </row>
     <row r="145">
@@ -2607,7 +2601,7 @@
         <v>16</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.0672452638932928</v>
+        <v>0.0436299205332167</v>
       </c>
     </row>
     <row r="147">
@@ -2629,7 +2623,7 @@
         <v>16</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.259668697698205</v>
+        <v>-0.544999908084101</v>
       </c>
     </row>
     <row r="149">
@@ -2640,7 +2634,7 @@
         <v>16</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.408263165697595</v>
+        <v>-0.611974067928663</v>
       </c>
     </row>
     <row r="150">
@@ -2651,7 +2645,7 @@
         <v>16</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.0765625176836051</v>
+        <v>-1.44372386623744</v>
       </c>
     </row>
     <row r="151">
@@ -2662,7 +2656,7 @@
         <v>16</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.337081831616783</v>
+        <v>-0.232430691241972</v>
       </c>
     </row>
     <row r="152">
@@ -2673,7 +2667,7 @@
         <v>16</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.708540475025397</v>
+        <v>-0.372548164574211</v>
       </c>
     </row>
     <row r="153">
@@ -2684,7 +2678,7 @@
         <v>16</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.327462225375052</v>
+        <v>-1.37948678916425</v>
       </c>
     </row>
     <row r="154">
@@ -2706,7 +2700,7 @@
         <v>16</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.403536970295437</v>
+        <v>-0.427397240935761</v>
       </c>
     </row>
     <row r="156">
@@ -2717,7 +2711,7 @@
         <v>16</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.739669946166804</v>
       </c>
     </row>
     <row r="157">
@@ -2728,7 +2722,7 @@
         <v>16</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.620541272368613</v>
+        <v>-0.78187871132938</v>
       </c>
     </row>
     <row r="158">
@@ -2739,7 +2733,7 @@
         <v>16</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.45094348848919</v>
+        <v>-0.508378360476215</v>
       </c>
     </row>
     <row r="159">
@@ -2761,7 +2755,7 @@
         <v>16</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.194085503760283</v>
+        <v>-0.981636138755882</v>
       </c>
     </row>
     <row r="161">
@@ -2772,7 +2766,7 @@
         <v>16</v>
       </c>
       <c r="C161" t="n">
-        <v>-1.11839132229793</v>
+        <v>-0.24824893685153</v>
       </c>
     </row>
     <row r="162">
@@ -2783,7 +2777,7 @@
         <v>16</v>
       </c>
       <c r="C162" t="n">
-        <v>-0.548566938824746</v>
+        <v>-0.726296979831654</v>
       </c>
     </row>
     <row r="163">
@@ -2816,7 +2810,7 @@
         <v>16</v>
       </c>
       <c r="C165" t="n">
-        <v>0.0536824912454436</v>
+        <v>0.0411193725188805</v>
       </c>
     </row>
     <row r="166">
@@ -2827,7 +2821,7 @@
         <v>16</v>
       </c>
       <c r="C166" t="n">
-        <v>0.103282704618799</v>
+        <v>0.334091769318769</v>
       </c>
     </row>
     <row r="167">
@@ -2849,7 +2843,7 @@
         <v>16</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.49598950161113</v>
+        <v>-0.39740584807266</v>
       </c>
     </row>
     <row r="169">
@@ -2860,7 +2854,7 @@
         <v>16</v>
       </c>
       <c r="C169" t="n">
-        <v>0.184796854587544</v>
+        <v>-1.33585531817037</v>
       </c>
     </row>
     <row r="170">
@@ -2871,7 +2865,7 @@
         <v>16</v>
       </c>
       <c r="C170" t="n">
-        <v>-1.90373782679841</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="171">
@@ -2882,7 +2876,7 @@
         <v>16</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.405552702685949</v>
       </c>
     </row>
     <row r="172">
@@ -2893,7 +2887,7 @@
         <v>16</v>
       </c>
       <c r="C172" t="n">
-        <v>0.306542567191693</v>
+        <v>-0.361943190666889</v>
       </c>
     </row>
     <row r="173">
@@ -2904,7 +2898,7 @@
         <v>16</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.622310561707602</v>
+        <v>-0.0271641690794211</v>
       </c>
     </row>
     <row r="174">
@@ -2915,7 +2909,7 @@
         <v>16</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.356909882757277</v>
+        <v>-0.256791846465523</v>
       </c>
     </row>
     <row r="175">
@@ -2926,7 +2920,7 @@
         <v>16</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.175121465732978</v>
+        <v>0.228974544024437</v>
       </c>
     </row>
     <row r="176">
@@ -2937,7 +2931,7 @@
         <v>16</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.110218634082711</v>
+        <v>-3.31384431432882</v>
       </c>
     </row>
     <row r="177">
@@ -2948,7 +2942,7 @@
         <v>16</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.256868341150042</v>
+        <v>-0.216452733876803</v>
       </c>
     </row>
     <row r="178">
@@ -2959,7 +2953,7 @@
         <v>16</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.232803368370673</v>
+        <v>-0.297301372040021</v>
       </c>
     </row>
     <row r="179">
@@ -2970,7 +2964,7 @@
         <v>16</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.263876210398759</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="180">
@@ -2981,7 +2975,7 @@
         <v>16</v>
       </c>
       <c r="C180" t="n">
-        <v>0.192258143693733</v>
+        <v>-1.53458758180986</v>
       </c>
     </row>
     <row r="181">
@@ -2992,7 +2986,7 @@
         <v>16</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.6864749665974</v>
+        <v>-0.438326810182427</v>
       </c>
     </row>
     <row r="182">
@@ -3003,7 +2997,7 @@
         <v>16</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.777244861550889</v>
+        <v>-0.52121829526809</v>
       </c>
     </row>
     <row r="183">
@@ -3014,7 +3008,7 @@
         <v>16</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.278525195363873</v>
+        <v>-0.352428531262746</v>
       </c>
     </row>
     <row r="184">
@@ -3025,7 +3019,7 @@
         <v>16</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.362049950830926</v>
+        <v>-0.733870110569612</v>
       </c>
     </row>
     <row r="185">
@@ -3036,7 +3030,7 @@
         <v>16</v>
       </c>
       <c r="C185" t="n">
-        <v>0.336812684056776</v>
+        <v>0.476694999694586</v>
       </c>
     </row>
     <row r="186">
@@ -3047,7 +3041,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="n">
-        <v>0.749994658481338</v>
+        <v>0.677026792191488</v>
       </c>
     </row>
     <row r="187">
@@ -3058,7 +3052,7 @@
         <v>16</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.423401083450119</v>
       </c>
     </row>
     <row r="188">
@@ -3069,7 +3063,7 @@
         <v>16</v>
       </c>
       <c r="C188" t="n">
-        <v>0.272244312053169</v>
+        <v>-0.51239958644728</v>
       </c>
     </row>
     <row r="189">
@@ -3080,7 +3074,7 @@
         <v>16</v>
       </c>
       <c r="C189" t="n">
-        <v>0.0777399563576607</v>
+        <v>0.309422890385057</v>
       </c>
     </row>
     <row r="190">
@@ -3091,7 +3085,7 @@
         <v>16</v>
       </c>
       <c r="C190" t="n">
-        <v>0.508541723338892</v>
+        <v>0.0681485247194177</v>
       </c>
     </row>
     <row r="191">
@@ -3113,7 +3107,7 @@
         <v>16</v>
       </c>
       <c r="C192" t="n">
-        <v>-1.27434122726306</v>
+        <v>-0.353801971869854</v>
       </c>
     </row>
     <row r="193">
@@ -3124,7 +3118,7 @@
         <v>16</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.230052988281957</v>
       </c>
     </row>
     <row r="194">
@@ -3135,7 +3129,7 @@
         <v>16</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.541603917613003</v>
+        <v>0.0558896741104788</v>
       </c>
     </row>
     <row r="195">
@@ -3146,7 +3140,7 @@
         <v>16</v>
       </c>
       <c r="C195" t="n">
-        <v>-1.02453759889597</v>
+        <v>-0.502735604625675</v>
       </c>
     </row>
     <row r="196">
@@ -3157,7 +3151,7 @@
         <v>16</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.49720735745419</v>
       </c>
     </row>
     <row r="197">
@@ -3168,7 +3162,7 @@
         <v>16</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.649319474822581</v>
       </c>
     </row>
     <row r="198">
@@ -3179,7 +3173,7 @@
         <v>16</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.678271236812305</v>
+        <v>-4.12481065769709</v>
       </c>
     </row>
     <row r="199">
@@ -3190,7 +3184,7 @@
         <v>16</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.126814502030753</v>
       </c>
     </row>
     <row r="200">
@@ -3201,7 +3195,7 @@
         <v>16</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.56997263939294</v>
+        <v>-0.435021611511133</v>
       </c>
     </row>
     <row r="201">
@@ -3223,7 +3217,7 @@
         <v>16</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.596258885743321</v>
+        <v>-2.22196499722703</v>
       </c>
     </row>
     <row r="203">
@@ -3234,7 +3228,7 @@
         <v>16</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.371643274469913</v>
       </c>
     </row>
     <row r="204">
@@ -3245,7 +3239,7 @@
         <v>16</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.210131798122269</v>
+        <v>-0.855397518154677</v>
       </c>
     </row>
     <row r="205">
@@ -3267,7 +3261,7 @@
         <v>16</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.183501286173559</v>
+        <v>-0.335921506677165</v>
       </c>
     </row>
     <row r="207">
@@ -3278,7 +3272,7 @@
         <v>16</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.378566365017421</v>
+        <v>-2.32304971172396</v>
       </c>
     </row>
     <row r="208">
@@ -3289,7 +3283,7 @@
         <v>16</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.544350486887476</v>
+        <v>-0.588929108102866</v>
       </c>
     </row>
     <row r="209">
@@ -3311,7 +3305,7 @@
         <v>16</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.414913690099509</v>
+        <v>-0.297912139840412</v>
       </c>
     </row>
     <row r="211">
@@ -3322,7 +3316,7 @@
         <v>16</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.178110178700317</v>
+        <v>-0.164744005324204</v>
       </c>
     </row>
     <row r="212">
@@ -3333,7 +3327,7 @@
         <v>16</v>
       </c>
       <c r="C212" t="n">
-        <v>-1.37144579544224</v>
+        <v>0.564080456003333</v>
       </c>
     </row>
     <row r="213">
@@ -3344,7 +3338,7 @@
         <v>16</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.133797275782301</v>
+        <v>-0.51858832161044</v>
       </c>
     </row>
     <row r="214">
@@ -3355,7 +3349,7 @@
         <v>16</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.43563823167945</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="215">
@@ -3366,7 +3360,7 @@
         <v>16</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.183333453415964</v>
       </c>
     </row>
     <row r="216">
@@ -3377,7 +3371,7 @@
         <v>16</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.239330210862031</v>
+        <v>-0.398035626078193</v>
       </c>
     </row>
     <row r="217">
@@ -3388,7 +3382,7 @@
         <v>16</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.417575303746915</v>
+        <v>-0.198823292711258</v>
       </c>
     </row>
     <row r="218">
@@ -3399,7 +3393,7 @@
         <v>16</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.53946102649565</v>
+        <v>-0.23042157885915</v>
       </c>
     </row>
     <row r="219">
@@ -3410,7 +3404,7 @@
         <v>16</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.22584761009861</v>
       </c>
     </row>
     <row r="220">
@@ -3421,7 +3415,7 @@
         <v>16</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.505715752107574</v>
       </c>
     </row>
     <row r="221">
@@ -3432,7 +3426,7 @@
         <v>16</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.252475971242896</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="222">
@@ -3443,7 +3437,7 @@
         <v>16</v>
       </c>
       <c r="C222" t="n">
-        <v>-1.77227503547964</v>
+        <v>-0.877470940345004</v>
       </c>
     </row>
     <row r="223">
@@ -3454,7 +3448,7 @@
         <v>16</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.761075133865677</v>
       </c>
     </row>
     <row r="224">
@@ -3476,7 +3470,7 @@
         <v>16</v>
       </c>
       <c r="C225" t="n">
-        <v>-0.169111937245318</v>
+        <v>-0.988027245517998</v>
       </c>
     </row>
     <row r="226">
@@ -3487,7 +3481,7 @@
         <v>16</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.327445540872574</v>
+        <v>-0.693864442145935</v>
       </c>
     </row>
     <row r="227">
@@ -3509,7 +3503,7 @@
         <v>16</v>
       </c>
       <c r="C228" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.707728875069674</v>
       </c>
     </row>
     <row r="229">
@@ -3520,7 +3514,7 @@
         <v>16</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.212803330664073</v>
+        <v>-0.187596536551127</v>
       </c>
     </row>
     <row r="230">
@@ -3531,7 +3525,7 @@
         <v>16</v>
       </c>
       <c r="C230" t="n">
-        <v>-0.421803789308496</v>
+        <v>-0.261991323732214</v>
       </c>
     </row>
     <row r="231">
@@ -3542,7 +3536,7 @@
         <v>16</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.156010477368847</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="232">
@@ -3553,7 +3547,7 @@
         <v>16</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.114227256545296</v>
+        <v>-0.957664677283248</v>
       </c>
     </row>
     <row r="233">
@@ -3575,7 +3569,7 @@
         <v>16</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.227412320173881</v>
+        <v>-0.397554225363952</v>
       </c>
     </row>
     <row r="235">
@@ -3586,7 +3580,7 @@
         <v>16</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.165934787999007</v>
+        <v>-0.760846010419421</v>
       </c>
     </row>
     <row r="236">
@@ -3597,7 +3591,7 @@
         <v>16</v>
       </c>
       <c r="C236" t="n">
-        <v>-1.06490346493161</v>
+        <v>-1.10980257812973</v>
       </c>
     </row>
     <row r="237">
@@ -3608,7 +3602,7 @@
         <v>16</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.647507858336478</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="238">
@@ -3619,7 +3613,7 @@
         <v>16</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.331265451200921</v>
+        <v>-0.617895389813382</v>
       </c>
     </row>
     <row r="239">
@@ -3641,7 +3635,7 @@
         <v>16</v>
       </c>
       <c r="C240" t="n">
-        <v>-0.169703438222502</v>
+        <v>-0.71341899324893</v>
       </c>
     </row>
     <row r="241">
@@ -3652,7 +3646,7 @@
         <v>16</v>
       </c>
       <c r="C241" t="n">
-        <v>-1.15314484015486</v>
+        <v>-0.425242308950767</v>
       </c>
     </row>
     <row r="242">
@@ -3674,7 +3668,7 @@
         <v>16</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.375637024553225</v>
+        <v>-1.15778985553022</v>
       </c>
     </row>
     <row r="244">
@@ -3685,7 +3679,7 @@
         <v>16</v>
       </c>
       <c r="C244" t="n">
-        <v>-1.41287999338383</v>
+        <v>-0.483378143222376</v>
       </c>
     </row>
     <row r="245">
@@ -3696,7 +3690,7 @@
         <v>16</v>
       </c>
       <c r="C245" t="n">
-        <v>-0.357073166087417</v>
+        <v>-0.537006146724431</v>
       </c>
     </row>
     <row r="246">
@@ -3707,7 +3701,7 @@
         <v>16</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.732595556178088</v>
+        <v>-0.583590219296035</v>
       </c>
     </row>
     <row r="247">
@@ -3718,7 +3712,7 @@
         <v>16</v>
       </c>
       <c r="C247" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.517124938796835</v>
       </c>
     </row>
     <row r="248">
@@ -3729,7 +3723,7 @@
         <v>16</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.276698980056675</v>
       </c>
     </row>
     <row r="249">
@@ -3740,7 +3734,7 @@
         <v>16</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.727243500750521</v>
+        <v>-1.15267794875512</v>
       </c>
     </row>
     <row r="250">
@@ -3751,7 +3745,7 @@
         <v>16</v>
       </c>
       <c r="C250" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.170961312165726</v>
       </c>
     </row>
     <row r="251">
@@ -3762,7 +3756,7 @@
         <v>16</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.388441482916309</v>
+        <v>-1.04096097860479</v>
       </c>
     </row>
     <row r="252">
@@ -3773,7 +3767,7 @@
         <v>16</v>
       </c>
       <c r="C252" t="n">
-        <v>-0.355037896053381</v>
+        <v>-0.651840795466343</v>
       </c>
     </row>
     <row r="253">
@@ -3784,7 +3778,7 @@
         <v>16</v>
       </c>
       <c r="C253" t="n">
-        <v>-0.218154714443088</v>
+        <v>-0.879574003705291</v>
       </c>
     </row>
     <row r="254">
@@ -3795,7 +3789,7 @@
         <v>16</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.288777628728147</v>
+        <v>-0.804914517499237</v>
       </c>
     </row>
     <row r="255">
@@ -3806,7 +3800,7 @@
         <v>16</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.252250931776335</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="256">
@@ -3817,7 +3811,7 @@
         <v>16</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.179745605162449</v>
+        <v>-0.184083115326531</v>
       </c>
     </row>
     <row r="257">
@@ -3839,7 +3833,7 @@
         <v>16</v>
       </c>
       <c r="C258" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.473528904454181</v>
       </c>
     </row>
     <row r="259">
@@ -3850,7 +3844,7 @@
         <v>16</v>
       </c>
       <c r="C259" t="n">
-        <v>-0.192390130152957</v>
+        <v>-0.209510500778577</v>
       </c>
     </row>
     <row r="260">
@@ -3861,7 +3855,7 @@
         <v>16</v>
       </c>
       <c r="C260" t="n">
-        <v>-0.659275463847909</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="261">
@@ -3872,7 +3866,7 @@
         <v>16</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.300024727989822</v>
+        <v>-0.357273208052559</v>
       </c>
     </row>
     <row r="262">
@@ -3883,7 +3877,7 @@
         <v>16</v>
       </c>
       <c r="C262" t="n">
-        <v>-0.247261587825503</v>
+        <v>-1.08222618114644</v>
       </c>
     </row>
     <row r="263">
@@ -3905,7 +3899,7 @@
         <v>16</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.3933092616313</v>
+        <v>-0.838525459735475</v>
       </c>
     </row>
     <row r="265">
@@ -3916,7 +3910,7 @@
         <v>16</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.390185979028026</v>
+        <v>-0.992941838786174</v>
       </c>
     </row>
     <row r="266">
@@ -3927,7 +3921,7 @@
         <v>16</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.194066632129998</v>
+        <v>-0.311451400954543</v>
       </c>
     </row>
     <row r="267">
@@ -3938,7 +3932,7 @@
         <v>16</v>
       </c>
       <c r="C267" t="n">
-        <v>-1.40461113411606</v>
+        <v>-2.88419427459878</v>
       </c>
     </row>
     <row r="268">
@@ -3949,7 +3943,7 @@
         <v>16</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.100310404483539</v>
+        <v>-0.728863966735161</v>
       </c>
     </row>
     <row r="269">
@@ -3960,7 +3954,7 @@
         <v>16</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.179831539319519</v>
       </c>
     </row>
     <row r="270">
@@ -3971,7 +3965,7 @@
         <v>16</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.51672882167076</v>
       </c>
     </row>
     <row r="271">
@@ -3982,7 +3976,7 @@
         <v>16</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.285072302028132</v>
+        <v>-1.28984678307443</v>
       </c>
     </row>
     <row r="272">
@@ -3993,7 +3987,7 @@
         <v>16</v>
       </c>
       <c r="C272" t="n">
-        <v>-1.42668731489052</v>
+        <v>-1.85295376135247</v>
       </c>
     </row>
     <row r="273">
@@ -4004,7 +3998,7 @@
         <v>16</v>
       </c>
       <c r="C273" t="n">
-        <v>-0.22894972748123</v>
+        <v>-0.663754564553467</v>
       </c>
     </row>
     <row r="274">
@@ -4015,7 +4009,7 @@
         <v>16</v>
       </c>
       <c r="C274" t="n">
-        <v>-0.667329694191051</v>
+        <v>-0.753084890992401</v>
       </c>
     </row>
     <row r="275">
@@ -4026,7 +4020,7 @@
         <v>16</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.197606894121026</v>
+        <v>-0.194551112751078</v>
       </c>
     </row>
     <row r="276">
@@ -4037,7 +4031,7 @@
         <v>16</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.339985696238112</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="277">
@@ -4059,7 +4053,7 @@
         <v>16</v>
       </c>
       <c r="C278" t="n">
-        <v>-0.173556204081982</v>
+        <v>-0.551103967219631</v>
       </c>
     </row>
     <row r="279">
@@ -4070,7 +4064,7 @@
         <v>16</v>
       </c>
       <c r="C279" t="n">
-        <v>-0.239775700529089</v>
+        <v>-1.54231181892163</v>
       </c>
     </row>
     <row r="280">
@@ -4092,7 +4086,7 @@
         <v>16</v>
       </c>
       <c r="C281" t="n">
-        <v>-0.119530132515909</v>
+        <v>-2.2033316920894</v>
       </c>
     </row>
     <row r="282">
@@ -4103,7 +4097,7 @@
         <v>16</v>
       </c>
       <c r="C282" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.0488889934586111</v>
       </c>
     </row>
     <row r="283">
@@ -4114,7 +4108,7 @@
         <v>16</v>
       </c>
       <c r="C283" t="n">
-        <v>-0.622611851896843</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="284">
@@ -4125,7 +4119,7 @@
         <v>16</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.268112799313917</v>
+        <v>-0.692141608151845</v>
       </c>
     </row>
     <row r="285">
@@ -4136,7 +4130,7 @@
         <v>16</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.571159607745301</v>
+        <v>-0.450003883664512</v>
       </c>
     </row>
     <row r="286">
@@ -4147,7 +4141,7 @@
         <v>16</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.211122520912563</v>
+        <v>-0.288169721139849</v>
       </c>
     </row>
     <row r="287">
@@ -4158,7 +4152,7 @@
         <v>16</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.18277630285039</v>
       </c>
     </row>
     <row r="288">
@@ -4169,7 +4163,7 @@
         <v>16</v>
       </c>
       <c r="C288" t="n">
-        <v>-1.40294225699723</v>
+        <v>-0.288685808512271</v>
       </c>
     </row>
     <row r="289">
@@ -4180,7 +4174,7 @@
         <v>16</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.66137774984615</v>
+        <v>-0.735411074681137</v>
       </c>
     </row>
     <row r="290">
@@ -4191,7 +4185,7 @@
         <v>16</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.295567849273009</v>
+        <v>-0.478416873840811</v>
       </c>
     </row>
     <row r="291">
@@ -4213,7 +4207,7 @@
         <v>16</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.670624366694096</v>
+        <v>-1.08020636306361</v>
       </c>
     </row>
     <row r="293">
@@ -4224,7 +4218,7 @@
         <v>16</v>
       </c>
       <c r="C293" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.343442320322481</v>
       </c>
     </row>
     <row r="294">
@@ -4235,7 +4229,7 @@
         <v>16</v>
       </c>
       <c r="C294" t="n">
-        <v>-0.154887806017019</v>
+        <v>-0.450141283843761</v>
       </c>
     </row>
     <row r="295">
@@ -4246,7 +4240,7 @@
         <v>16</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.171278012360418</v>
+        <v>-0.176196990832726</v>
       </c>
     </row>
     <row r="296">
@@ -4257,7 +4251,7 @@
         <v>16</v>
       </c>
       <c r="C296" t="n">
-        <v>-0.921680640685184</v>
+        <v>-2.70197919915531</v>
       </c>
     </row>
     <row r="297">
@@ -4268,7 +4262,7 @@
         <v>16</v>
       </c>
       <c r="C297" t="n">
-        <v>0.633024207113996</v>
+        <v>0.438390032848255</v>
       </c>
     </row>
     <row r="298">
@@ -4279,7 +4273,7 @@
         <v>16</v>
       </c>
       <c r="C298" t="n">
-        <v>-2.43393721464548</v>
+        <v>-0.383774235849415</v>
       </c>
     </row>
     <row r="299">
@@ -4290,7 +4284,7 @@
         <v>16</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.24771923588974</v>
       </c>
     </row>
     <row r="300">
@@ -4301,7 +4295,7 @@
         <v>16</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.340338343716465</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="301">
@@ -4312,7 +4306,7 @@
         <v>16</v>
       </c>
       <c r="C301" t="n">
-        <v>-0.303229104073129</v>
+        <v>-0.792208975892381</v>
       </c>
     </row>
     <row r="302">
@@ -4323,7 +4317,7 @@
         <v>16</v>
       </c>
       <c r="C302" t="n">
-        <v>-0.327750856399777</v>
+        <v>-0.528327213061387</v>
       </c>
     </row>
     <row r="303">
@@ -4334,7 +4328,7 @@
         <v>16</v>
       </c>
       <c r="C303" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.536877995766104</v>
       </c>
     </row>
     <row r="304">
@@ -4345,7 +4339,7 @@
         <v>16</v>
       </c>
       <c r="C304" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.509268642382976</v>
       </c>
     </row>
     <row r="305">
@@ -4367,7 +4361,7 @@
         <v>16</v>
       </c>
       <c r="C306" t="n">
-        <v>-0.182711834945677</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="307">
@@ -4378,7 +4372,7 @@
         <v>16</v>
       </c>
       <c r="C307" t="n">
-        <v>-0.257018864974181</v>
+        <v>0.392174035453034</v>
       </c>
     </row>
     <row r="308">
@@ -4389,7 +4383,7 @@
         <v>16</v>
       </c>
       <c r="C308" t="n">
-        <v>-0.258243564117839</v>
+        <v>-0.303897139637597</v>
       </c>
     </row>
     <row r="309">
@@ -4400,7 +4394,7 @@
         <v>16</v>
       </c>
       <c r="C309" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.812757256573176</v>
       </c>
     </row>
     <row r="310">
@@ -4411,7 +4405,7 @@
         <v>16</v>
       </c>
       <c r="C310" t="n">
-        <v>-0.35085488902427</v>
+        <v>-0.463650579725734</v>
       </c>
     </row>
     <row r="311">
@@ -4422,7 +4416,7 @@
         <v>16</v>
       </c>
       <c r="C311" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.239563134556322</v>
       </c>
     </row>
     <row r="312">
@@ -4433,7 +4427,7 @@
         <v>16</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.934252619422139</v>
+        <v>-0.690272205636639</v>
       </c>
     </row>
     <row r="313">
@@ -4444,7 +4438,7 @@
         <v>16</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.19204065118051</v>
+        <v>-0.851356797981675</v>
       </c>
     </row>
     <row r="314">
@@ -4455,7 +4449,7 @@
         <v>16</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.188440739077196</v>
+        <v>-0.2414186863656</v>
       </c>
     </row>
     <row r="315">
@@ -4466,7 +4460,7 @@
         <v>16</v>
       </c>
       <c r="C315" t="n">
-        <v>-0.177617958832567</v>
+        <v>-0.110068319969415</v>
       </c>
     </row>
     <row r="316">
@@ -4488,7 +4482,7 @@
         <v>16</v>
       </c>
       <c r="C317" t="n">
-        <v>-0.287296622702521</v>
+        <v>-0.269672948932425</v>
       </c>
     </row>
     <row r="318">
@@ -4499,7 +4493,7 @@
         <v>16</v>
       </c>
       <c r="C318" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.669141049567212</v>
       </c>
     </row>
     <row r="319">
@@ -4521,7 +4515,7 @@
         <v>16</v>
       </c>
       <c r="C320" t="n">
-        <v>-0.461257502003565</v>
+        <v>-0.506989289724184</v>
       </c>
     </row>
     <row r="321">
@@ -4532,7 +4526,7 @@
         <v>16</v>
       </c>
       <c r="C321" t="n">
-        <v>-0.350192881919361</v>
+        <v>-0.450880315793789</v>
       </c>
     </row>
     <row r="322">
@@ -4543,7 +4537,7 @@
         <v>16</v>
       </c>
       <c r="C322" t="n">
-        <v>-0.426398435504236</v>
+        <v>-0.349219780699314</v>
       </c>
     </row>
     <row r="323">
@@ -4554,7 +4548,7 @@
         <v>16</v>
       </c>
       <c r="C323" t="n">
-        <v>0.232154729862156</v>
+        <v>-0.398571606767836</v>
       </c>
     </row>
     <row r="324">
@@ -4565,7 +4559,7 @@
         <v>16</v>
       </c>
       <c r="C324" t="n">
-        <v>-0.342565180074306</v>
+        <v>-0.358491207474753</v>
       </c>
     </row>
     <row r="325">
@@ -4576,7 +4570,7 @@
         <v>16</v>
       </c>
       <c r="C325" t="n">
-        <v>-0.248022899763099</v>
+        <v>-0.27167758956395</v>
       </c>
     </row>
     <row r="326">
@@ -4587,7 +4581,7 @@
         <v>16</v>
       </c>
       <c r="C326" t="n">
-        <v>-1.32239694592832</v>
+        <v>-0.169360183474423</v>
       </c>
     </row>
     <row r="327">
@@ -4609,7 +4603,7 @@
         <v>16</v>
       </c>
       <c r="C328" t="n">
-        <v>-0.518993835870092</v>
+        <v>-0.451823382440447</v>
       </c>
     </row>
     <row r="329">
@@ -4620,7 +4614,7 @@
         <v>16</v>
       </c>
       <c r="C329" t="n">
-        <v>-0.411127921580538</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="330">
@@ -4631,7 +4625,7 @@
         <v>16</v>
       </c>
       <c r="C330" t="n">
-        <v>-0.597954591637724</v>
+        <v>0.157822438986441</v>
       </c>
     </row>
     <row r="331">
@@ -4642,7 +4636,7 @@
         <v>16</v>
       </c>
       <c r="C331" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.16104590516752</v>
       </c>
     </row>
     <row r="332">
@@ -4653,7 +4647,7 @@
         <v>16</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.221507390542293</v>
+        <v>-0.240156827702573</v>
       </c>
     </row>
     <row r="333">
@@ -4664,7 +4658,7 @@
         <v>16</v>
       </c>
       <c r="C333" t="n">
-        <v>-0.544027896019602</v>
+        <v>-1.060425484594</v>
       </c>
     </row>
     <row r="334">
@@ -4675,7 +4669,7 @@
         <v>16</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.193620075206826</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="335">
@@ -4686,7 +4680,7 @@
         <v>16</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.174383185678467</v>
       </c>
     </row>
     <row r="336">
@@ -4697,7 +4691,7 @@
         <v>16</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.647506974557781</v>
+        <v>-1.34602400236268</v>
       </c>
     </row>
     <row r="337">
@@ -4708,7 +4702,7 @@
         <v>16</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.136030966548496</v>
+        <v>0.0936631130428357</v>
       </c>
     </row>
     <row r="338">
@@ -4719,7 +4713,7 @@
         <v>16</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.172388998397524</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="339">
@@ -4730,7 +4724,7 @@
         <v>16</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.199643122241418</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="340">
@@ -4741,7 +4735,7 @@
         <v>16</v>
       </c>
       <c r="C340" t="n">
-        <v>-0.139523640175799</v>
+        <v>-0.618212352523678</v>
       </c>
     </row>
     <row r="341">
@@ -4752,7 +4746,7 @@
         <v>16</v>
       </c>
       <c r="C341" t="n">
-        <v>-0.172710755332019</v>
+        <v>-0.172476175616506</v>
       </c>
     </row>
     <row r="342">
@@ -4763,7 +4757,7 @@
         <v>16</v>
       </c>
       <c r="C342" t="n">
-        <v>-0.219852559941186</v>
+        <v>-1.81811775457943</v>
       </c>
     </row>
     <row r="343">
@@ -4774,7 +4768,7 @@
         <v>16</v>
       </c>
       <c r="C343" t="n">
-        <v>-1.23389942736285</v>
+        <v>-0.914343926115767</v>
       </c>
     </row>
     <row r="344">
@@ -4796,7 +4790,7 @@
         <v>16</v>
       </c>
       <c r="C345" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.199976269083856</v>
       </c>
     </row>
     <row r="346">
@@ -4807,7 +4801,7 @@
         <v>16</v>
       </c>
       <c r="C346" t="n">
-        <v>0.140509067573999</v>
+        <v>0.0552063633127519</v>
       </c>
     </row>
     <row r="347">
@@ -4818,7 +4812,7 @@
         <v>16</v>
       </c>
       <c r="C347" t="n">
-        <v>-0.348504630219163</v>
+        <v>-1.24342849709616</v>
       </c>
     </row>
     <row r="348">
@@ -4829,7 +4823,7 @@
         <v>16</v>
       </c>
       <c r="C348" t="n">
-        <v>0.0147784314971333</v>
+        <v>0.124620498673734</v>
       </c>
     </row>
     <row r="349">
@@ -4840,7 +4834,7 @@
         <v>16</v>
       </c>
       <c r="C349" t="n">
-        <v>-0.286571367105732</v>
+        <v>-0.579370040465182</v>
       </c>
     </row>
     <row r="350">
@@ -4851,7 +4845,7 @@
         <v>16</v>
       </c>
       <c r="C350" t="n">
-        <v>-0.650720894271503</v>
+        <v>-1.38778076758329</v>
       </c>
     </row>
     <row r="351">
@@ -4862,7 +4856,7 @@
         <v>16</v>
       </c>
       <c r="C351" t="n">
-        <v>-1.04758869111714</v>
+        <v>-0.308344088110665</v>
       </c>
     </row>
     <row r="352">
@@ -4873,7 +4867,7 @@
         <v>16</v>
       </c>
       <c r="C352" t="n">
-        <v>-0.618650576848203</v>
+        <v>-0.535832863457961</v>
       </c>
     </row>
     <row r="353">
@@ -4884,7 +4878,7 @@
         <v>16</v>
       </c>
       <c r="C353" t="n">
-        <v>0.0071425780670139</v>
+        <v>0.553374696425083</v>
       </c>
     </row>
     <row r="354">
@@ -4906,7 +4900,7 @@
         <v>16</v>
       </c>
       <c r="C355" t="n">
-        <v>-0.422341405543793</v>
+        <v>-0.443541401836087</v>
       </c>
     </row>
     <row r="356">
@@ -4917,7 +4911,7 @@
         <v>16</v>
       </c>
       <c r="C356" t="n">
-        <v>-1.53228462978725</v>
+        <v>-1.28839646042857</v>
       </c>
     </row>
     <row r="357">
@@ -4928,7 +4922,7 @@
         <v>16</v>
       </c>
       <c r="C357" t="n">
-        <v>-0.535230485942772</v>
+        <v>-0.715241451213767</v>
       </c>
     </row>
     <row r="358">
@@ -4939,7 +4933,7 @@
         <v>16</v>
       </c>
       <c r="C358" t="n">
-        <v>-0.323492760039186</v>
+        <v>-0.213167133008407</v>
       </c>
     </row>
     <row r="359">
@@ -4961,7 +4955,7 @@
         <v>16</v>
       </c>
       <c r="C360" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.123460036641943</v>
       </c>
     </row>
     <row r="361">
@@ -4972,7 +4966,7 @@
         <v>16</v>
       </c>
       <c r="C361" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.227315711234993</v>
       </c>
     </row>
     <row r="362">
@@ -4983,7 +4977,7 @@
         <v>16</v>
       </c>
       <c r="C362" t="n">
-        <v>-0.303590969011282</v>
+        <v>-0.400798329692514</v>
       </c>
     </row>
     <row r="363">
@@ -5005,7 +4999,7 @@
         <v>16</v>
       </c>
       <c r="C364" t="n">
-        <v>-0.24388237430039</v>
+        <v>-0.21619861563944</v>
       </c>
     </row>
     <row r="365">
@@ -5016,7 +5010,7 @@
         <v>16</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.192814718054449</v>
+        <v>-0.0949594155318014</v>
       </c>
     </row>
     <row r="366">
@@ -5027,7 +5021,7 @@
         <v>16</v>
       </c>
       <c r="C366" t="n">
-        <v>-0.194180606267258</v>
+        <v>-1.08638148773321</v>
       </c>
     </row>
     <row r="367">
@@ -5038,7 +5032,7 @@
         <v>16</v>
       </c>
       <c r="C367" t="n">
-        <v>-0.85813948722325</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="368">
@@ -5049,7 +5043,7 @@
         <v>16</v>
       </c>
       <c r="C368" t="n">
-        <v>-0.544802929259882</v>
+        <v>-2.15728214295309</v>
       </c>
     </row>
     <row r="369">
@@ -5060,7 +5054,7 @@
         <v>16</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.23430250106138</v>
+        <v>-1.00063029274373</v>
       </c>
     </row>
     <row r="370">
@@ -5071,7 +5065,7 @@
         <v>16</v>
       </c>
       <c r="C370" t="n">
-        <v>-0.428805780390313</v>
+        <v>-0.836067116572299</v>
       </c>
     </row>
     <row r="371">
@@ -5082,7 +5076,7 @@
         <v>16</v>
       </c>
       <c r="C371" t="n">
-        <v>-0.340074412778884</v>
+        <v>-0.184940189835735</v>
       </c>
     </row>
     <row r="372">
@@ -5093,7 +5087,7 @@
         <v>16</v>
       </c>
       <c r="C372" t="n">
-        <v>-0.263351454919574</v>
+        <v>-0.23827459275036</v>
       </c>
     </row>
     <row r="373">
@@ -5104,7 +5098,7 @@
         <v>16</v>
       </c>
       <c r="C373" t="n">
-        <v>-0.177642956643923</v>
+        <v>-0.752636721517712</v>
       </c>
     </row>
     <row r="374">
@@ -5115,7 +5109,7 @@
         <v>16</v>
       </c>
       <c r="C374" t="n">
-        <v>-0.252803310354029</v>
+        <v>-0.25064234085566</v>
       </c>
     </row>
     <row r="375">
@@ -5126,7 +5120,7 @@
         <v>16</v>
       </c>
       <c r="C375" t="n">
-        <v>0.401251279371134</v>
+        <v>0.437550039695952</v>
       </c>
     </row>
     <row r="376">
@@ -5137,7 +5131,7 @@
         <v>16</v>
       </c>
       <c r="C376" t="n">
-        <v>-0.714438262873539</v>
+        <v>-0.207696091893672</v>
       </c>
     </row>
     <row r="377">
@@ -5148,7 +5142,7 @@
         <v>16</v>
       </c>
       <c r="C377" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.230096961398797</v>
       </c>
     </row>
     <row r="378">
@@ -5159,7 +5153,7 @@
         <v>16</v>
       </c>
       <c r="C378" t="n">
-        <v>-0.484067185939721</v>
+        <v>-0.18001661864616</v>
       </c>
     </row>
     <row r="379">
@@ -5170,7 +5164,7 @@
         <v>16</v>
       </c>
       <c r="C379" t="n">
-        <v>-0.163351126509499</v>
+        <v>-0.369661368221617</v>
       </c>
     </row>
     <row r="380">
@@ -5181,7 +5175,7 @@
         <v>16</v>
       </c>
       <c r="C380" t="n">
-        <v>-0.47314025689951</v>
+        <v>-0.432237065220962</v>
       </c>
     </row>
     <row r="381">
@@ -5192,7 +5186,7 @@
         <v>16</v>
       </c>
       <c r="C381" t="n">
-        <v>-0.308289901668153</v>
+        <v>-0.390565594172147</v>
       </c>
     </row>
     <row r="382">
@@ -5203,7 +5197,7 @@
         <v>16</v>
       </c>
       <c r="C382" t="n">
-        <v>-0.766993623930816</v>
+        <v>-0.63924919236136</v>
       </c>
     </row>
     <row r="383">
@@ -5214,7 +5208,7 @@
         <v>16</v>
       </c>
       <c r="C383" t="n">
-        <v>-0.175329146906568</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="384">
@@ -5236,7 +5230,7 @@
         <v>16</v>
       </c>
       <c r="C385" t="n">
-        <v>-0.278299994144988</v>
+        <v>-0.0464036726166004</v>
       </c>
     </row>
     <row r="386">
@@ -5247,7 +5241,7 @@
         <v>16</v>
       </c>
       <c r="C386" t="n">
-        <v>-0.00545365321171976</v>
+        <v>-0.134732993544483</v>
       </c>
     </row>
     <row r="387">
@@ -5258,7 +5252,7 @@
         <v>16</v>
       </c>
       <c r="C387" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.959743314065518</v>
       </c>
     </row>
     <row r="388">
@@ -5269,7 +5263,7 @@
         <v>16</v>
       </c>
       <c r="C388" t="n">
-        <v>0.324789310566057</v>
+        <v>-0.416415565263549</v>
       </c>
     </row>
     <row r="389">
@@ -5280,7 +5274,7 @@
         <v>16</v>
       </c>
       <c r="C389" t="n">
-        <v>-0.0483324197012982</v>
+        <v>-0.207555143887555</v>
       </c>
     </row>
     <row r="390">
@@ -5291,7 +5285,7 @@
         <v>16</v>
       </c>
       <c r="C390" t="n">
-        <v>-0.228639142372543</v>
+        <v>-0.197578314755925</v>
       </c>
     </row>
     <row r="391">
@@ -5302,7 +5296,7 @@
         <v>16</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.212932311184881</v>
+        <v>-0.616772111274253</v>
       </c>
     </row>
     <row r="392">
@@ -5313,7 +5307,7 @@
         <v>16</v>
       </c>
       <c r="C392" t="n">
-        <v>-0.539375020179841</v>
+        <v>-0.239286450994915</v>
       </c>
     </row>
     <row r="393">
@@ -5335,7 +5329,7 @@
         <v>16</v>
       </c>
       <c r="C394" t="n">
-        <v>-0.671252378523634</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="395">
@@ -5346,7 +5340,7 @@
         <v>16</v>
       </c>
       <c r="C395" t="n">
-        <v>-0.831117359677242</v>
+        <v>-0.319588294756557</v>
       </c>
     </row>
     <row r="396">
@@ -5357,7 +5351,7 @@
         <v>16</v>
       </c>
       <c r="C396" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.25559857547767</v>
       </c>
     </row>
     <row r="397">
@@ -5368,7 +5362,7 @@
         <v>16</v>
       </c>
       <c r="C397" t="n">
-        <v>-3.63574554114086</v>
+        <v>-1.35298750829313</v>
       </c>
     </row>
     <row r="398">
@@ -5379,7 +5373,7 @@
         <v>16</v>
       </c>
       <c r="C398" t="n">
-        <v>-1.8549990604098</v>
+        <v>-3.9709151479937</v>
       </c>
     </row>
     <row r="399">
@@ -5423,7 +5417,7 @@
         <v>16</v>
       </c>
       <c r="C402" t="n">
-        <v>-1.04053875048089</v>
+        <v>-2.6987387534226</v>
       </c>
     </row>
     <row r="403">
@@ -5445,7 +5439,7 @@
         <v>16</v>
       </c>
       <c r="C404" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.370154639703497</v>
       </c>
     </row>
     <row r="405">
@@ -5467,7 +5461,7 @@
         <v>16</v>
       </c>
       <c r="C406" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.517235480126737</v>
       </c>
     </row>
     <row r="407">
@@ -5478,7 +5472,7 @@
         <v>16</v>
       </c>
       <c r="C407" t="n">
-        <v>-0.560380202013486</v>
+        <v>-2.34711169490821</v>
       </c>
     </row>
     <row r="408">
@@ -5489,7 +5483,7 @@
         <v>16</v>
       </c>
       <c r="C408" t="n">
-        <v>-0.560367550531678</v>
+        <v>-0.417183743692714</v>
       </c>
     </row>
     <row r="409">
@@ -5511,7 +5505,7 @@
         <v>16</v>
       </c>
       <c r="C410" t="n">
-        <v>-0.21847060915509</v>
+        <v>-0.25869310088338</v>
       </c>
     </row>
     <row r="411">
@@ -5533,7 +5527,7 @@
         <v>16</v>
       </c>
       <c r="C412" t="n">
-        <v>-0.950229258396103</v>
+        <v>0.0415349761631818</v>
       </c>
     </row>
     <row r="413">
@@ -5544,7 +5538,7 @@
         <v>16</v>
       </c>
       <c r="C413" t="n">
-        <v>-0.147800557799511</v>
+        <v>0.092494490322781</v>
       </c>
     </row>
     <row r="414">
@@ -5555,7 +5549,7 @@
         <v>16</v>
       </c>
       <c r="C414" t="n">
-        <v>-0.8365931489028</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="415">
@@ -5566,7 +5560,7 @@
         <v>16</v>
       </c>
       <c r="C415" t="n">
-        <v>-0.309256447843576</v>
+        <v>-0.278108209212257</v>
       </c>
     </row>
     <row r="416">
@@ -5577,7 +5571,7 @@
         <v>16</v>
       </c>
       <c r="C416" t="n">
-        <v>-0.337721950942507</v>
+        <v>-0.529333608865255</v>
       </c>
     </row>
     <row r="417">
@@ -5588,7 +5582,7 @@
         <v>16</v>
       </c>
       <c r="C417" t="n">
-        <v>-0.811330922915029</v>
+        <v>-0.322569902657119</v>
       </c>
     </row>
     <row r="418">
@@ -5599,7 +5593,7 @@
         <v>16</v>
       </c>
       <c r="C418" t="n">
-        <v>-0.622198157077957</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="419">
@@ -5621,7 +5615,7 @@
         <v>16</v>
       </c>
       <c r="C420" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.596092203997252</v>
       </c>
     </row>
     <row r="421">
@@ -5643,7 +5637,7 @@
         <v>16</v>
       </c>
       <c r="C422" t="n">
-        <v>-2.02771325349116</v>
+        <v>-0.400986809996042</v>
       </c>
     </row>
     <row r="423">
@@ -5654,7 +5648,7 @@
         <v>16</v>
       </c>
       <c r="C423" t="n">
-        <v>-0.442792173029305</v>
+        <v>-0.660356246450743</v>
       </c>
     </row>
     <row r="424">
@@ -5665,7 +5659,7 @@
         <v>16</v>
       </c>
       <c r="C424" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.17317682198467</v>
       </c>
     </row>
     <row r="425">
@@ -5687,7 +5681,7 @@
         <v>16</v>
       </c>
       <c r="C426" t="n">
-        <v>-0.594799372614694</v>
+        <v>-0.567289609672324</v>
       </c>
     </row>
     <row r="427">
@@ -5709,7 +5703,7 @@
         <v>16</v>
       </c>
       <c r="C428" t="n">
-        <v>-0.16824390643754</v>
+        <v>-0.194411712226144</v>
       </c>
     </row>
     <row r="429">
@@ -5720,7 +5714,7 @@
         <v>16</v>
       </c>
       <c r="C429" t="n">
-        <v>-0.361934707444464</v>
+        <v>-0.195470973865544</v>
       </c>
     </row>
     <row r="430">
@@ -5742,7 +5736,7 @@
         <v>16</v>
       </c>
       <c r="C431" t="n">
-        <v>-2.59461107289344</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="432">
@@ -5753,7 +5747,7 @@
         <v>16</v>
       </c>
       <c r="C432" t="n">
-        <v>-0.084304194394661</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="433">
@@ -5775,7 +5769,7 @@
         <v>16</v>
       </c>
       <c r="C434" t="n">
-        <v>-0.198476808887812</v>
+        <v>-0.485554811718132</v>
       </c>
     </row>
     <row r="435">
@@ -5786,7 +5780,7 @@
         <v>16</v>
       </c>
       <c r="C435" t="n">
-        <v>-0.168393353731537</v>
+        <v>-0.474581843084852</v>
       </c>
     </row>
     <row r="436">
@@ -5797,7 +5791,7 @@
         <v>16</v>
       </c>
       <c r="C436" t="n">
-        <v>-0.502241292400948</v>
+        <v>-2.61848997084787</v>
       </c>
     </row>
     <row r="437">
@@ -5819,7 +5813,7 @@
         <v>16</v>
       </c>
       <c r="C438" t="n">
-        <v>-0.171111373377683</v>
+        <v>-0.708660912292844</v>
       </c>
     </row>
     <row r="439">
@@ -5830,7 +5824,7 @@
         <v>16</v>
       </c>
       <c r="C439" t="n">
-        <v>-0.204093998597743</v>
+        <v>-2.36391877555407</v>
       </c>
     </row>
     <row r="440">
@@ -5841,7 +5835,7 @@
         <v>16</v>
       </c>
       <c r="C440" t="n">
-        <v>-0.230512913670337</v>
+        <v>-0.722456490652094</v>
       </c>
     </row>
     <row r="441">
@@ -5852,7 +5846,7 @@
         <v>16</v>
       </c>
       <c r="C441" t="n">
-        <v>-1.37352321502624</v>
+        <v>-0.905899126928343</v>
       </c>
     </row>
     <row r="442">
@@ -5885,7 +5879,7 @@
         <v>16</v>
       </c>
       <c r="C444" t="n">
-        <v>-0.379900881165156</v>
+        <v>-0.758645382732809</v>
       </c>
     </row>
     <row r="445">
@@ -5896,7 +5890,7 @@
         <v>16</v>
       </c>
       <c r="C445" t="n">
-        <v>-0.791846215043363</v>
+        <v>-0.557658163895215</v>
       </c>
     </row>
     <row r="446">
@@ -5907,7 +5901,7 @@
         <v>16</v>
       </c>
       <c r="C446" t="n">
-        <v>-0.166325746180081</v>
+        <v>-0.205263348566771</v>
       </c>
     </row>
     <row r="447">
@@ -5918,7 +5912,7 @@
         <v>16</v>
       </c>
       <c r="C447" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.619967049371049</v>
       </c>
     </row>
     <row r="448">
@@ -5940,7 +5934,7 @@
         <v>16</v>
       </c>
       <c r="C449" t="n">
-        <v>-0.537535664346726</v>
+        <v>-1.00472330643046</v>
       </c>
     </row>
     <row r="450">
@@ -5951,7 +5945,7 @@
         <v>16</v>
       </c>
       <c r="C450" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.57947474538414</v>
       </c>
     </row>
     <row r="451">
@@ -5962,7 +5956,7 @@
         <v>16</v>
       </c>
       <c r="C451" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.251628177690575</v>
       </c>
     </row>
     <row r="452">
@@ -5973,7 +5967,7 @@
         <v>16</v>
       </c>
       <c r="C452" t="n">
-        <v>-0.234166632378294</v>
+        <v>-0.92527187220113</v>
       </c>
     </row>
     <row r="453">
@@ -5984,7 +5978,7 @@
         <v>16</v>
       </c>
       <c r="C453" t="n">
-        <v>-1.5733792899171</v>
+        <v>-1.35363540893725</v>
       </c>
     </row>
     <row r="454">
@@ -5995,7 +5989,7 @@
         <v>16</v>
       </c>
       <c r="C454" t="n">
-        <v>-0.246967682756273</v>
+        <v>-1.18232099746607</v>
       </c>
     </row>
     <row r="455">
@@ -6006,7 +6000,7 @@
         <v>16</v>
       </c>
       <c r="C455" t="n">
-        <v>-0.479551266729709</v>
+        <v>-0.484736810224361</v>
       </c>
     </row>
     <row r="456">
@@ -6017,7 +6011,7 @@
         <v>16</v>
       </c>
       <c r="C456" t="n">
-        <v>-0.341573867782812</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="457">
@@ -6039,7 +6033,7 @@
         <v>16</v>
       </c>
       <c r="C458" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.613397112643491</v>
       </c>
     </row>
     <row r="459">
@@ -6050,7 +6044,7 @@
         <v>16</v>
       </c>
       <c r="C459" t="n">
-        <v>-0.307812543614778</v>
+        <v>-0.311366798275596</v>
       </c>
     </row>
     <row r="460">
@@ -6061,7 +6055,7 @@
         <v>16</v>
       </c>
       <c r="C460" t="n">
-        <v>-0.216918714952861</v>
+        <v>-0.486838986393707</v>
       </c>
     </row>
     <row r="461">
@@ -6072,7 +6066,7 @@
         <v>16</v>
       </c>
       <c r="C461" t="n">
-        <v>-0.307028434498091</v>
+        <v>-0.702276690385031</v>
       </c>
     </row>
     <row r="462">
@@ -6094,7 +6088,7 @@
         <v>16</v>
       </c>
       <c r="C463" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.438110448290091</v>
       </c>
     </row>
     <row r="464">
@@ -6105,7 +6099,7 @@
         <v>16</v>
       </c>
       <c r="C464" t="n">
-        <v>-1.17489922950135</v>
+        <v>-0.471065290611625</v>
       </c>
     </row>
     <row r="465">
@@ -6116,7 +6110,7 @@
         <v>16</v>
       </c>
       <c r="C465" t="n">
-        <v>-0.46390014289541</v>
+        <v>-1.44467564807403</v>
       </c>
     </row>
     <row r="466">
@@ -6127,7 +6121,7 @@
         <v>16</v>
       </c>
       <c r="C466" t="n">
-        <v>-0.508747019108975</v>
+        <v>-0.941728184971495</v>
       </c>
     </row>
     <row r="467">
@@ -6138,7 +6132,7 @@
         <v>16</v>
       </c>
       <c r="C467" t="n">
-        <v>-2.1575732533222</v>
+        <v>-0.644209441415006</v>
       </c>
     </row>
     <row r="468">
@@ -6149,7 +6143,7 @@
         <v>16</v>
       </c>
       <c r="C468" t="n">
-        <v>-0.518379868739078</v>
+        <v>-0.245130407940702</v>
       </c>
     </row>
     <row r="469">
@@ -6160,7 +6154,7 @@
         <v>16</v>
       </c>
       <c r="C469" t="n">
-        <v>-0.193803328966078</v>
+        <v>-0.196789973608686</v>
       </c>
     </row>
     <row r="470">
@@ -6171,7 +6165,7 @@
         <v>16</v>
       </c>
       <c r="C470" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.789118110131505</v>
       </c>
     </row>
     <row r="471">
@@ -6182,7 +6176,7 @@
         <v>16</v>
       </c>
       <c r="C471" t="n">
-        <v>-0.504437695728726</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="472">
@@ -6193,7 +6187,7 @@
         <v>16</v>
       </c>
       <c r="C472" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.09192823468819</v>
       </c>
     </row>
     <row r="473">
@@ -6204,7 +6198,7 @@
         <v>16</v>
       </c>
       <c r="C473" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.80620947427821</v>
       </c>
     </row>
     <row r="474">
@@ -6215,7 +6209,7 @@
         <v>16</v>
       </c>
       <c r="C474" t="n">
-        <v>-0.752309086200781</v>
+        <v>-0.592712511021756</v>
       </c>
     </row>
     <row r="475">
@@ -6259,7 +6253,7 @@
         <v>16</v>
       </c>
       <c r="C478" t="n">
-        <v>-0.260686592965726</v>
+        <v>-0.273054920986379</v>
       </c>
     </row>
     <row r="479">
@@ -6270,7 +6264,7 @@
         <v>16</v>
       </c>
       <c r="C479" t="n">
-        <v>-0.339321618663351</v>
+        <v>-0.648424637412844</v>
       </c>
     </row>
     <row r="480">
@@ -6292,7 +6286,7 @@
         <v>16</v>
       </c>
       <c r="C481" t="n">
-        <v>-0.172748221514786</v>
+        <v>-3.02167396394849</v>
       </c>
     </row>
     <row r="482">
@@ -6303,7 +6297,7 @@
         <v>16</v>
       </c>
       <c r="C482" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.239649626734936</v>
       </c>
     </row>
     <row r="483">
@@ -6314,7 +6308,7 @@
         <v>16</v>
       </c>
       <c r="C483" t="n">
-        <v>-0.478361621420852</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="484">
@@ -6325,7 +6319,7 @@
         <v>16</v>
       </c>
       <c r="C484" t="n">
-        <v>-0.269546528276831</v>
+        <v>-0.456412695924202</v>
       </c>
     </row>
     <row r="485">
@@ -6336,7 +6330,7 @@
         <v>16</v>
       </c>
       <c r="C485" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.20710945837412</v>
       </c>
     </row>
     <row r="486">
@@ -6358,7 +6352,7 @@
         <v>16</v>
       </c>
       <c r="C487" t="n">
-        <v>-0.511629510766142</v>
+        <v>-0.716000988133552</v>
       </c>
     </row>
     <row r="488">
@@ -6369,7 +6363,7 @@
         <v>16</v>
       </c>
       <c r="C488" t="n">
-        <v>-0.473824193054849</v>
+        <v>-0.393588632958575</v>
       </c>
     </row>
     <row r="489">
@@ -6380,7 +6374,7 @@
         <v>16</v>
       </c>
       <c r="C489" t="n">
-        <v>-0.494530775545858</v>
+        <v>-0.178721051987141</v>
       </c>
     </row>
     <row r="490">
@@ -6391,7 +6385,7 @@
         <v>16</v>
       </c>
       <c r="C490" t="n">
-        <v>-0.267870212892914</v>
+        <v>-0.201722149223657</v>
       </c>
     </row>
     <row r="491">
@@ -6402,7 +6396,7 @@
         <v>16</v>
       </c>
       <c r="C491" t="n">
-        <v>-0.648390425679484</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="492">
@@ -6413,7 +6407,7 @@
         <v>16</v>
       </c>
       <c r="C492" t="n">
-        <v>-0.561666953263568</v>
+        <v>-0.462473577017343</v>
       </c>
     </row>
     <row r="493">
@@ -6424,7 +6418,7 @@
         <v>16</v>
       </c>
       <c r="C493" t="n">
-        <v>-2.2583147468816</v>
+        <v>-1.02400019156383</v>
       </c>
     </row>
     <row r="494">
@@ -6435,7 +6429,7 @@
         <v>16</v>
       </c>
       <c r="C494" t="n">
-        <v>-0.253159011674866</v>
+        <v>-0.41574057809852</v>
       </c>
     </row>
     <row r="495">
@@ -6446,7 +6440,7 @@
         <v>16</v>
       </c>
       <c r="C495" t="n">
-        <v>-0.194710365940848</v>
+        <v>-0.239975449206562</v>
       </c>
     </row>
     <row r="496">
@@ -6457,7 +6451,7 @@
         <v>16</v>
       </c>
       <c r="C496" t="n">
-        <v>-0.159763313609468</v>
+        <v>-2.53182873392252</v>
       </c>
     </row>
     <row r="497">
@@ -6468,7 +6462,7 @@
         <v>16</v>
       </c>
       <c r="C497" t="n">
-        <v>0.46556738129579</v>
+        <v>-0.254204465360572</v>
       </c>
     </row>
     <row r="498">
@@ -6479,7 +6473,7 @@
         <v>16</v>
       </c>
       <c r="C498" t="n">
-        <v>-1.53677717299445</v>
+        <v>-1.34071472207069</v>
       </c>
     </row>
     <row r="499">
@@ -6490,7 +6484,7 @@
         <v>16</v>
       </c>
       <c r="C499" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.396397582976489</v>
       </c>
     </row>
     <row r="500">
@@ -6501,7 +6495,7 @@
         <v>16</v>
       </c>
       <c r="C500" t="n">
-        <v>-0.640713246762873</v>
+        <v>-0.0990993092993546</v>
       </c>
     </row>
     <row r="501">
@@ -6512,7 +6506,7 @@
         <v>16</v>
       </c>
       <c r="C501" t="n">
-        <v>-0.385303612983712</v>
+        <v>-0.695000071482606</v>
       </c>
     </row>
     <row r="502">
@@ -6523,7 +6517,7 @@
         <v>16</v>
       </c>
       <c r="C502" t="n">
-        <v>-0.211009226126549</v>
+        <v>-1.75558753570569</v>
       </c>
     </row>
     <row r="503">
@@ -6534,7 +6528,7 @@
         <v>16</v>
       </c>
       <c r="C503" t="n">
-        <v>-0.576726009357236</v>
+        <v>-0.56172935826814</v>
       </c>
     </row>
     <row r="504">
@@ -6545,7 +6539,7 @@
         <v>16</v>
       </c>
       <c r="C504" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.311793629962885</v>
       </c>
     </row>
     <row r="505">
@@ -6567,7 +6561,7 @@
         <v>16</v>
       </c>
       <c r="C506" t="n">
-        <v>-0.281298352791833</v>
+        <v>-0.22960986922322</v>
       </c>
     </row>
     <row r="507">
@@ -6578,7 +6572,7 @@
         <v>16</v>
       </c>
       <c r="C507" t="n">
-        <v>-0.816975664888202</v>
+        <v>-0.321925415368601</v>
       </c>
     </row>
     <row r="508">
@@ -6589,7 +6583,7 @@
         <v>16</v>
       </c>
       <c r="C508" t="n">
-        <v>-0.702518036378968</v>
+        <v>-0.380980161847899</v>
       </c>
     </row>
     <row r="509">
@@ -6600,7 +6594,7 @@
         <v>16</v>
       </c>
       <c r="C509" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.811171028388812</v>
       </c>
     </row>
     <row r="510">
@@ -6611,7 +6605,7 @@
         <v>16</v>
       </c>
       <c r="C510" t="n">
-        <v>-0.427440800247896</v>
+        <v>0.37233946722839</v>
       </c>
     </row>
     <row r="511">
@@ -6633,7 +6627,7 @@
         <v>16</v>
       </c>
       <c r="C512" t="n">
-        <v>-0.935903970016081</v>
+        <v>-0.285312049699002</v>
       </c>
     </row>
     <row r="513">
@@ -6644,7 +6638,7 @@
         <v>16</v>
       </c>
       <c r="C513" t="n">
-        <v>-0.855389123485251</v>
+        <v>-1.46217621340707</v>
       </c>
     </row>
     <row r="514">
@@ -6655,7 +6649,7 @@
         <v>16</v>
       </c>
       <c r="C514" t="n">
-        <v>-0.343325303374957</v>
+        <v>-0.757370511182978</v>
       </c>
     </row>
     <row r="515">
@@ -6666,7 +6660,7 @@
         <v>16</v>
       </c>
       <c r="C515" t="n">
-        <v>-0.270719113265253</v>
+        <v>-0.321802849360818</v>
       </c>
     </row>
     <row r="516">
@@ -6677,7 +6671,7 @@
         <v>16</v>
       </c>
       <c r="C516" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.35023854597183</v>
       </c>
     </row>
     <row r="517">
@@ -6688,7 +6682,7 @@
         <v>16</v>
       </c>
       <c r="C517" t="n">
-        <v>-0.312448648964511</v>
+        <v>-0.238815777782209</v>
       </c>
     </row>
     <row r="518">
@@ -6699,7 +6693,7 @@
         <v>16</v>
       </c>
       <c r="C518" t="n">
-        <v>-0.205271789362273</v>
+        <v>-0.744146412369508</v>
       </c>
     </row>
     <row r="519">
@@ -6721,7 +6715,7 @@
         <v>16</v>
       </c>
       <c r="C520" t="n">
-        <v>-0.296247262594098</v>
+        <v>-0.496305879493406</v>
       </c>
     </row>
     <row r="521">
@@ -6732,7 +6726,7 @@
         <v>16</v>
       </c>
       <c r="C521" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.564771641051412</v>
       </c>
     </row>
     <row r="522">
@@ -6743,7 +6737,7 @@
         <v>16</v>
       </c>
       <c r="C522" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.519467779380288</v>
       </c>
     </row>
     <row r="523">
@@ -6754,7 +6748,7 @@
         <v>16</v>
       </c>
       <c r="C523" t="n">
-        <v>-0.0104490865951083</v>
+        <v>-2.27776252868612</v>
       </c>
     </row>
     <row r="524">
@@ -6765,7 +6759,7 @@
         <v>16</v>
       </c>
       <c r="C524" t="n">
-        <v>-0.913751857899011</v>
+        <v>-0.20245744117838</v>
       </c>
     </row>
     <row r="525">
@@ -6776,7 +6770,7 @@
         <v>16</v>
       </c>
       <c r="C525" t="n">
-        <v>-0.19427970554202</v>
+        <v>-0.678077765838877</v>
       </c>
     </row>
     <row r="526">
@@ -6787,7 +6781,7 @@
         <v>16</v>
       </c>
       <c r="C526" t="n">
-        <v>-1.20107711534786</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="527">
@@ -6809,7 +6803,7 @@
         <v>16</v>
       </c>
       <c r="C528" t="n">
-        <v>-0.424389200496932</v>
+        <v>-0.721457014541167</v>
       </c>
     </row>
     <row r="529">
@@ -6820,7 +6814,7 @@
         <v>16</v>
       </c>
       <c r="C529" t="n">
-        <v>-0.671568532280386</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="530">
@@ -6831,7 +6825,7 @@
         <v>16</v>
       </c>
       <c r="C530" t="n">
-        <v>-0.520353542648087</v>
+        <v>-0.553766875849569</v>
       </c>
     </row>
     <row r="531">
@@ -6842,7 +6836,7 @@
         <v>16</v>
       </c>
       <c r="C531" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.140395974250554</v>
       </c>
     </row>
     <row r="532">
@@ -6853,7 +6847,7 @@
         <v>16</v>
       </c>
       <c r="C532" t="n">
-        <v>-0.362411954934093</v>
+        <v>-0.203839663617198</v>
       </c>
     </row>
     <row r="533">
@@ -6864,7 +6858,7 @@
         <v>16</v>
       </c>
       <c r="C533" t="n">
-        <v>-0.952671262308957</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="534">
@@ -6875,7 +6869,7 @@
         <v>16</v>
       </c>
       <c r="C534" t="n">
-        <v>-0.44114608855081</v>
+        <v>-0.350416567086124</v>
       </c>
     </row>
     <row r="535">
@@ -6886,7 +6880,7 @@
         <v>16</v>
       </c>
       <c r="C535" t="n">
-        <v>-0.189225910704526</v>
+        <v>-0.200039956460646</v>
       </c>
     </row>
     <row r="536">
@@ -6897,7 +6891,7 @@
         <v>16</v>
       </c>
       <c r="C536" t="n">
-        <v>-0.832822312243677</v>
+        <v>-1.51129084907733</v>
       </c>
     </row>
     <row r="537">
@@ -6908,7 +6902,7 @@
         <v>16</v>
       </c>
       <c r="C537" t="n">
-        <v>0.83173403834944</v>
+        <v>0.933605513824971</v>
       </c>
     </row>
     <row r="538">
@@ -6930,7 +6924,7 @@
         <v>16</v>
       </c>
       <c r="C539" t="n">
-        <v>-0.160085950095346</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="540">
@@ -6941,7 +6935,7 @@
         <v>16</v>
       </c>
       <c r="C540" t="n">
-        <v>-0.498130376426553</v>
+        <v>-0.907740778821455</v>
       </c>
     </row>
     <row r="541">
@@ -6952,7 +6946,7 @@
         <v>16</v>
       </c>
       <c r="C541" t="n">
-        <v>-0.165376891579403</v>
+        <v>-1.77305330162211</v>
       </c>
     </row>
     <row r="542">
@@ -6996,7 +6990,7 @@
         <v>16</v>
       </c>
       <c r="C545" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.617674789665334</v>
       </c>
     </row>
     <row r="546">
@@ -7007,7 +7001,7 @@
         <v>16</v>
       </c>
       <c r="C546" t="n">
-        <v>-0.0775534748464615</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="547">
@@ -7018,7 +7012,7 @@
         <v>16</v>
       </c>
       <c r="C547" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.289280441497646</v>
       </c>
     </row>
     <row r="548">
@@ -7029,7 +7023,7 @@
         <v>16</v>
       </c>
       <c r="C548" t="n">
-        <v>-1.26305562454455</v>
+        <v>-0.522353507724022</v>
       </c>
     </row>
     <row r="549">
@@ -7040,7 +7034,7 @@
         <v>16</v>
       </c>
       <c r="C549" t="n">
-        <v>0.118877105675406</v>
+        <v>-1.66368815794835</v>
       </c>
     </row>
     <row r="550">
@@ -7051,7 +7045,7 @@
         <v>16</v>
       </c>
       <c r="C550" t="n">
-        <v>-0.268419462599295</v>
+        <v>-0.444192089570542</v>
       </c>
     </row>
     <row r="551">
@@ -7062,7 +7056,7 @@
         <v>16</v>
       </c>
       <c r="C551" t="n">
-        <v>-0.941061494918313</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="552">
@@ -7073,7 +7067,7 @@
         <v>16</v>
       </c>
       <c r="C552" t="n">
-        <v>-0.719964719950419</v>
+        <v>-1.06418272057063</v>
       </c>
     </row>
     <row r="553">
@@ -7084,7 +7078,7 @@
         <v>16</v>
       </c>
       <c r="C553" t="n">
-        <v>-0.168639420363392</v>
+        <v>-0.231093310633795</v>
       </c>
     </row>
     <row r="554">
@@ -7106,7 +7100,7 @@
         <v>16</v>
       </c>
       <c r="C555" t="n">
-        <v>-0.520536854011522</v>
+        <v>-0.263421898048614</v>
       </c>
     </row>
     <row r="556">
@@ -7117,7 +7111,7 @@
         <v>16</v>
       </c>
       <c r="C556" t="n">
-        <v>-2.06434802178572</v>
+        <v>0.411336920020335</v>
       </c>
     </row>
     <row r="557">
@@ -7128,7 +7122,7 @@
         <v>16</v>
       </c>
       <c r="C557" t="n">
-        <v>-1.27732620486834</v>
+        <v>-0.553349656266956</v>
       </c>
     </row>
     <row r="558">
@@ -7139,7 +7133,7 @@
         <v>16</v>
       </c>
       <c r="C558" t="n">
-        <v>-0.202676511850308</v>
+        <v>-0.590683958458998</v>
       </c>
     </row>
     <row r="559">
@@ -7172,7 +7166,7 @@
         <v>16</v>
       </c>
       <c r="C561" t="n">
-        <v>-0.287127384776334</v>
+        <v>-0.490049218336978</v>
       </c>
     </row>
     <row r="562">
@@ -7183,7 +7177,7 @@
         <v>16</v>
       </c>
       <c r="C562" t="n">
-        <v>-0.345000483700004</v>
+        <v>-0.712004802235565</v>
       </c>
     </row>
     <row r="563">
@@ -7205,7 +7199,7 @@
         <v>16</v>
       </c>
       <c r="C564" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.62219479799833</v>
       </c>
     </row>
     <row r="565">
@@ -7216,7 +7210,7 @@
         <v>16</v>
       </c>
       <c r="C565" t="n">
-        <v>-0.103814153792985</v>
+        <v>-0.483607147501483</v>
       </c>
     </row>
     <row r="566">
@@ -7227,7 +7221,7 @@
         <v>16</v>
       </c>
       <c r="C566" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.170493170743847</v>
       </c>
     </row>
     <row r="567">
@@ -7238,7 +7232,7 @@
         <v>16</v>
       </c>
       <c r="C567" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.230978757358</v>
       </c>
     </row>
     <row r="568">
@@ -7249,7 +7243,7 @@
         <v>16</v>
       </c>
       <c r="C568" t="n">
-        <v>-0.41879715248131</v>
+        <v>-1.17426027215419</v>
       </c>
     </row>
     <row r="569">
@@ -7260,7 +7254,7 @@
         <v>16</v>
       </c>
       <c r="C569" t="n">
-        <v>-0.310673027325833</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="570">
@@ -7282,7 +7276,7 @@
         <v>16</v>
       </c>
       <c r="C571" t="n">
-        <v>-0.245180313281689</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="572">
@@ -7293,7 +7287,7 @@
         <v>16</v>
       </c>
       <c r="C572" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.44596595929019</v>
       </c>
     </row>
     <row r="573">
@@ -7304,7 +7298,7 @@
         <v>16</v>
       </c>
       <c r="C573" t="n">
-        <v>-0.381969857493535</v>
+        <v>-0.487508573770938</v>
       </c>
     </row>
     <row r="574">
@@ -7315,7 +7309,7 @@
         <v>16</v>
       </c>
       <c r="C574" t="n">
-        <v>-0.162427621312363</v>
+        <v>-2.24081153562444</v>
       </c>
     </row>
     <row r="575">
@@ -7326,7 +7320,7 @@
         <v>16</v>
       </c>
       <c r="C575" t="n">
-        <v>0.763776439806119</v>
+        <v>0.727528430880353</v>
       </c>
     </row>
     <row r="576">
@@ -7337,7 +7331,7 @@
         <v>16</v>
       </c>
       <c r="C576" t="n">
-        <v>-0.0906174862489684</v>
+        <v>-2.95628456951301</v>
       </c>
     </row>
     <row r="577">
@@ -7348,7 +7342,7 @@
         <v>16</v>
       </c>
       <c r="C577" t="n">
-        <v>-0.213557938743786</v>
+        <v>-0.44885864040995</v>
       </c>
     </row>
     <row r="578">
@@ -7359,7 +7353,7 @@
         <v>16</v>
       </c>
       <c r="C578" t="n">
-        <v>-0.733351772995769</v>
+        <v>-1.09199296865023</v>
       </c>
     </row>
     <row r="579">
@@ -7370,7 +7364,7 @@
         <v>16</v>
       </c>
       <c r="C579" t="n">
-        <v>-0.73987114231494</v>
+        <v>-0.892305937638111</v>
       </c>
     </row>
     <row r="580">
@@ -7381,7 +7375,7 @@
         <v>16</v>
       </c>
       <c r="C580" t="n">
-        <v>-0.437585785964343</v>
+        <v>-0.566445342470458</v>
       </c>
     </row>
     <row r="581">
@@ -7392,7 +7386,7 @@
         <v>16</v>
       </c>
       <c r="C581" t="n">
-        <v>-0.174608247189997</v>
+        <v>0.20673454675815</v>
       </c>
     </row>
     <row r="582">
@@ -7403,7 +7397,7 @@
         <v>16</v>
       </c>
       <c r="C582" t="n">
-        <v>-0.779152112914504</v>
+        <v>-0.61001788270461</v>
       </c>
     </row>
     <row r="583">
@@ -7436,7 +7430,7 @@
         <v>16</v>
       </c>
       <c r="C585" t="n">
-        <v>-0.700241844537524</v>
+        <v>-0.00282963851786922</v>
       </c>
     </row>
     <row r="586">
@@ -7447,7 +7441,7 @@
         <v>16</v>
       </c>
       <c r="C586" t="n">
-        <v>-0.509575665680173</v>
+        <v>-0.0521363170368823</v>
       </c>
     </row>
     <row r="587">
@@ -7458,7 +7452,7 @@
         <v>16</v>
       </c>
       <c r="C587" t="n">
-        <v>-0.200526105010972</v>
+        <v>-0.732342112727795</v>
       </c>
     </row>
     <row r="588">
@@ -7469,7 +7463,7 @@
         <v>16</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.881938613292258</v>
+        <v>-0.513846213123179</v>
       </c>
     </row>
     <row r="589">
@@ -7480,7 +7474,7 @@
         <v>16</v>
       </c>
       <c r="C589" t="n">
-        <v>0.0463531308215335</v>
+        <v>0.0103561838680034</v>
       </c>
     </row>
     <row r="590">
@@ -7491,7 +7485,7 @@
         <v>16</v>
       </c>
       <c r="C590" t="n">
-        <v>-0.1815598777465</v>
+        <v>-0.17426303592334</v>
       </c>
     </row>
     <row r="591">
@@ -7502,7 +7496,7 @@
         <v>16</v>
       </c>
       <c r="C591" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.434966830586419</v>
       </c>
     </row>
     <row r="592">
@@ -7513,7 +7507,7 @@
         <v>16</v>
       </c>
       <c r="C592" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.59092537613056</v>
       </c>
     </row>
     <row r="593">
@@ -7524,7 +7518,7 @@
         <v>16</v>
       </c>
       <c r="C593" t="n">
-        <v>-1.45980846991351</v>
+        <v>-0.852217227677901</v>
       </c>
     </row>
     <row r="594">
@@ -7535,7 +7529,7 @@
         <v>16</v>
       </c>
       <c r="C594" t="n">
-        <v>-0.943768955353068</v>
+        <v>-0.696731045745293</v>
       </c>
     </row>
     <row r="595">
@@ -7546,7 +7540,7 @@
         <v>16</v>
       </c>
       <c r="C595" t="n">
-        <v>-0.485578312489032</v>
+        <v>-2.95468330667845</v>
       </c>
     </row>
     <row r="596">
@@ -7557,7 +7551,7 @@
         <v>16</v>
       </c>
       <c r="C596" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.634647433832513</v>
       </c>
     </row>
     <row r="597">
@@ -7568,7 +7562,7 @@
         <v>16</v>
       </c>
       <c r="C597" t="n">
-        <v>-3.09119789969829</v>
+        <v>-2.05079071267842</v>
       </c>
     </row>
     <row r="598">
@@ -7579,7 +7573,7 @@
         <v>16</v>
       </c>
       <c r="C598" t="n">
-        <v>-1.54797234242454</v>
+        <v>-1.93665978796272</v>
       </c>
     </row>
     <row r="599">
@@ -7590,7 +7584,7 @@
         <v>16</v>
       </c>
       <c r="C599" t="n">
-        <v>-1.05073104901471</v>
+        <v>-0.35981317406519</v>
       </c>
     </row>
     <row r="600">
@@ -7601,7 +7595,7 @@
         <v>16</v>
       </c>
       <c r="C600" t="n">
-        <v>-0.102265117169609</v>
+        <v>-0.456978092985455</v>
       </c>
     </row>
     <row r="601">
@@ -7612,7 +7606,7 @@
         <v>16</v>
       </c>
       <c r="C601" t="n">
-        <v>-0.703001729405975</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="602">
@@ -7634,7 +7628,7 @@
         <v>16</v>
       </c>
       <c r="C603" t="n">
-        <v>-0.159763313609467</v>
+        <v>-3.72680588936845</v>
       </c>
     </row>
     <row r="604">
@@ -7645,7 +7639,7 @@
         <v>16</v>
       </c>
       <c r="C604" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.806294259156286</v>
       </c>
     </row>
     <row r="605">
@@ -7656,7 +7650,7 @@
         <v>16</v>
       </c>
       <c r="C605" t="n">
-        <v>-0.500546886777174</v>
+        <v>-0.732992987355618</v>
       </c>
     </row>
     <row r="606">
@@ -7667,7 +7661,7 @@
         <v>16</v>
       </c>
       <c r="C606" t="n">
-        <v>-0.162100537827608</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="607">
@@ -7689,7 +7683,7 @@
         <v>16</v>
       </c>
       <c r="C608" t="n">
-        <v>-1.88795913703744</v>
+        <v>-5.56853290310129</v>
       </c>
     </row>
     <row r="609">
@@ -7711,7 +7705,7 @@
         <v>16</v>
       </c>
       <c r="C610" t="n">
-        <v>-0.470506171957286</v>
+        <v>-0.479614272129742</v>
       </c>
     </row>
     <row r="611">
@@ -7722,7 +7716,7 @@
         <v>16</v>
       </c>
       <c r="C611" t="n">
-        <v>-0.949182463632635</v>
+        <v>-0.909165866913101</v>
       </c>
     </row>
     <row r="612">
@@ -7733,7 +7727,7 @@
         <v>16</v>
       </c>
       <c r="C612" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.171623899047685</v>
       </c>
     </row>
     <row r="613">
@@ -7744,7 +7738,7 @@
         <v>16</v>
       </c>
       <c r="C613" t="n">
-        <v>-0.346618321599978</v>
+        <v>-0.930099889698278</v>
       </c>
     </row>
     <row r="614">
@@ -7755,7 +7749,7 @@
         <v>16</v>
       </c>
       <c r="C614" t="n">
-        <v>-0.398307944514358</v>
+        <v>-0.166275062017895</v>
       </c>
     </row>
     <row r="615">
@@ -7766,7 +7760,7 @@
         <v>16</v>
       </c>
       <c r="C615" t="n">
-        <v>-0.28198654800334</v>
+        <v>-0.52594352647867</v>
       </c>
     </row>
     <row r="616">
@@ -7788,7 +7782,7 @@
         <v>16</v>
       </c>
       <c r="C617" t="n">
-        <v>-1.48280969460082</v>
+        <v>-0.698222030626366</v>
       </c>
     </row>
     <row r="618">
@@ -7799,7 +7793,7 @@
         <v>16</v>
       </c>
       <c r="C618" t="n">
-        <v>-0.432624658724488</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="619">
@@ -7821,7 +7815,7 @@
         <v>16</v>
       </c>
       <c r="C620" t="n">
-        <v>-0.224076671558186</v>
+        <v>-1.21965218621211</v>
       </c>
     </row>
     <row r="621">
@@ -7832,7 +7826,7 @@
         <v>16</v>
       </c>
       <c r="C621" t="n">
-        <v>-0.15728946839061</v>
+        <v>-0.2973418208768</v>
       </c>
     </row>
     <row r="622">
@@ -7843,7 +7837,7 @@
         <v>16</v>
       </c>
       <c r="C622" t="n">
-        <v>-0.248829956637284</v>
+        <v>-0.29759307307898</v>
       </c>
     </row>
     <row r="623">
@@ -7854,7 +7848,7 @@
         <v>16</v>
       </c>
       <c r="C623" t="n">
-        <v>-0.491761902726241</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="624">
@@ -7865,7 +7859,7 @@
         <v>16</v>
       </c>
       <c r="C624" t="n">
-        <v>-0.960235927713958</v>
+        <v>-0.965179592925778</v>
       </c>
     </row>
     <row r="625">
@@ -7876,7 +7870,7 @@
         <v>16</v>
       </c>
       <c r="C625" t="n">
-        <v>-0.676872068435743</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="626">
@@ -7887,7 +7881,7 @@
         <v>16</v>
       </c>
       <c r="C626" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.827444546578346</v>
       </c>
     </row>
     <row r="627">
@@ -7898,7 +7892,7 @@
         <v>16</v>
       </c>
       <c r="C627" t="n">
-        <v>-0.288899671719971</v>
+        <v>-0.934688075716416</v>
       </c>
     </row>
     <row r="628">
@@ -7909,7 +7903,7 @@
         <v>16</v>
       </c>
       <c r="C628" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.8154824339376</v>
       </c>
     </row>
     <row r="629">
@@ -7920,7 +7914,7 @@
         <v>16</v>
       </c>
       <c r="C629" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.313596210742461</v>
       </c>
     </row>
     <row r="630">
@@ -7931,7 +7925,7 @@
         <v>16</v>
       </c>
       <c r="C630" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.936964388307533</v>
       </c>
     </row>
     <row r="631">
@@ -7942,7 +7936,7 @@
         <v>16</v>
       </c>
       <c r="C631" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.443315417566917</v>
       </c>
     </row>
     <row r="632">
@@ -7953,7 +7947,7 @@
         <v>16</v>
       </c>
       <c r="C632" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.790851015184857</v>
       </c>
     </row>
     <row r="633">
@@ -7964,7 +7958,7 @@
         <v>16</v>
       </c>
       <c r="C633" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.227459602493326</v>
       </c>
     </row>
     <row r="634">
@@ -7997,7 +7991,7 @@
         <v>16</v>
       </c>
       <c r="C636" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.17099514291318</v>
       </c>
     </row>
     <row r="637">
@@ -8008,7 +8002,7 @@
         <v>16</v>
       </c>
       <c r="C637" t="n">
-        <v>-0.149763943763057</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="638">
@@ -8019,7 +8013,7 @@
         <v>16</v>
       </c>
       <c r="C638" t="n">
-        <v>-0.235934607187208</v>
+        <v>-0.0179539560526449</v>
       </c>
     </row>
     <row r="639">
@@ -8030,7 +8024,7 @@
         <v>16</v>
       </c>
       <c r="C639" t="n">
-        <v>-0.408135880464088</v>
+        <v>-0.780441716382529</v>
       </c>
     </row>
     <row r="640">
@@ -8041,7 +8035,7 @@
         <v>16</v>
       </c>
       <c r="C640" t="n">
-        <v>-0.944665729419324</v>
+        <v>-0.784183675838019</v>
       </c>
     </row>
     <row r="641">
@@ -8085,7 +8079,7 @@
         <v>16</v>
       </c>
       <c r="C644" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.277943088685811</v>
       </c>
     </row>
     <row r="645">
@@ -8096,7 +8090,7 @@
         <v>16</v>
       </c>
       <c r="C645" t="n">
-        <v>-1.6307623182562</v>
+        <v>-0.871684378419626</v>
       </c>
     </row>
     <row r="646">
@@ -8118,7 +8112,7 @@
         <v>16</v>
       </c>
       <c r="C647" t="n">
-        <v>-0.317070378002368</v>
+        <v>-0.193326854110784</v>
       </c>
     </row>
     <row r="648">
@@ -8129,7 +8123,7 @@
         <v>16</v>
       </c>
       <c r="C648" t="n">
-        <v>-1.38616851014416</v>
+        <v>-1.58260273912839</v>
       </c>
     </row>
     <row r="649">
@@ -8140,7 +8134,7 @@
         <v>16</v>
       </c>
       <c r="C649" t="n">
-        <v>-0.595726641348719</v>
+        <v>-0.352385053727288</v>
       </c>
     </row>
     <row r="650">
@@ -8151,7 +8145,7 @@
         <v>16</v>
       </c>
       <c r="C650" t="n">
-        <v>-2.18795938873394</v>
+        <v>-0.234545277309298</v>
       </c>
     </row>
     <row r="651">
@@ -8162,7 +8156,7 @@
         <v>16</v>
       </c>
       <c r="C651" t="n">
-        <v>0.0252879833153714</v>
+        <v>0.625243752466115</v>
       </c>
     </row>
     <row r="652">
@@ -8173,7 +8167,7 @@
         <v>16</v>
       </c>
       <c r="C652" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.295079714318981</v>
       </c>
     </row>
     <row r="653">
@@ -8184,7 +8178,7 @@
         <v>16</v>
       </c>
       <c r="C653" t="n">
-        <v>-0.257669041421938</v>
+        <v>-0.208475022431416</v>
       </c>
     </row>
     <row r="654">
@@ -8195,7 +8189,7 @@
         <v>16</v>
       </c>
       <c r="C654" t="n">
-        <v>-0.418956725105208</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="655">
@@ -8206,7 +8200,7 @@
         <v>16</v>
       </c>
       <c r="C655" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.330006669140312</v>
       </c>
     </row>
     <row r="656">
@@ -8239,7 +8233,7 @@
         <v>16</v>
       </c>
       <c r="C658" t="n">
-        <v>0.396143552600394</v>
+        <v>-0.926974982945833</v>
       </c>
     </row>
     <row r="659">
@@ -8261,7 +8255,7 @@
         <v>16</v>
       </c>
       <c r="C660" t="n">
-        <v>-1.05114165013308</v>
+        <v>-0.0598466661059494</v>
       </c>
     </row>
     <row r="661">
@@ -8272,7 +8266,7 @@
         <v>16</v>
       </c>
       <c r="C661" t="n">
-        <v>-0.41476453101817</v>
+        <v>-3.81813805051413</v>
       </c>
     </row>
     <row r="662">
@@ -8283,7 +8277,7 @@
         <v>16</v>
       </c>
       <c r="C662" t="n">
-        <v>0.448860339827582</v>
+        <v>0.40650386094361</v>
       </c>
     </row>
     <row r="663">
@@ -8294,7 +8288,7 @@
         <v>16</v>
       </c>
       <c r="C663" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.43846121978653</v>
       </c>
     </row>
     <row r="664">
@@ -8305,7 +8299,7 @@
         <v>16</v>
       </c>
       <c r="C664" t="n">
-        <v>-0.351896567317944</v>
+        <v>-0.400836655679225</v>
       </c>
     </row>
     <row r="665">
@@ -8316,7 +8310,7 @@
         <v>16</v>
       </c>
       <c r="C665" t="n">
-        <v>-0.486205202269752</v>
+        <v>-0.539409130637039</v>
       </c>
     </row>
     <row r="666">
@@ -8327,7 +8321,7 @@
         <v>16</v>
       </c>
       <c r="C666" t="n">
-        <v>-0.282896864653998</v>
+        <v>-1.38287599011714</v>
       </c>
     </row>
     <row r="667">
@@ -8349,7 +8343,7 @@
         <v>16</v>
       </c>
       <c r="C668" t="n">
-        <v>-1.45050720827632</v>
+        <v>-0.409074860904797</v>
       </c>
     </row>
     <row r="669">
@@ -8371,7 +8365,7 @@
         <v>16</v>
       </c>
       <c r="C670" t="n">
-        <v>-0.226998739735568</v>
+        <v>-0.194666283325872</v>
       </c>
     </row>
     <row r="671">
@@ -8382,7 +8376,7 @@
         <v>16</v>
       </c>
       <c r="C671" t="n">
-        <v>-0.489969116519727</v>
+        <v>-0.741462015335059</v>
       </c>
     </row>
     <row r="672">
@@ -8393,7 +8387,7 @@
         <v>16</v>
       </c>
       <c r="C672" t="n">
-        <v>-0.682337242633421</v>
+        <v>-0.943341230445168</v>
       </c>
     </row>
     <row r="673">
@@ -8404,7 +8398,7 @@
         <v>16</v>
       </c>
       <c r="C673" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.415101734320263</v>
       </c>
     </row>
     <row r="674">
@@ -8415,7 +8409,7 @@
         <v>16</v>
       </c>
       <c r="C674" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.620234679657798</v>
       </c>
     </row>
     <row r="675">
@@ -8426,7 +8420,7 @@
         <v>16</v>
       </c>
       <c r="C675" t="n">
-        <v>-0.610600574092445</v>
+        <v>-4.47835162170942</v>
       </c>
     </row>
     <row r="676">
@@ -8448,7 +8442,7 @@
         <v>16</v>
       </c>
       <c r="C677" t="n">
-        <v>-0.125548551476652</v>
+        <v>-0.175592432908122</v>
       </c>
     </row>
     <row r="678">
@@ -8459,7 +8453,7 @@
         <v>16</v>
       </c>
       <c r="C678" t="n">
-        <v>-3.56021458420081</v>
+        <v>-0.829027006015017</v>
       </c>
     </row>
     <row r="679">
@@ -8470,7 +8464,7 @@
         <v>16</v>
       </c>
       <c r="C679" t="n">
-        <v>-0.400547663508577</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="680">
@@ -8503,7 +8497,7 @@
         <v>16</v>
       </c>
       <c r="C682" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.161888846177644</v>
       </c>
     </row>
     <row r="683">
@@ -8514,7 +8508,7 @@
         <v>16</v>
       </c>
       <c r="C683" t="n">
-        <v>-0.0750435649131214</v>
+        <v>-1.0841804830016</v>
       </c>
     </row>
     <row r="684">
@@ -8525,7 +8519,7 @@
         <v>16</v>
       </c>
       <c r="C684" t="n">
-        <v>-1.57107878526328</v>
+        <v>-2.28772984469632</v>
       </c>
     </row>
     <row r="685">
@@ -8536,7 +8530,7 @@
         <v>16</v>
       </c>
       <c r="C685" t="n">
-        <v>-0.400035362575368</v>
+        <v>-0.992993617492876</v>
       </c>
     </row>
     <row r="686">
@@ -8547,7 +8541,7 @@
         <v>16</v>
       </c>
       <c r="C686" t="n">
-        <v>-0.18425446057231</v>
+        <v>-0.185249484924445</v>
       </c>
     </row>
     <row r="687">
@@ -8569,7 +8563,7 @@
         <v>16</v>
       </c>
       <c r="C688" t="n">
-        <v>0.177960847106665</v>
+        <v>-0.608223930783883</v>
       </c>
     </row>
     <row r="689">
@@ -8580,7 +8574,7 @@
         <v>16</v>
       </c>
       <c r="C689" t="n">
-        <v>-0.407463436176356</v>
+        <v>-0.497709963208296</v>
       </c>
     </row>
     <row r="690">
@@ -8591,7 +8585,7 @@
         <v>16</v>
       </c>
       <c r="C690" t="n">
-        <v>-0.17141114359035</v>
+        <v>0.0366141986998906</v>
       </c>
     </row>
     <row r="691">
@@ -8602,7 +8596,7 @@
         <v>16</v>
       </c>
       <c r="C691" t="n">
-        <v>-0.0623626500937886</v>
+        <v>-0.156538352811361</v>
       </c>
     </row>
     <row r="692">
@@ -8613,7 +8607,7 @@
         <v>16</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.186396798859518</v>
       </c>
     </row>
     <row r="693">
@@ -8624,7 +8618,7 @@
         <v>16</v>
       </c>
       <c r="C693" t="n">
-        <v>-0.47249366217138</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="694">
@@ -8635,7 +8629,7 @@
         <v>16</v>
       </c>
       <c r="C694" t="n">
-        <v>-0.65254789244328</v>
+        <v>-0.732490530635272</v>
       </c>
     </row>
     <row r="695">
@@ -8646,7 +8640,7 @@
         <v>16</v>
       </c>
       <c r="C695" t="n">
-        <v>0.20616033775765</v>
+        <v>-0.440088508927678</v>
       </c>
     </row>
     <row r="696">
@@ -8657,7 +8651,7 @@
         <v>16</v>
       </c>
       <c r="C696" t="n">
-        <v>0.779732052457504</v>
+        <v>0.756772709684002</v>
       </c>
     </row>
     <row r="697">
@@ -8668,7 +8662,7 @@
         <v>16</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.410468642321424</v>
       </c>
     </row>
     <row r="698">
@@ -8690,7 +8684,7 @@
         <v>16</v>
       </c>
       <c r="C699" t="n">
-        <v>-0.306361877928451</v>
+        <v>-0.348638683104435</v>
       </c>
     </row>
     <row r="700">
@@ -8701,7 +8695,7 @@
         <v>16</v>
       </c>
       <c r="C700" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.03272791090889</v>
       </c>
     </row>
     <row r="701">
@@ -8723,7 +8717,7 @@
         <v>16</v>
       </c>
       <c r="C702" t="n">
-        <v>-0.17921146452033</v>
+        <v>-0.40713075859266</v>
       </c>
     </row>
     <row r="703">
@@ -8756,7 +8750,7 @@
         <v>16</v>
       </c>
       <c r="C705" t="n">
-        <v>-0.303643867109082</v>
+        <v>-0.243053033342064</v>
       </c>
     </row>
     <row r="706">
@@ -8767,7 +8761,7 @@
         <v>16</v>
       </c>
       <c r="C706" t="n">
-        <v>-1.35595525395474</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="707">
@@ -8778,7 +8772,7 @@
         <v>16</v>
       </c>
       <c r="C707" t="n">
-        <v>-0.213908913191568</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="708">
@@ -8789,7 +8783,7 @@
         <v>16</v>
       </c>
       <c r="C708" t="n">
-        <v>-0.395764246946315</v>
+        <v>-0.557588799000974</v>
       </c>
     </row>
     <row r="709">
@@ -8800,7 +8794,7 @@
         <v>16</v>
       </c>
       <c r="C709" t="n">
-        <v>-0.37973069084676</v>
+        <v>-0.185908456234127</v>
       </c>
     </row>
     <row r="710">
@@ -8811,7 +8805,7 @@
         <v>16</v>
       </c>
       <c r="C710" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.53366162008528</v>
       </c>
     </row>
     <row r="711">
@@ -8822,7 +8816,7 @@
         <v>16</v>
       </c>
       <c r="C711" t="n">
-        <v>-0.748432070962752</v>
+        <v>-0.162269584094268</v>
       </c>
     </row>
     <row r="712">
@@ -8844,7 +8838,7 @@
         <v>16</v>
       </c>
       <c r="C713" t="n">
-        <v>-0.466583405970544</v>
+        <v>-0.290654952162225</v>
       </c>
     </row>
     <row r="714">
@@ -8855,7 +8849,7 @@
         <v>16</v>
       </c>
       <c r="C714" t="n">
-        <v>-0.159763313609467</v>
+        <v>-2.2746155577322</v>
       </c>
     </row>
     <row r="715">
@@ -8866,7 +8860,7 @@
         <v>16</v>
       </c>
       <c r="C715" t="n">
-        <v>-0.477309391691569</v>
+        <v>-0.920581022093878</v>
       </c>
     </row>
     <row r="716">
@@ -8877,7 +8871,7 @@
         <v>16</v>
       </c>
       <c r="C716" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.35665010510964</v>
       </c>
     </row>
     <row r="717">
@@ -8888,7 +8882,7 @@
         <v>16</v>
       </c>
       <c r="C717" t="n">
-        <v>-0.589960599441548</v>
+        <v>-0.10692289577792</v>
       </c>
     </row>
     <row r="718">
@@ -8899,7 +8893,7 @@
         <v>16</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.126835334326535</v>
+        <v>-0.089508828087685</v>
       </c>
     </row>
     <row r="719">
@@ -8910,7 +8904,7 @@
         <v>16</v>
       </c>
       <c r="C719" t="n">
-        <v>-0.0740663807983559</v>
+        <v>-0.506187995505264</v>
       </c>
     </row>
     <row r="720">
@@ -8921,7 +8915,7 @@
         <v>16</v>
       </c>
       <c r="C720" t="n">
-        <v>-1.15838965069809</v>
+        <v>-1.54154604187849</v>
       </c>
     </row>
     <row r="721">
@@ -8932,7 +8926,7 @@
         <v>16</v>
       </c>
       <c r="C721" t="n">
-        <v>-0.46278554704859</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="722">
@@ -8943,7 +8937,7 @@
         <v>16</v>
       </c>
       <c r="C722" t="n">
-        <v>-0.803680429412141</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="723">
@@ -8954,7 +8948,7 @@
         <v>16</v>
       </c>
       <c r="C723" t="n">
-        <v>-0.548350878356254</v>
+        <v>-0.202470329751018</v>
       </c>
     </row>
     <row r="724">
@@ -8965,7 +8959,7 @@
         <v>16</v>
       </c>
       <c r="C724" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.276279843394947</v>
       </c>
     </row>
     <row r="725">
@@ -8976,7 +8970,7 @@
         <v>16</v>
       </c>
       <c r="C725" t="n">
-        <v>-1.00982649094615</v>
+        <v>-0.982771403362851</v>
       </c>
     </row>
     <row r="726">
@@ -9009,7 +9003,7 @@
         <v>16</v>
       </c>
       <c r="C728" t="n">
-        <v>-0.816363077019819</v>
+        <v>-0.334792475782886</v>
       </c>
     </row>
     <row r="729">
@@ -9020,7 +9014,7 @@
         <v>16</v>
       </c>
       <c r="C729" t="n">
-        <v>0.221791277344313</v>
+        <v>0.123716251506971</v>
       </c>
     </row>
     <row r="730">
@@ -9031,7 +9025,7 @@
         <v>16</v>
       </c>
       <c r="C730" t="n">
-        <v>-0.184230226243563</v>
+        <v>-0.747466582936535</v>
       </c>
     </row>
     <row r="731">
@@ -9042,7 +9036,7 @@
         <v>16</v>
       </c>
       <c r="C731" t="n">
-        <v>-0.199609701528821</v>
+        <v>-3.91958180335744</v>
       </c>
     </row>
     <row r="732">
@@ -9053,7 +9047,7 @@
         <v>16</v>
       </c>
       <c r="C732" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.02527640943852</v>
       </c>
     </row>
     <row r="733">
@@ -9064,7 +9058,7 @@
         <v>16</v>
       </c>
       <c r="C733" t="n">
-        <v>-0.25219567337384</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="734">
@@ -9075,7 +9069,7 @@
         <v>16</v>
       </c>
       <c r="C734" t="n">
-        <v>-0.112727573510035</v>
+        <v>-0.0955834872928176</v>
       </c>
     </row>
     <row r="735">
@@ -9097,7 +9091,7 @@
         <v>16</v>
       </c>
       <c r="C736" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.28173253138921</v>
       </c>
     </row>
     <row r="737">
@@ -9108,7 +9102,7 @@
         <v>16</v>
       </c>
       <c r="C737" t="n">
-        <v>-0.47133239279152</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="738">
@@ -9141,7 +9135,7 @@
         <v>16</v>
       </c>
       <c r="C740" t="n">
-        <v>-0.232638234127016</v>
+        <v>-0.392036892058435</v>
       </c>
     </row>
     <row r="741">
@@ -9152,7 +9146,7 @@
         <v>16</v>
       </c>
       <c r="C741" t="n">
-        <v>-0.227781749147077</v>
+        <v>-0.315921449319887</v>
       </c>
     </row>
     <row r="742">
@@ -9174,7 +9168,7 @@
         <v>16</v>
       </c>
       <c r="C743" t="n">
-        <v>-0.320893969411391</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="744">
@@ -9196,7 +9190,7 @@
         <v>16</v>
       </c>
       <c r="C745" t="n">
-        <v>-0.588422791202037</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="746">
@@ -9207,7 +9201,7 @@
         <v>16</v>
       </c>
       <c r="C746" t="n">
-        <v>-0.531942321135351</v>
+        <v>-1.00722183196819</v>
       </c>
     </row>
     <row r="747">
@@ -9240,7 +9234,7 @@
         <v>16</v>
       </c>
       <c r="C749" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.376253468199568</v>
       </c>
     </row>
     <row r="750">
@@ -9251,7 +9245,7 @@
         <v>16</v>
       </c>
       <c r="C750" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.367680687149467</v>
       </c>
     </row>
     <row r="751">
@@ -9262,7 +9256,7 @@
         <v>16</v>
       </c>
       <c r="C751" t="n">
-        <v>-0.19705607911055</v>
+        <v>0.156084099425129</v>
       </c>
     </row>
     <row r="752">
@@ -9273,7 +9267,7 @@
         <v>16</v>
       </c>
       <c r="C752" t="n">
-        <v>0.236217516012649</v>
+        <v>-0.231182903843617</v>
       </c>
     </row>
     <row r="753">
@@ -9284,7 +9278,7 @@
         <v>16</v>
       </c>
       <c r="C753" t="n">
-        <v>-0.111897486075246</v>
+        <v>-0.581656531305764</v>
       </c>
     </row>
     <row r="754">
@@ -9295,7 +9289,7 @@
         <v>16</v>
       </c>
       <c r="C754" t="n">
-        <v>-0.519270987133343</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="755">
@@ -9317,7 +9311,7 @@
         <v>16</v>
       </c>
       <c r="C756" t="n">
-        <v>-0.151636667884865</v>
+        <v>-0.737720162352456</v>
       </c>
     </row>
     <row r="757">
@@ -9339,7 +9333,7 @@
         <v>16</v>
       </c>
       <c r="C758" t="n">
-        <v>-0.265716844180471</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="759">
@@ -9361,7 +9355,7 @@
         <v>16</v>
       </c>
       <c r="C760" t="n">
-        <v>-0.274949794128285</v>
+        <v>0.4176540011027</v>
       </c>
     </row>
     <row r="761">
@@ -9372,7 +9366,7 @@
         <v>16</v>
       </c>
       <c r="C761" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.695138453170354</v>
       </c>
     </row>
     <row r="762">
@@ -9383,7 +9377,7 @@
         <v>16</v>
       </c>
       <c r="C762" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.925310766556742</v>
       </c>
     </row>
     <row r="763">
@@ -9416,7 +9410,7 @@
         <v>16</v>
       </c>
       <c r="C765" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.677179781191334</v>
       </c>
     </row>
     <row r="766">
@@ -9427,7 +9421,7 @@
         <v>16</v>
       </c>
       <c r="C766" t="n">
-        <v>-0.149651623108917</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="767">
@@ -9438,7 +9432,7 @@
         <v>16</v>
       </c>
       <c r="C767" t="n">
-        <v>-0.366822455417262</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="768">
@@ -9449,7 +9443,7 @@
         <v>16</v>
       </c>
       <c r="C768" t="n">
-        <v>-0.360307283505165</v>
+        <v>-0.421389810854553</v>
       </c>
     </row>
     <row r="769">
@@ -9460,7 +9454,7 @@
         <v>16</v>
       </c>
       <c r="C769" t="n">
-        <v>-0.251170481721366</v>
+        <v>-0.322043448331911</v>
       </c>
     </row>
     <row r="770">
@@ -9471,7 +9465,7 @@
         <v>16</v>
       </c>
       <c r="C770" t="n">
-        <v>-0.385148281906229</v>
+        <v>-0.438372472745023</v>
       </c>
     </row>
     <row r="771">
@@ -9482,7 +9476,7 @@
         <v>16</v>
       </c>
       <c r="C771" t="n">
-        <v>-0.301254479140594</v>
+        <v>-0.400155357867347</v>
       </c>
     </row>
     <row r="772">
@@ -9493,7 +9487,7 @@
         <v>16</v>
       </c>
       <c r="C772" t="n">
-        <v>-0.294344772043128</v>
+        <v>-0.204768869361253</v>
       </c>
     </row>
     <row r="773">
@@ -9504,7 +9498,7 @@
         <v>16</v>
       </c>
       <c r="C773" t="n">
-        <v>-0.278631857195935</v>
+        <v>0.705169999928952</v>
       </c>
     </row>
     <row r="774">
@@ -9515,7 +9509,7 @@
         <v>16</v>
       </c>
       <c r="C774" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.67721197304277</v>
       </c>
     </row>
     <row r="775">
@@ -9526,7 +9520,7 @@
         <v>16</v>
       </c>
       <c r="C775" t="n">
-        <v>-0.199544838309555</v>
+        <v>-0.213371765514748</v>
       </c>
     </row>
     <row r="776">
@@ -9548,7 +9542,7 @@
         <v>16</v>
       </c>
       <c r="C777" t="n">
-        <v>-0.197701676343587</v>
+        <v>-0.670361430807248</v>
       </c>
     </row>
     <row r="778">
@@ -9603,7 +9597,7 @@
         <v>16</v>
       </c>
       <c r="C782" t="n">
-        <v>-0.665286773663281</v>
+        <v>-0.587408079462041</v>
       </c>
     </row>
     <row r="783">
@@ -9625,7 +9619,7 @@
         <v>16</v>
       </c>
       <c r="C784" t="n">
-        <v>-0.403640923615815</v>
+        <v>-0.627895865551828</v>
       </c>
     </row>
     <row r="785">
@@ -9636,7 +9630,7 @@
         <v>16</v>
       </c>
       <c r="C785" t="n">
-        <v>-0.204398332949941</v>
+        <v>-0.491953590718451</v>
       </c>
     </row>
     <row r="786">
@@ -9647,7 +9641,7 @@
         <v>16</v>
       </c>
       <c r="C786" t="n">
-        <v>-0.179139269037498</v>
+        <v>-0.180925355924654</v>
       </c>
     </row>
     <row r="787">
@@ -9658,7 +9652,7 @@
         <v>16</v>
       </c>
       <c r="C787" t="n">
-        <v>-0.159763313609467</v>
+        <v>-7.09101479935117</v>
       </c>
     </row>
     <row r="788">
@@ -9669,7 +9663,7 @@
         <v>16</v>
       </c>
       <c r="C788" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.412267346706573</v>
       </c>
     </row>
     <row r="789">
@@ -9680,7 +9674,7 @@
         <v>16</v>
       </c>
       <c r="C789" t="n">
-        <v>-0.00125182190146722</v>
+        <v>0.358094967442005</v>
       </c>
     </row>
     <row r="790">
@@ -9691,7 +9685,7 @@
         <v>16</v>
       </c>
       <c r="C790" t="n">
-        <v>-0.187876706337625</v>
+        <v>0.0128708511632837</v>
       </c>
     </row>
     <row r="791">
@@ -9713,7 +9707,7 @@
         <v>16</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.73833864413259</v>
       </c>
     </row>
     <row r="793">
@@ -9757,7 +9751,7 @@
         <v>16</v>
       </c>
       <c r="C796" t="n">
-        <v>0.137578349311056</v>
+        <v>-1.62412826508293</v>
       </c>
     </row>
     <row r="797">
@@ -9768,7 +9762,7 @@
         <v>16</v>
       </c>
       <c r="C797" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.436019525199177</v>
       </c>
     </row>
     <row r="798">
@@ -9779,7 +9773,7 @@
         <v>16</v>
       </c>
       <c r="C798" t="n">
-        <v>-0.224442883151142</v>
+        <v>-0.23886186727405</v>
       </c>
     </row>
     <row r="799">
@@ -9790,7 +9784,7 @@
         <v>16</v>
       </c>
       <c r="C799" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.226564476256344</v>
       </c>
     </row>
     <row r="800">
@@ -9801,7 +9795,7 @@
         <v>16</v>
       </c>
       <c r="C800" t="n">
-        <v>-1.04681806067122</v>
+        <v>-0.40869032566673</v>
       </c>
     </row>
     <row r="801">
@@ -9812,7 +9806,7 @@
         <v>16</v>
       </c>
       <c r="C801" t="n">
-        <v>-0.34286477796504</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="802">
@@ -9823,7 +9817,7 @@
         <v>16</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.670821468953405</v>
+        <v>-0.272056214696282</v>
       </c>
     </row>
     <row r="803">
@@ -9834,7 +9828,7 @@
         <v>16</v>
       </c>
       <c r="C803" t="n">
-        <v>-0.555782485912149</v>
+        <v>-0.309400144362013</v>
       </c>
     </row>
     <row r="804">
@@ -9845,7 +9839,7 @@
         <v>16</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.776288135519648</v>
+        <v>-0.718955967951218</v>
       </c>
     </row>
     <row r="805">
@@ -9856,7 +9850,7 @@
         <v>16</v>
       </c>
       <c r="C805" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.677112153058385</v>
       </c>
     </row>
     <row r="806">
@@ -9867,7 +9861,7 @@
         <v>16</v>
       </c>
       <c r="C806" t="n">
-        <v>-0.0769645213183872</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="807">
@@ -9889,7 +9883,7 @@
         <v>16</v>
       </c>
       <c r="C808" t="n">
-        <v>0.240203241227115</v>
+        <v>0.092634110590165</v>
       </c>
     </row>
     <row r="809">
@@ -9911,7 +9905,7 @@
         <v>16</v>
       </c>
       <c r="C810" t="n">
-        <v>-0.244972866555324</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="811">
@@ -9933,7 +9927,7 @@
         <v>16</v>
       </c>
       <c r="C812" t="n">
-        <v>-0.217860884066754</v>
+        <v>-0.198976684077801</v>
       </c>
     </row>
     <row r="813">
@@ -9944,7 +9938,7 @@
         <v>16</v>
       </c>
       <c r="C813" t="n">
-        <v>-0.511518574698007</v>
+        <v>-0.294312343609362</v>
       </c>
     </row>
     <row r="814">
@@ -9955,7 +9949,7 @@
         <v>16</v>
       </c>
       <c r="C814" t="n">
-        <v>-0.46220772641942</v>
+        <v>0.00694568636416715</v>
       </c>
     </row>
     <row r="815">
@@ -9966,7 +9960,7 @@
         <v>16</v>
       </c>
       <c r="C815" t="n">
-        <v>-0.225363658924949</v>
+        <v>-0.483715809194438</v>
       </c>
     </row>
     <row r="816">
@@ -9977,7 +9971,7 @@
         <v>16</v>
       </c>
       <c r="C816" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.394623847078372</v>
       </c>
     </row>
     <row r="817">
@@ -9999,7 +9993,7 @@
         <v>16</v>
       </c>
       <c r="C818" t="n">
-        <v>0.342159452056617</v>
+        <v>0.323909708341807</v>
       </c>
     </row>
     <row r="819">
@@ -10010,7 +10004,7 @@
         <v>16</v>
       </c>
       <c r="C819" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.37353230652166</v>
       </c>
     </row>
     <row r="820">
@@ -10021,7 +10015,7 @@
         <v>16</v>
       </c>
       <c r="C820" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.433998730897353</v>
       </c>
     </row>
     <row r="821">
@@ -10032,7 +10026,7 @@
         <v>16</v>
       </c>
       <c r="C821" t="n">
-        <v>-0.258965583080051</v>
+        <v>-0.6332170592895</v>
       </c>
     </row>
     <row r="822">
@@ -10054,7 +10048,7 @@
         <v>16</v>
       </c>
       <c r="C823" t="n">
-        <v>-0.658231506043533</v>
+        <v>-0.749189635327739</v>
       </c>
     </row>
     <row r="824">
@@ -10065,7 +10059,7 @@
         <v>16</v>
       </c>
       <c r="C824" t="n">
-        <v>-0.230445009989318</v>
+        <v>-0.249204159693381</v>
       </c>
     </row>
     <row r="825">
@@ -10076,7 +10070,7 @@
         <v>16</v>
       </c>
       <c r="C825" t="n">
-        <v>-0.319272657879816</v>
+        <v>-0.544607394901956</v>
       </c>
     </row>
     <row r="826">
@@ -10087,7 +10081,7 @@
         <v>16</v>
       </c>
       <c r="C826" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.575605998245506</v>
       </c>
     </row>
     <row r="827">
@@ -10098,7 +10092,7 @@
         <v>16</v>
       </c>
       <c r="C827" t="n">
-        <v>-0.217877819965863</v>
+        <v>-2.56105949092218</v>
       </c>
     </row>
     <row r="828">
@@ -10109,7 +10103,7 @@
         <v>16</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.753697784943548</v>
       </c>
     </row>
     <row r="829">
@@ -10120,7 +10114,7 @@
         <v>16</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.217865900437562</v>
+        <v>-0.254602630941221</v>
       </c>
     </row>
     <row r="830">
@@ -10131,7 +10125,7 @@
         <v>16</v>
       </c>
       <c r="C830" t="n">
-        <v>-0.726806999196489</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="831">
@@ -10142,7 +10136,7 @@
         <v>16</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.38661993847907</v>
+        <v>-1.66167979835515</v>
       </c>
     </row>
     <row r="832">
@@ -10164,7 +10158,7 @@
         <v>16</v>
       </c>
       <c r="C833" t="n">
-        <v>-0.496338831845186</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="834">
@@ -10175,7 +10169,7 @@
         <v>16</v>
       </c>
       <c r="C834" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.378075147510245</v>
       </c>
     </row>
     <row r="835">
@@ -10186,7 +10180,7 @@
         <v>16</v>
       </c>
       <c r="C835" t="n">
-        <v>0.635438281652688</v>
+        <v>-0.0337908115767058</v>
       </c>
     </row>
     <row r="836">
@@ -10197,7 +10191,7 @@
         <v>16</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.382397873882151</v>
+        <v>-0.457023455623585</v>
       </c>
     </row>
     <row r="837">
@@ -10219,7 +10213,7 @@
         <v>16</v>
       </c>
       <c r="C838" t="n">
-        <v>-0.296919574284826</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="839">
@@ -10241,7 +10235,7 @@
         <v>16</v>
       </c>
       <c r="C840" t="n">
-        <v>-0.189488823545347</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="841">
@@ -10252,7 +10246,7 @@
         <v>16</v>
       </c>
       <c r="C841" t="n">
-        <v>-0.515958385521591</v>
+        <v>-0.63256177685755</v>
       </c>
     </row>
     <row r="842">
@@ -10263,7 +10257,7 @@
         <v>16</v>
       </c>
       <c r="C842" t="n">
-        <v>-0.271793505569119</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="843">
@@ -10274,7 +10268,7 @@
         <v>16</v>
       </c>
       <c r="C843" t="n">
-        <v>-0.17091941166631</v>
+        <v>-0.846698026234534</v>
       </c>
     </row>
     <row r="844">
@@ -10285,7 +10279,7 @@
         <v>16</v>
       </c>
       <c r="C844" t="n">
-        <v>-0.245195247456133</v>
+        <v>-0.225151028857364</v>
       </c>
     </row>
     <row r="845">
@@ -10296,7 +10290,7 @@
         <v>16</v>
       </c>
       <c r="C845" t="n">
-        <v>-0.700833511893066</v>
+        <v>-0.450694193298529</v>
       </c>
     </row>
     <row r="846">
@@ -10318,7 +10312,7 @@
         <v>16</v>
       </c>
       <c r="C847" t="n">
-        <v>-0.526833995968893</v>
+        <v>-0.943049699699319</v>
       </c>
     </row>
     <row r="848">
@@ -10329,7 +10323,7 @@
         <v>16</v>
       </c>
       <c r="C848" t="n">
-        <v>-0.184773907753375</v>
+        <v>-4.28715059554554</v>
       </c>
     </row>
     <row r="849">
@@ -10340,7 +10334,7 @@
         <v>16</v>
       </c>
       <c r="C849" t="n">
-        <v>0.412596944109996</v>
+        <v>0.501212733715013</v>
       </c>
     </row>
     <row r="850">
@@ -10351,7 +10345,7 @@
         <v>16</v>
       </c>
       <c r="C850" t="n">
-        <v>-0.430677978694907</v>
+        <v>-0.199374115446404</v>
       </c>
     </row>
     <row r="851">
@@ -10362,7 +10356,7 @@
         <v>16</v>
       </c>
       <c r="C851" t="n">
-        <v>-2.25800779568602</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="852">
@@ -10384,7 +10378,7 @@
         <v>16</v>
       </c>
       <c r="C853" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.417911603936222</v>
       </c>
     </row>
     <row r="854">
@@ -10395,7 +10389,7 @@
         <v>16</v>
       </c>
       <c r="C854" t="n">
-        <v>-0.238766676025971</v>
+        <v>-0.368811385124131</v>
       </c>
     </row>
     <row r="855">
@@ -10406,7 +10400,7 @@
         <v>16</v>
       </c>
       <c r="C855" t="n">
-        <v>0.293050338941493</v>
+        <v>0.433692052892966</v>
       </c>
     </row>
     <row r="856">
@@ -10417,7 +10411,7 @@
         <v>16</v>
       </c>
       <c r="C856" t="n">
-        <v>-0.55242528513621</v>
+        <v>-0.909784116664108</v>
       </c>
     </row>
     <row r="857">
@@ -10428,7 +10422,7 @@
         <v>16</v>
       </c>
       <c r="C857" t="n">
-        <v>-0.25906272506761</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="858">
@@ -10439,7 +10433,7 @@
         <v>16</v>
       </c>
       <c r="C858" t="n">
-        <v>0.636710055777734</v>
+        <v>0.508238090626971</v>
       </c>
     </row>
     <row r="859">
@@ -10450,7 +10444,7 @@
         <v>16</v>
       </c>
       <c r="C859" t="n">
-        <v>-0.521439525387853</v>
+        <v>0.204391044235302</v>
       </c>
     </row>
     <row r="860">
@@ -10461,7 +10455,7 @@
         <v>16</v>
       </c>
       <c r="C860" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.537021346878347</v>
       </c>
     </row>
     <row r="861">
@@ -10472,7 +10466,7 @@
         <v>16</v>
       </c>
       <c r="C861" t="n">
-        <v>-0.294362086205777</v>
+        <v>-0.256766167544566</v>
       </c>
     </row>
     <row r="862">
@@ -10483,7 +10477,7 @@
         <v>16</v>
       </c>
       <c r="C862" t="n">
-        <v>-0.674632855663496</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="863">
@@ -10494,7 +10488,7 @@
         <v>16</v>
       </c>
       <c r="C863" t="n">
-        <v>-4.5607834598418</v>
+        <v>-2.41668745502888</v>
       </c>
     </row>
     <row r="864">
@@ -10505,7 +10499,7 @@
         <v>16</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.421706874483813</v>
+        <v>-1.85516899138733</v>
       </c>
     </row>
     <row r="865">
@@ -10516,7 +10510,7 @@
         <v>16</v>
       </c>
       <c r="C865" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.215838257983549</v>
       </c>
     </row>
     <row r="866">
@@ -10527,7 +10521,7 @@
         <v>16</v>
       </c>
       <c r="C866" t="n">
-        <v>0.111887020343068</v>
+        <v>-0.660151801466512</v>
       </c>
     </row>
     <row r="867">
@@ -10538,7 +10532,7 @@
         <v>16</v>
       </c>
       <c r="C867" t="n">
-        <v>-0.295464183356051</v>
+        <v>-0.210669447003553</v>
       </c>
     </row>
     <row r="868">
@@ -10549,7 +10543,7 @@
         <v>16</v>
       </c>
       <c r="C868" t="n">
-        <v>-0.0491944654582337</v>
+        <v>-0.307327377799381</v>
       </c>
     </row>
     <row r="869">
@@ -10560,7 +10554,7 @@
         <v>16</v>
       </c>
       <c r="C869" t="n">
-        <v>-0.213274295047449</v>
+        <v>-0.228435504667946</v>
       </c>
     </row>
     <row r="870">
@@ -10571,7 +10565,7 @@
         <v>16</v>
       </c>
       <c r="C870" t="n">
-        <v>-0.323245230653371</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="871">
@@ -10582,7 +10576,7 @@
         <v>16</v>
       </c>
       <c r="C871" t="n">
-        <v>-0.274473468238647</v>
+        <v>-1.11677026088598</v>
       </c>
     </row>
     <row r="872">
@@ -10593,7 +10587,7 @@
         <v>16</v>
       </c>
       <c r="C872" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.34735878874523</v>
       </c>
     </row>
     <row r="873">
@@ -10604,7 +10598,7 @@
         <v>16</v>
       </c>
       <c r="C873" t="n">
-        <v>-0.358907390162219</v>
+        <v>-0.378294525538721</v>
       </c>
     </row>
     <row r="874">
@@ -10615,7 +10609,7 @@
         <v>16</v>
       </c>
       <c r="C874" t="n">
-        <v>-0.33263600966922</v>
+        <v>0.02089404367673</v>
       </c>
     </row>
     <row r="875">
@@ -10626,7 +10620,7 @@
         <v>16</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.249594597869606</v>
+        <v>-1.19866750142933</v>
       </c>
     </row>
     <row r="876">
@@ -10637,7 +10631,7 @@
         <v>16</v>
       </c>
       <c r="C876" t="n">
-        <v>-0.759671529927788</v>
+        <v>-0.673270324005963</v>
       </c>
     </row>
     <row r="877">
@@ -10648,7 +10642,7 @@
         <v>16</v>
       </c>
       <c r="C877" t="n">
-        <v>-0.33714765880413</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="878">
@@ -10659,7 +10653,7 @@
         <v>16</v>
       </c>
       <c r="C878" t="n">
-        <v>0.0242215760420288</v>
+        <v>0.133108476855907</v>
       </c>
     </row>
     <row r="879">
@@ -10670,7 +10664,7 @@
         <v>16</v>
       </c>
       <c r="C879" t="n">
-        <v>0.695698905291765</v>
+        <v>-0.39866578791808</v>
       </c>
     </row>
     <row r="880">
@@ -10681,7 +10675,7 @@
         <v>16</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.441051894449415</v>
       </c>
     </row>
     <row r="881">
@@ -10692,7 +10686,7 @@
         <v>16</v>
       </c>
       <c r="C881" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.865529665657053</v>
       </c>
     </row>
     <row r="882">
@@ -10703,7 +10697,7 @@
         <v>16</v>
       </c>
       <c r="C882" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.884206172637665</v>
       </c>
     </row>
     <row r="883">
@@ -10714,7 +10708,7 @@
         <v>16</v>
       </c>
       <c r="C883" t="n">
-        <v>-0.850198973126389</v>
+        <v>-0.629639801887766</v>
       </c>
     </row>
     <row r="884">
@@ -10725,7 +10719,7 @@
         <v>16</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.324130072788642</v>
+        <v>-0.330172830999042</v>
       </c>
     </row>
     <row r="885">
@@ -10736,7 +10730,7 @@
         <v>16</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.652514705333342</v>
+        <v>-0.483192101369731</v>
       </c>
     </row>
     <row r="886">
@@ -10747,7 +10741,7 @@
         <v>16</v>
       </c>
       <c r="C886" t="n">
-        <v>-0.197768544567208</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="887">
@@ -10758,7 +10752,7 @@
         <v>16</v>
       </c>
       <c r="C887" t="n">
-        <v>0.0111179977720673</v>
+        <v>-0.243484841915656</v>
       </c>
     </row>
     <row r="888">
@@ -10769,7 +10763,7 @@
         <v>16</v>
       </c>
       <c r="C888" t="n">
-        <v>-1.61820408670852</v>
+        <v>-0.747696367909901</v>
       </c>
     </row>
     <row r="889">
@@ -10780,7 +10774,7 @@
         <v>16</v>
       </c>
       <c r="C889" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.115689357444323</v>
       </c>
     </row>
     <row r="890">
@@ -10791,7 +10785,7 @@
         <v>16</v>
       </c>
       <c r="C890" t="n">
-        <v>-0.410887637631294</v>
+        <v>-0.782182125423899</v>
       </c>
     </row>
     <row r="891">
@@ -10802,7 +10796,7 @@
         <v>16</v>
       </c>
       <c r="C891" t="n">
-        <v>-0.159763313609467</v>
+        <v>-6.34834346472886</v>
       </c>
     </row>
     <row r="892">
@@ -10813,7 +10807,7 @@
         <v>16</v>
       </c>
       <c r="C892" t="n">
-        <v>-0.22854512725531</v>
+        <v>-0.202003159166365</v>
       </c>
     </row>
     <row r="893">
@@ -10824,7 +10818,7 @@
         <v>16</v>
       </c>
       <c r="C893" t="n">
-        <v>0.0268251090632061</v>
+        <v>-0.244316159583875</v>
       </c>
     </row>
     <row r="894">
@@ -10835,7 +10829,7 @@
         <v>16</v>
       </c>
       <c r="C894" t="n">
-        <v>-0.487269461641522</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="895">
@@ -10846,7 +10840,7 @@
         <v>16</v>
       </c>
       <c r="C895" t="n">
-        <v>-0.360408739039294</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="896">
@@ -10857,7 +10851,7 @@
         <v>16</v>
       </c>
       <c r="C896" t="n">
-        <v>-0.188061161161142</v>
+        <v>-0.187088601647734</v>
       </c>
     </row>
     <row r="897">
@@ -10868,7 +10862,7 @@
         <v>16</v>
       </c>
       <c r="C897" t="n">
-        <v>-1.35370232465703</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="898">
@@ -10879,7 +10873,7 @@
         <v>16</v>
       </c>
       <c r="C898" t="n">
-        <v>-0.0774062922772984</v>
+        <v>-0.835814455515398</v>
       </c>
     </row>
     <row r="899">
@@ -10890,7 +10884,7 @@
         <v>16</v>
       </c>
       <c r="C899" t="n">
-        <v>-1.00126137875467</v>
+        <v>-4.18973522604323</v>
       </c>
     </row>
     <row r="900">
@@ -10901,7 +10895,7 @@
         <v>16</v>
       </c>
       <c r="C900" t="n">
-        <v>-0.264644066706928</v>
+        <v>-0.259523872885675</v>
       </c>
     </row>
     <row r="901">
@@ -10912,7 +10906,7 @@
         <v>16</v>
       </c>
       <c r="C901" t="n">
-        <v>-0.187722669756468</v>
+        <v>-0.184784478500252</v>
       </c>
     </row>
     <row r="902">
@@ -10923,7 +10917,7 @@
         <v>16</v>
       </c>
       <c r="C902" t="n">
-        <v>-0.0675762531923121</v>
+        <v>-0.758453565799581</v>
       </c>
     </row>
     <row r="903">
@@ -10934,7 +10928,7 @@
         <v>16</v>
       </c>
       <c r="C903" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.177346301756129</v>
       </c>
     </row>
     <row r="904">
@@ -10967,7 +10961,7 @@
         <v>16</v>
       </c>
       <c r="C906" t="n">
-        <v>-0.0734875126521686</v>
+        <v>-0.656504015071365</v>
       </c>
     </row>
     <row r="907">
@@ -10989,7 +10983,7 @@
         <v>16</v>
       </c>
       <c r="C908" t="n">
-        <v>-0.29799139258802</v>
+        <v>-0.625355865658761</v>
       </c>
     </row>
     <row r="909">
@@ -11000,7 +10994,7 @@
         <v>16</v>
       </c>
       <c r="C909" t="n">
-        <v>-0.840677101327001</v>
+        <v>-1.07225541686103</v>
       </c>
     </row>
     <row r="910">
@@ -11011,7 +11005,7 @@
         <v>16</v>
       </c>
       <c r="C910" t="n">
-        <v>-0.20600908073495</v>
+        <v>0.0776631913542096</v>
       </c>
     </row>
     <row r="911">
@@ -11033,7 +11027,7 @@
         <v>16</v>
       </c>
       <c r="C912" t="n">
-        <v>-0.0736047661982775</v>
+        <v>-0.393548436671298</v>
       </c>
     </row>
     <row r="913">
@@ -11044,7 +11038,7 @@
         <v>16</v>
       </c>
       <c r="C913" t="n">
-        <v>-0.386095823227995</v>
+        <v>-0.198315586324948</v>
       </c>
     </row>
     <row r="914">
@@ -11066,7 +11060,7 @@
         <v>16</v>
       </c>
       <c r="C915" t="n">
-        <v>0.600797091295398</v>
+        <v>0.562258805153036</v>
       </c>
     </row>
     <row r="916">
@@ -11077,7 +11071,7 @@
         <v>16</v>
       </c>
       <c r="C916" t="n">
-        <v>-1.30167164872152</v>
+        <v>-0.839583124158938</v>
       </c>
     </row>
     <row r="917">
@@ -11088,7 +11082,7 @@
         <v>16</v>
       </c>
       <c r="C917" t="n">
-        <v>-0.279998068201213</v>
+        <v>-1.30362250607353</v>
       </c>
     </row>
     <row r="918">
@@ -11099,7 +11093,7 @@
         <v>16</v>
       </c>
       <c r="C918" t="n">
-        <v>-0.786694349965348</v>
+        <v>-0.682906211321746</v>
       </c>
     </row>
     <row r="919">
@@ -11121,7 +11115,7 @@
         <v>16</v>
       </c>
       <c r="C920" t="n">
-        <v>-0.262879019365933</v>
+        <v>-0.251777980105935</v>
       </c>
     </row>
     <row r="921">
@@ -11132,7 +11126,7 @@
         <v>16</v>
       </c>
       <c r="C921" t="n">
-        <v>-0.258280766031961</v>
+        <v>-0.212082270480441</v>
       </c>
     </row>
     <row r="922">
@@ -11143,7 +11137,7 @@
         <v>16</v>
       </c>
       <c r="C922" t="n">
-        <v>-0.845295028602811</v>
+        <v>-0.45671473980006</v>
       </c>
     </row>
     <row r="923">
@@ -11154,7 +11148,7 @@
         <v>16</v>
       </c>
       <c r="C923" t="n">
-        <v>-0.182527769149502</v>
+        <v>-0.117113921565193</v>
       </c>
     </row>
     <row r="924">
@@ -11165,7 +11159,7 @@
         <v>16</v>
       </c>
       <c r="C924" t="n">
-        <v>-0.189112439730291</v>
+        <v>-0.218107843301954</v>
       </c>
     </row>
     <row r="925">
@@ -11176,7 +11170,7 @@
         <v>16</v>
       </c>
       <c r="C925" t="n">
-        <v>-0.330104876843146</v>
+        <v>-1.03394849147967</v>
       </c>
     </row>
     <row r="926">
@@ -11198,7 +11192,7 @@
         <v>16</v>
       </c>
       <c r="C927" t="n">
-        <v>-1.3503425175238</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="928">
@@ -11209,7 +11203,7 @@
         <v>16</v>
       </c>
       <c r="C928" t="n">
-        <v>-0.60685380988866</v>
+        <v>-0.0639780426563032</v>
       </c>
     </row>
     <row r="929">
@@ -11220,7 +11214,7 @@
         <v>16</v>
       </c>
       <c r="C929" t="n">
-        <v>-0.256814433594443</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="930">
@@ -11231,7 +11225,7 @@
         <v>16</v>
       </c>
       <c r="C930" t="n">
-        <v>-0.15793981680221</v>
+        <v>-1.20378542995846</v>
       </c>
     </row>
     <row r="931">
@@ -11242,7 +11236,7 @@
         <v>16</v>
       </c>
       <c r="C931" t="n">
-        <v>-0.383799166128846</v>
+        <v>-2.38001419419725</v>
       </c>
     </row>
     <row r="932">
@@ -11253,7 +11247,7 @@
         <v>16</v>
       </c>
       <c r="C932" t="n">
-        <v>-0.548427823020204</v>
+        <v>-0.206267115612187</v>
       </c>
     </row>
     <row r="933">
@@ -11264,7 +11258,7 @@
         <v>16</v>
       </c>
       <c r="C933" t="n">
-        <v>0.204248310410873</v>
+        <v>0.280811549036334</v>
       </c>
     </row>
     <row r="934">
@@ -11275,7 +11269,7 @@
         <v>16</v>
       </c>
       <c r="C934" t="n">
-        <v>0.775972600316382</v>
+        <v>-1.02249992309348</v>
       </c>
     </row>
     <row r="935">
@@ -11297,7 +11291,7 @@
         <v>16</v>
       </c>
       <c r="C936" t="n">
-        <v>-2.74279639158485</v>
+        <v>-10.0009153333993</v>
       </c>
     </row>
     <row r="937">
@@ -11308,7 +11302,7 @@
         <v>16</v>
       </c>
       <c r="C937" t="n">
-        <v>-0.308572883176768</v>
+        <v>0.221506833512667</v>
       </c>
     </row>
     <row r="938">
@@ -11319,7 +11313,7 @@
         <v>16</v>
       </c>
       <c r="C938" t="n">
-        <v>0.686657229372228</v>
+        <v>0.728646396885461</v>
       </c>
     </row>
     <row r="939">
@@ -11330,7 +11324,7 @@
         <v>16</v>
       </c>
       <c r="C939" t="n">
-        <v>-2.62273737140817</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="940">
@@ -11341,7 +11335,7 @@
         <v>16</v>
       </c>
       <c r="C940" t="n">
-        <v>-0.20163169976361</v>
+        <v>-0.027233349742311</v>
       </c>
     </row>
     <row r="941">
@@ -11352,7 +11346,7 @@
         <v>16</v>
       </c>
       <c r="C941" t="n">
-        <v>-0.30255592443894</v>
+        <v>-0.348910906028071</v>
       </c>
     </row>
     <row r="942">
@@ -11363,7 +11357,7 @@
         <v>16</v>
       </c>
       <c r="C942" t="n">
-        <v>-0.0818467851795837</v>
+        <v>-1.24068702069254</v>
       </c>
     </row>
     <row r="943">
@@ -11374,7 +11368,7 @@
         <v>16</v>
       </c>
       <c r="C943" t="n">
-        <v>-0.740796578420732</v>
+        <v>-1.09217384833746</v>
       </c>
     </row>
     <row r="944">
@@ -11385,7 +11379,7 @@
         <v>16</v>
       </c>
       <c r="C944" t="n">
-        <v>-0.23157717203434</v>
+        <v>-2.26032109591687</v>
       </c>
     </row>
     <row r="945">
@@ -11396,7 +11390,7 @@
         <v>16</v>
       </c>
       <c r="C945" t="n">
-        <v>-0.961666922293089</v>
+        <v>-0.985306038730617</v>
       </c>
     </row>
     <row r="946">
@@ -11418,7 +11412,7 @@
         <v>16</v>
       </c>
       <c r="C947" t="n">
-        <v>-1.56261004073649</v>
+        <v>-0.293190100231123</v>
       </c>
     </row>
     <row r="948">
@@ -11429,7 +11423,7 @@
         <v>16</v>
       </c>
       <c r="C948" t="n">
-        <v>-1.20558276574707</v>
+        <v>-0.69198203581413</v>
       </c>
     </row>
     <row r="949">
@@ -11440,7 +11434,7 @@
         <v>16</v>
       </c>
       <c r="C949" t="n">
-        <v>-0.243119647552438</v>
+        <v>-0.202743127115442</v>
       </c>
     </row>
     <row r="950">
@@ -11451,7 +11445,7 @@
         <v>16</v>
       </c>
       <c r="C950" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.724900583346713</v>
       </c>
     </row>
     <row r="951">
@@ -11473,7 +11467,7 @@
         <v>16</v>
       </c>
       <c r="C952" t="n">
-        <v>-0.76334292180402</v>
+        <v>-0.604474795296287</v>
       </c>
     </row>
     <row r="953">
@@ -11484,7 +11478,7 @@
         <v>16</v>
       </c>
       <c r="C953" t="n">
-        <v>-0.503243163536601</v>
+        <v>-0.529261797144531</v>
       </c>
     </row>
     <row r="954">
@@ -11495,7 +11489,7 @@
         <v>16</v>
       </c>
       <c r="C954" t="n">
-        <v>-0.203956224424698</v>
+        <v>-0.230844844113177</v>
       </c>
     </row>
     <row r="955">
@@ -11506,7 +11500,7 @@
         <v>16</v>
       </c>
       <c r="C955" t="n">
-        <v>-0.0412289314297412</v>
+        <v>-0.238039109838639</v>
       </c>
     </row>
     <row r="956">
@@ -11517,7 +11511,7 @@
         <v>16</v>
       </c>
       <c r="C956" t="n">
-        <v>-0.58902784466081</v>
+        <v>-1.84170133458108</v>
       </c>
     </row>
     <row r="957">
@@ -11528,7 +11522,7 @@
         <v>16</v>
       </c>
       <c r="C957" t="n">
-        <v>-0.943818678058259</v>
+        <v>-0.380733531513205</v>
       </c>
     </row>
     <row r="958">
@@ -11539,7 +11533,7 @@
         <v>16</v>
       </c>
       <c r="C958" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.514471586836407</v>
       </c>
     </row>
     <row r="959">
@@ -11550,7 +11544,7 @@
         <v>16</v>
       </c>
       <c r="C959" t="n">
-        <v>-0.190598867528973</v>
+        <v>-0.316209808395579</v>
       </c>
     </row>
     <row r="960">
@@ -11561,7 +11555,7 @@
         <v>16</v>
       </c>
       <c r="C960" t="n">
-        <v>-0.714482621390489</v>
+        <v>-0.67647987210457</v>
       </c>
     </row>
     <row r="961">
@@ -11572,7 +11566,7 @@
         <v>16</v>
       </c>
       <c r="C961" t="n">
-        <v>-0.14384201125198</v>
+        <v>-0.540743162208075</v>
       </c>
     </row>
     <row r="962">
@@ -11583,7 +11577,7 @@
         <v>16</v>
       </c>
       <c r="C962" t="n">
-        <v>-0.433118921813153</v>
+        <v>-6.96508499266185</v>
       </c>
     </row>
     <row r="963">
@@ -11594,7 +11588,7 @@
         <v>16</v>
       </c>
       <c r="C963" t="n">
-        <v>-0.885962528114479</v>
+        <v>-0.397332419110164</v>
       </c>
     </row>
     <row r="964">
@@ -11605,7 +11599,7 @@
         <v>16</v>
       </c>
       <c r="C964" t="n">
-        <v>-2.64358932858158</v>
+        <v>-0.338851170349614</v>
       </c>
     </row>
     <row r="965">
@@ -11616,7 +11610,7 @@
         <v>16</v>
       </c>
       <c r="C965" t="n">
-        <v>-0.516030949497724</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="966">
@@ -11627,7 +11621,7 @@
         <v>16</v>
       </c>
       <c r="C966" t="n">
-        <v>-0.180309590037076</v>
+        <v>-0.273647081913034</v>
       </c>
     </row>
     <row r="967">
@@ -11638,7 +11632,7 @@
         <v>16</v>
       </c>
       <c r="C967" t="n">
-        <v>-0.598988009886162</v>
+        <v>-1.43834837523827</v>
       </c>
     </row>
     <row r="968">
@@ -11649,7 +11643,7 @@
         <v>16</v>
       </c>
       <c r="C968" t="n">
-        <v>-0.373408653445212</v>
+        <v>-0.195136481215789</v>
       </c>
     </row>
     <row r="969">
@@ -11660,7 +11654,7 @@
         <v>16</v>
       </c>
       <c r="C969" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.166548103008898</v>
       </c>
     </row>
     <row r="970">
@@ -11682,7 +11676,7 @@
         <v>16</v>
       </c>
       <c r="C971" t="n">
-        <v>-0.250748930128912</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="972">
@@ -11693,7 +11687,7 @@
         <v>16</v>
       </c>
       <c r="C972" t="n">
-        <v>-2.60864599791304</v>
+        <v>-0.247976325854565</v>
       </c>
     </row>
     <row r="973">
@@ -11704,7 +11698,7 @@
         <v>16</v>
       </c>
       <c r="C973" t="n">
-        <v>-0.336185201285683</v>
+        <v>-5.29846740766017</v>
       </c>
     </row>
     <row r="974">
@@ -11715,7 +11709,7 @@
         <v>16</v>
       </c>
       <c r="C974" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.520194615621369</v>
       </c>
     </row>
     <row r="975">
@@ -11726,7 +11720,7 @@
         <v>16</v>
       </c>
       <c r="C975" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.284562828419602</v>
       </c>
     </row>
     <row r="976">
@@ -11737,7 +11731,7 @@
         <v>16</v>
       </c>
       <c r="C976" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.664928901289076</v>
       </c>
     </row>
     <row r="977">
@@ -11759,7 +11753,7 @@
         <v>16</v>
       </c>
       <c r="C978" t="n">
-        <v>-0.950275132813426</v>
+        <v>-0.854026173401952</v>
       </c>
     </row>
     <row r="979">
@@ -11770,7 +11764,7 @@
         <v>16</v>
       </c>
       <c r="C979" t="n">
-        <v>0.284639312631774</v>
+        <v>0.167125622961212</v>
       </c>
     </row>
     <row r="980">
@@ -11803,7 +11797,7 @@
         <v>16</v>
       </c>
       <c r="C982" t="n">
-        <v>-0.27585002902927</v>
+        <v>-0.164061468062479</v>
       </c>
     </row>
     <row r="983">
@@ -11814,7 +11808,7 @@
         <v>16</v>
       </c>
       <c r="C983" t="n">
-        <v>-0.127090492806143</v>
+        <v>-1.26172074785214</v>
       </c>
     </row>
     <row r="984">
@@ -11836,7 +11830,7 @@
         <v>16</v>
       </c>
       <c r="C985" t="n">
-        <v>-0.286920427229234</v>
+        <v>-0.384107107500156</v>
       </c>
     </row>
     <row r="986">
@@ -11847,7 +11841,7 @@
         <v>16</v>
       </c>
       <c r="C986" t="n">
-        <v>0.132082627269298</v>
+        <v>-0.671634052606617</v>
       </c>
     </row>
     <row r="987">
@@ -11869,7 +11863,7 @@
         <v>16</v>
       </c>
       <c r="C988" t="n">
-        <v>-0.437774757408608</v>
+        <v>-0.576787016169982</v>
       </c>
     </row>
     <row r="989">
@@ -11880,7 +11874,7 @@
         <v>16</v>
       </c>
       <c r="C989" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.09998565821109</v>
       </c>
     </row>
     <row r="990">
@@ -11891,7 +11885,7 @@
         <v>16</v>
       </c>
       <c r="C990" t="n">
-        <v>-0.443518234557453</v>
+        <v>-0.702405401365738</v>
       </c>
     </row>
     <row r="991">
@@ -11902,7 +11896,7 @@
         <v>16</v>
       </c>
       <c r="C991" t="n">
-        <v>-0.0880697488824607</v>
+        <v>-0.107063229939036</v>
       </c>
     </row>
     <row r="992">
@@ -11913,7 +11907,7 @@
         <v>16</v>
       </c>
       <c r="C992" t="n">
-        <v>-1.73619720379628</v>
+        <v>-1.68460114046262</v>
       </c>
     </row>
     <row r="993">
@@ -11935,7 +11929,7 @@
         <v>16</v>
       </c>
       <c r="C994" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.908279294549931</v>
       </c>
     </row>
     <row r="995">
@@ -11957,7 +11951,7 @@
         <v>16</v>
       </c>
       <c r="C996" t="n">
-        <v>-0.361481121196958</v>
+        <v>0.00353962255650231</v>
       </c>
     </row>
     <row r="997">
@@ -11968,7 +11962,7 @@
         <v>16</v>
       </c>
       <c r="C997" t="n">
-        <v>-1.17278324569263</v>
+        <v>-0.319420374735823</v>
       </c>
     </row>
     <row r="998">
@@ -11979,7 +11973,7 @@
         <v>16</v>
       </c>
       <c r="C998" t="n">
-        <v>-0.0940670371736705</v>
+        <v>-0.47268346992791</v>
       </c>
     </row>
     <row r="999">
@@ -12001,7 +11995,7 @@
         <v>16</v>
       </c>
       <c r="C1000" t="n">
-        <v>-0.282528352292808</v>
+        <v>-0.330895146265165</v>
       </c>
     </row>
     <row r="1001">
@@ -12012,7 +12006,7 @@
         <v>16</v>
       </c>
       <c r="C1001" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.202895622046733</v>
       </c>
     </row>
     <row r="1002">
@@ -12023,7 +12017,7 @@
         <v>16</v>
       </c>
       <c r="C1002" t="n">
-        <v>-0.437163974467193</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1003">
@@ -12034,7 +12028,7 @@
         <v>16</v>
       </c>
       <c r="C1003" t="n">
-        <v>-0.287547266682828</v>
+        <v>-0.237336941505565</v>
       </c>
     </row>
     <row r="1004">
@@ -12045,7 +12039,7 @@
         <v>16</v>
       </c>
       <c r="C1004" t="n">
-        <v>-0.375930101609003</v>
+        <v>-1.94826747155842</v>
       </c>
     </row>
     <row r="1005">
@@ -12056,7 +12050,7 @@
         <v>16</v>
       </c>
       <c r="C1005" t="n">
-        <v>-0.301151591956556</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1006">
@@ -12067,7 +12061,7 @@
         <v>16</v>
       </c>
       <c r="C1006" t="n">
-        <v>-0.922602344318659</v>
+        <v>-0.140233804072821</v>
       </c>
     </row>
     <row r="1007">
@@ -12078,7 +12072,7 @@
         <v>16</v>
       </c>
       <c r="C1007" t="n">
-        <v>-0.426644931473069</v>
+        <v>-0.192933821494219</v>
       </c>
     </row>
     <row r="1008">
@@ -12089,7 +12083,7 @@
         <v>16</v>
       </c>
       <c r="C1008" t="n">
-        <v>-0.482879933496718</v>
+        <v>-0.0717240312959189</v>
       </c>
     </row>
     <row r="1009">
@@ -12100,7 +12094,7 @@
         <v>16</v>
       </c>
       <c r="C1009" t="n">
-        <v>-0.377366005248669</v>
+        <v>-0.539240521738366</v>
       </c>
     </row>
     <row r="1010">
@@ -12111,7 +12105,7 @@
         <v>16</v>
       </c>
       <c r="C1010" t="n">
-        <v>-1.89744498279957</v>
+        <v>-1.36040808606205</v>
       </c>
     </row>
     <row r="1011">
@@ -12155,7 +12149,7 @@
         <v>16</v>
       </c>
       <c r="C1014" t="n">
-        <v>-0.233360337948906</v>
+        <v>-0.381836093926763</v>
       </c>
     </row>
     <row r="1015">
@@ -12166,7 +12160,7 @@
         <v>16</v>
       </c>
       <c r="C1015" t="n">
-        <v>-0.209680498424921</v>
+        <v>-0.708212093261879</v>
       </c>
     </row>
     <row r="1016">
@@ -12177,7 +12171,7 @@
         <v>16</v>
       </c>
       <c r="C1016" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.447811588144954</v>
       </c>
     </row>
     <row r="1017">
@@ -12188,7 +12182,7 @@
         <v>16</v>
       </c>
       <c r="C1017" t="n">
-        <v>-1.03552240096068</v>
+        <v>-1.12107977464342</v>
       </c>
     </row>
     <row r="1018">
@@ -12199,7 +12193,7 @@
         <v>16</v>
       </c>
       <c r="C1018" t="n">
-        <v>-0.152187160710589</v>
+        <v>-0.39517091435396</v>
       </c>
     </row>
     <row r="1019">
@@ -12210,7 +12204,7 @@
         <v>16</v>
       </c>
       <c r="C1019" t="n">
-        <v>0.528879547172366</v>
+        <v>-0.348406399110711</v>
       </c>
     </row>
     <row r="1020">
@@ -12243,7 +12237,7 @@
         <v>16</v>
       </c>
       <c r="C1022" t="n">
-        <v>-0.236167989033194</v>
+        <v>-0.481206402701078</v>
       </c>
     </row>
     <row r="1023">
@@ -12254,7 +12248,7 @@
         <v>16</v>
       </c>
       <c r="C1023" t="n">
-        <v>-0.317876825669365</v>
+        <v>-0.0819277950277784</v>
       </c>
     </row>
     <row r="1024">
@@ -12265,7 +12259,7 @@
         <v>16</v>
       </c>
       <c r="C1024" t="n">
-        <v>-0.0357779415438204</v>
+        <v>-0.603410889945478</v>
       </c>
     </row>
     <row r="1025">
@@ -12276,7 +12270,7 @@
         <v>16</v>
       </c>
       <c r="C1025" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.324448191741385</v>
       </c>
     </row>
     <row r="1026">
@@ -12298,7 +12292,7 @@
         <v>16</v>
       </c>
       <c r="C1027" t="n">
-        <v>-0.792951496678151</v>
+        <v>-1.72078729303023</v>
       </c>
     </row>
     <row r="1028">
@@ -12309,7 +12303,7 @@
         <v>16</v>
       </c>
       <c r="C1028" t="n">
-        <v>-0.424430064491351</v>
+        <v>-0.481197717636152</v>
       </c>
     </row>
     <row r="1029">
@@ -12320,7 +12314,7 @@
         <v>16</v>
       </c>
       <c r="C1029" t="n">
-        <v>-0.967309720033077</v>
+        <v>-0.184299185858009</v>
       </c>
     </row>
     <row r="1030">
@@ -12331,7 +12325,7 @@
         <v>16</v>
       </c>
       <c r="C1030" t="n">
-        <v>-0.173611111111111</v>
+        <v>-1.34060530180373</v>
       </c>
     </row>
     <row r="1031">
@@ -12342,7 +12336,7 @@
         <v>16</v>
       </c>
       <c r="C1031" t="n">
-        <v>-0.184130495804506</v>
+        <v>-0.958780498000403</v>
       </c>
     </row>
     <row r="1032">
@@ -12353,7 +12347,7 @@
         <v>16</v>
       </c>
       <c r="C1032" t="n">
-        <v>-0.340809074487553</v>
+        <v>-0.830816930719659</v>
       </c>
     </row>
     <row r="1033">
@@ -12364,7 +12358,7 @@
         <v>16</v>
       </c>
       <c r="C1033" t="n">
-        <v>-0.173611111111111</v>
+        <v>-1.14717358572578</v>
       </c>
     </row>
     <row r="1034">
@@ -12375,7 +12369,7 @@
         <v>16</v>
       </c>
       <c r="C1034" t="n">
-        <v>-0.529412498650065</v>
+        <v>-0.694400807932137</v>
       </c>
     </row>
     <row r="1035">
@@ -12386,7 +12380,7 @@
         <v>16</v>
       </c>
       <c r="C1035" t="n">
-        <v>-0.308570075356176</v>
+        <v>-1.1393081046383</v>
       </c>
     </row>
     <row r="1036">
@@ -12397,7 +12391,7 @@
         <v>16</v>
       </c>
       <c r="C1036" t="n">
-        <v>-0.626511070495019</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1037">
@@ -12408,7 +12402,7 @@
         <v>16</v>
       </c>
       <c r="C1037" t="n">
-        <v>-0.366820520347609</v>
+        <v>-1.22159586185028</v>
       </c>
     </row>
     <row r="1038">
@@ -12430,7 +12424,7 @@
         <v>16</v>
       </c>
       <c r="C1039" t="n">
-        <v>-0.244182511569479</v>
+        <v>-0.208282693810699</v>
       </c>
     </row>
     <row r="1040">
@@ -12441,7 +12435,7 @@
         <v>16</v>
       </c>
       <c r="C1040" t="n">
-        <v>-0.173611111111111</v>
+        <v>-2.87166067547024</v>
       </c>
     </row>
     <row r="1041">
@@ -12463,7 +12457,7 @@
         <v>16</v>
       </c>
       <c r="C1042" t="n">
-        <v>-0.216240465960007</v>
+        <v>-0.341878244549684</v>
       </c>
     </row>
     <row r="1043">
@@ -12474,7 +12468,7 @@
         <v>16</v>
       </c>
       <c r="C1043" t="n">
-        <v>-0.495704543121067</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1044">
@@ -12485,7 +12479,7 @@
         <v>16</v>
       </c>
       <c r="C1044" t="n">
-        <v>-0.131665445192144</v>
+        <v>-0.305490373730339</v>
       </c>
     </row>
     <row r="1045">
@@ -12496,7 +12490,7 @@
         <v>16</v>
       </c>
       <c r="C1045" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.352865585932272</v>
       </c>
     </row>
     <row r="1046">
@@ -12507,7 +12501,7 @@
         <v>16</v>
       </c>
       <c r="C1046" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.359157940637136</v>
       </c>
     </row>
     <row r="1047">
@@ -12518,7 +12512,7 @@
         <v>16</v>
       </c>
       <c r="C1047" t="n">
-        <v>-0.401401045919612</v>
+        <v>-0.487160449269298</v>
       </c>
     </row>
     <row r="1048">
@@ -12529,7 +12523,7 @@
         <v>16</v>
       </c>
       <c r="C1048" t="n">
-        <v>-0.178770358715858</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1049">
@@ -12540,7 +12534,7 @@
         <v>16</v>
       </c>
       <c r="C1049" t="n">
-        <v>-0.302410321476008</v>
+        <v>-0.446015966077568</v>
       </c>
     </row>
     <row r="1050">
@@ -12551,7 +12545,7 @@
         <v>16</v>
       </c>
       <c r="C1050" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.549239109778612</v>
       </c>
     </row>
     <row r="1051">
@@ -12562,7 +12556,7 @@
         <v>16</v>
       </c>
       <c r="C1051" t="n">
-        <v>-0.173611111111111</v>
+        <v>-1.92977784537979</v>
       </c>
     </row>
     <row r="1052">
@@ -12573,7 +12567,7 @@
         <v>16</v>
       </c>
       <c r="C1052" t="n">
-        <v>-0.207329978424789</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1053">
@@ -12584,7 +12578,7 @@
         <v>16</v>
       </c>
       <c r="C1053" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.189657149662387</v>
       </c>
     </row>
     <row r="1054">
@@ -12595,7 +12589,7 @@
         <v>16</v>
       </c>
       <c r="C1054" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.139734813439371</v>
       </c>
     </row>
     <row r="1055">
@@ -12606,7 +12600,7 @@
         <v>16</v>
       </c>
       <c r="C1055" t="n">
-        <v>-0.107484213433787</v>
+        <v>-0.67860091745549</v>
       </c>
     </row>
     <row r="1056">
@@ -12617,7 +12611,7 @@
         <v>16</v>
       </c>
       <c r="C1056" t="n">
-        <v>-0.173611111111111</v>
+        <v>0.293606085274079</v>
       </c>
     </row>
     <row r="1057">
@@ -12628,7 +12622,7 @@
         <v>16</v>
       </c>
       <c r="C1057" t="n">
-        <v>-0.246945017884793</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1058">
@@ -12639,7 +12633,7 @@
         <v>16</v>
       </c>
       <c r="C1058" t="n">
-        <v>-0.178444795731083</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1059">
@@ -12661,7 +12655,7 @@
         <v>16</v>
       </c>
       <c r="C1060" t="n">
-        <v>-0.18892612746756</v>
+        <v>-0.193621184583606</v>
       </c>
     </row>
     <row r="1061">
@@ -12672,7 +12666,7 @@
         <v>16</v>
       </c>
       <c r="C1061" t="n">
-        <v>-0.533769290336041</v>
+        <v>-5.41106553820826</v>
       </c>
     </row>
     <row r="1062">
@@ -12683,7 +12677,7 @@
         <v>16</v>
       </c>
       <c r="C1062" t="n">
-        <v>-0.847509202731132</v>
+        <v>-1.62718273531105</v>
       </c>
     </row>
     <row r="1063">
@@ -12694,7 +12688,7 @@
         <v>16</v>
       </c>
       <c r="C1063" t="n">
-        <v>-0.91116511496186</v>
+        <v>-0.134287505652843</v>
       </c>
     </row>
     <row r="1064">
@@ -12705,7 +12699,7 @@
         <v>16</v>
       </c>
       <c r="C1064" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.132071348200624</v>
       </c>
     </row>
     <row r="1065">
@@ -12716,7 +12710,7 @@
         <v>16</v>
       </c>
       <c r="C1065" t="n">
-        <v>-0.255646005122863</v>
+        <v>-0.379395657331061</v>
       </c>
     </row>
     <row r="1066">
@@ -12727,7 +12721,7 @@
         <v>16</v>
       </c>
       <c r="C1066" t="n">
-        <v>-1.05504232182474</v>
+        <v>-1.01152290405233</v>
       </c>
     </row>
     <row r="1067">
@@ -12738,7 +12732,7 @@
         <v>16</v>
       </c>
       <c r="C1067" t="n">
-        <v>-0.352435604688286</v>
+        <v>-0.465401710067736</v>
       </c>
     </row>
     <row r="1068">
@@ -12749,7 +12743,7 @@
         <v>16</v>
       </c>
       <c r="C1068" t="n">
-        <v>-0.580641552794493</v>
+        <v>-0.349466007775356</v>
       </c>
     </row>
     <row r="1069">
@@ -12771,7 +12765,7 @@
         <v>16</v>
       </c>
       <c r="C1070" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.358055414926985</v>
       </c>
     </row>
     <row r="1071">
@@ -12782,7 +12776,7 @@
         <v>16</v>
       </c>
       <c r="C1071" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.908540663007156</v>
       </c>
     </row>
     <row r="1072">
@@ -12793,7 +12787,7 @@
         <v>16</v>
       </c>
       <c r="C1072" t="n">
-        <v>-0.24969008344931</v>
+        <v>0.00356019854333423</v>
       </c>
     </row>
     <row r="1073">
@@ -12804,7 +12798,7 @@
         <v>16</v>
       </c>
       <c r="C1073" t="n">
-        <v>-0.525695843451402</v>
+        <v>-0.343120050716983</v>
       </c>
     </row>
     <row r="1074">
@@ -12815,7 +12809,7 @@
         <v>16</v>
       </c>
       <c r="C1074" t="n">
-        <v>-0.212404084228013</v>
+        <v>-0.980898560506862</v>
       </c>
     </row>
     <row r="1075">
@@ -12826,7 +12820,7 @@
         <v>16</v>
       </c>
       <c r="C1075" t="n">
-        <v>-1.72775882619433</v>
+        <v>-0.939983615345971</v>
       </c>
     </row>
     <row r="1076">
@@ -12837,7 +12831,7 @@
         <v>16</v>
       </c>
       <c r="C1076" t="n">
-        <v>-0.345242965580058</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1077">
@@ -12848,7 +12842,7 @@
         <v>16</v>
       </c>
       <c r="C1077" t="n">
-        <v>-0.469634903017</v>
+        <v>-0.19551825687647</v>
       </c>
     </row>
     <row r="1078">
@@ -12859,7 +12853,7 @@
         <v>16</v>
       </c>
       <c r="C1078" t="n">
-        <v>-0.354905885736641</v>
+        <v>0.123624334378474</v>
       </c>
     </row>
     <row r="1079">
@@ -12870,7 +12864,7 @@
         <v>16</v>
       </c>
       <c r="C1079" t="n">
-        <v>-0.434779232296548</v>
+        <v>-0.0014464033034185</v>
       </c>
     </row>
     <row r="1080">
@@ -12881,7 +12875,7 @@
         <v>16</v>
       </c>
       <c r="C1080" t="n">
-        <v>-0.286002599662177</v>
+        <v>-0.346557505689779</v>
       </c>
     </row>
     <row r="1081">
@@ -12892,7 +12886,7 @@
         <v>16</v>
       </c>
       <c r="C1081" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.736987906088617</v>
       </c>
     </row>
     <row r="1082">
@@ -12903,7 +12897,7 @@
         <v>16</v>
       </c>
       <c r="C1082" t="n">
-        <v>-0.340246743107319</v>
+        <v>-0.302727355030957</v>
       </c>
     </row>
     <row r="1083">
@@ -12914,7 +12908,7 @@
         <v>16</v>
       </c>
       <c r="C1083" t="n">
-        <v>-0.28523846322222</v>
+        <v>-0.238215956270732</v>
       </c>
     </row>
     <row r="1084">
@@ -12925,7 +12919,7 @@
         <v>16</v>
       </c>
       <c r="C1084" t="n">
-        <v>-0.671705886465327</v>
+        <v>-0.4293281424709</v>
       </c>
     </row>
     <row r="1085">
@@ -12936,7 +12930,7 @@
         <v>16</v>
       </c>
       <c r="C1085" t="n">
-        <v>-0.332550601607293</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1086">
@@ -12947,7 +12941,7 @@
         <v>16</v>
       </c>
       <c r="C1086" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.279198891734149</v>
       </c>
     </row>
     <row r="1087">
@@ -12958,7 +12952,7 @@
         <v>16</v>
       </c>
       <c r="C1087" t="n">
-        <v>-0.38314416453623</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1088">
@@ -12969,7 +12963,7 @@
         <v>16</v>
       </c>
       <c r="C1088" t="n">
-        <v>-0.139922473726063</v>
+        <v>-0.245117178367571</v>
       </c>
     </row>
     <row r="1089">
@@ -12980,7 +12974,7 @@
         <v>16</v>
       </c>
       <c r="C1089" t="n">
-        <v>-0.426760364848935</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1090">
@@ -12991,7 +12985,7 @@
         <v>16</v>
       </c>
       <c r="C1090" t="n">
-        <v>-0.435463791536469</v>
+        <v>-0.298260275122583</v>
       </c>
     </row>
     <row r="1091">
@@ -13002,7 +12996,7 @@
         <v>16</v>
       </c>
       <c r="C1091" t="n">
-        <v>-0.25864610475172</v>
+        <v>0.800740822211042</v>
       </c>
     </row>
     <row r="1092">
@@ -13013,7 +13007,7 @@
         <v>16</v>
       </c>
       <c r="C1092" t="n">
-        <v>-0.154960436421715</v>
+        <v>-1.21349975308599</v>
       </c>
     </row>
     <row r="1093">
@@ -13024,7 +13018,7 @@
         <v>16</v>
       </c>
       <c r="C1093" t="n">
-        <v>-0.185287578021311</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1094">
@@ -13035,7 +13029,7 @@
         <v>16</v>
       </c>
       <c r="C1094" t="n">
-        <v>-0.763988074369427</v>
+        <v>-0.497640213560347</v>
       </c>
     </row>
     <row r="1095">
@@ -13046,7 +13040,7 @@
         <v>16</v>
       </c>
       <c r="C1095" t="n">
-        <v>-0.216610563855095</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1096">
@@ -13057,7 +13051,7 @@
         <v>16</v>
       </c>
       <c r="C1096" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.198163618601763</v>
       </c>
     </row>
     <row r="1097">
@@ -13068,7 +13062,7 @@
         <v>16</v>
       </c>
       <c r="C1097" t="n">
-        <v>-0.134677894548897</v>
+        <v>-0.429928877890676</v>
       </c>
     </row>
     <row r="1098">
@@ -13101,7 +13095,7 @@
         <v>16</v>
       </c>
       <c r="C1100" t="n">
-        <v>-0.382772399333784</v>
+        <v>-0.170283860877434</v>
       </c>
     </row>
     <row r="1101">
@@ -13112,7 +13106,7 @@
         <v>16</v>
       </c>
       <c r="C1101" t="n">
-        <v>-0.238978349493827</v>
+        <v>0.221983608790692</v>
       </c>
     </row>
     <row r="1102">
@@ -13123,7 +13117,7 @@
         <v>16</v>
       </c>
       <c r="C1102" t="n">
-        <v>-0.944348287680363</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1103">
@@ -13145,7 +13139,7 @@
         <v>16</v>
       </c>
       <c r="C1104" t="n">
-        <v>-0.533389063861281</v>
+        <v>-0.87235531566748</v>
       </c>
     </row>
     <row r="1105">
@@ -13156,7 +13150,7 @@
         <v>16</v>
       </c>
       <c r="C1105" t="n">
-        <v>-0.68666225324253</v>
+        <v>-0.714502775866694</v>
       </c>
     </row>
     <row r="1106">
@@ -13167,7 +13161,7 @@
         <v>16</v>
       </c>
       <c r="C1106" t="n">
-        <v>-0.555656879806766</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1107">
@@ -13178,7 +13172,7 @@
         <v>16</v>
       </c>
       <c r="C1107" t="n">
-        <v>-0.26902304321508</v>
+        <v>-0.349336749772795</v>
       </c>
     </row>
     <row r="1108">
@@ -13211,7 +13205,7 @@
         <v>16</v>
       </c>
       <c r="C1110" t="n">
-        <v>-0.265411739701493</v>
+        <v>-0.0890278570450704</v>
       </c>
     </row>
     <row r="1111">
@@ -13222,7 +13216,7 @@
         <v>16</v>
       </c>
       <c r="C1111" t="n">
-        <v>-1.05781630986349</v>
+        <v>-0.150284541369506</v>
       </c>
     </row>
     <row r="1112">
@@ -13233,7 +13227,7 @@
         <v>16</v>
       </c>
       <c r="C1112" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.26991115616081</v>
       </c>
     </row>
     <row r="1113">
@@ -13255,7 +13249,7 @@
         <v>16</v>
       </c>
       <c r="C1114" t="n">
-        <v>0.46289260493374</v>
+        <v>0.264908163671536</v>
       </c>
     </row>
     <row r="1115">
@@ -13277,7 +13271,7 @@
         <v>16</v>
       </c>
       <c r="C1116" t="n">
-        <v>-0.454156558623172</v>
+        <v>-0.415360615876624</v>
       </c>
     </row>
     <row r="1117">
@@ -13288,7 +13282,7 @@
         <v>16</v>
       </c>
       <c r="C1117" t="n">
-        <v>-0.23760555964959</v>
+        <v>-0.244942702711539</v>
       </c>
     </row>
     <row r="1118">
@@ -13299,7 +13293,7 @@
         <v>16</v>
       </c>
       <c r="C1118" t="n">
-        <v>-1.06185264302256</v>
+        <v>-0.374934736722781</v>
       </c>
     </row>
     <row r="1119">
@@ -13310,7 +13304,7 @@
         <v>16</v>
       </c>
       <c r="C1119" t="n">
-        <v>-0.280860086105112</v>
+        <v>-0.253729808511724</v>
       </c>
     </row>
     <row r="1120">
@@ -13332,7 +13326,7 @@
         <v>16</v>
       </c>
       <c r="C1121" t="n">
-        <v>-0.468216579986359</v>
+        <v>-1.2581743119786</v>
       </c>
     </row>
     <row r="1122">
@@ -13343,7 +13337,7 @@
         <v>16</v>
       </c>
       <c r="C1122" t="n">
-        <v>0.0894604410519717</v>
+        <v>0.307263250730684</v>
       </c>
     </row>
     <row r="1123">
@@ -13354,7 +13348,7 @@
         <v>16</v>
       </c>
       <c r="C1123" t="n">
-        <v>-1.11961197293168</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1124">
@@ -13365,7 +13359,7 @@
         <v>16</v>
       </c>
       <c r="C1124" t="n">
-        <v>-0.165618372751098</v>
+        <v>-0.297009997139918</v>
       </c>
     </row>
     <row r="1125">
@@ -13376,7 +13370,7 @@
         <v>16</v>
       </c>
       <c r="C1125" t="n">
-        <v>-0.31094186228234</v>
+        <v>-0.491231603181063</v>
       </c>
     </row>
     <row r="1126">
@@ -13387,7 +13381,7 @@
         <v>16</v>
       </c>
       <c r="C1126" t="n">
-        <v>-0.173611111111111</v>
+        <v>-1.98659642832847</v>
       </c>
     </row>
     <row r="1127">
@@ -13398,7 +13392,7 @@
         <v>16</v>
       </c>
       <c r="C1127" t="n">
-        <v>-0.30627514842038</v>
+        <v>-0.346941203656162</v>
       </c>
     </row>
     <row r="1128">
@@ -13409,7 +13403,7 @@
         <v>16</v>
       </c>
       <c r="C1128" t="n">
-        <v>-0.173225310272112</v>
+        <v>-0.0679160379850503</v>
       </c>
     </row>
     <row r="1129">
@@ -13420,7 +13414,7 @@
         <v>16</v>
       </c>
       <c r="C1129" t="n">
-        <v>-0.173611111111111</v>
+        <v>-1.13687604189222</v>
       </c>
     </row>
     <row r="1130">
@@ -13431,7 +13425,7 @@
         <v>16</v>
       </c>
       <c r="C1130" t="n">
-        <v>-0.198355190481288</v>
+        <v>-0.164717761048889</v>
       </c>
     </row>
     <row r="1131">
@@ -13442,7 +13436,7 @@
         <v>16</v>
       </c>
       <c r="C1131" t="n">
-        <v>-0.28253016241053</v>
+        <v>-0.343444827191729</v>
       </c>
     </row>
     <row r="1132">
@@ -13464,7 +13458,7 @@
         <v>16</v>
       </c>
       <c r="C1133" t="n">
-        <v>-0.193699275164471</v>
+        <v>-0.288152926955457</v>
       </c>
     </row>
     <row r="1134">
@@ -13486,7 +13480,7 @@
         <v>16</v>
       </c>
       <c r="C1135" t="n">
-        <v>-0.696510019134112</v>
+        <v>-0.247977958207031</v>
       </c>
     </row>
     <row r="1136">
@@ -13497,7 +13491,7 @@
         <v>16</v>
       </c>
       <c r="C1136" t="n">
-        <v>-0.302254810248053</v>
+        <v>-0.579046305286162</v>
       </c>
     </row>
     <row r="1137">
@@ -13508,7 +13502,7 @@
         <v>16</v>
       </c>
       <c r="C1137" t="n">
-        <v>-0.173611111111111</v>
+        <v>-1.2388712761802</v>
       </c>
     </row>
     <row r="1138">
@@ -13519,7 +13513,7 @@
         <v>16</v>
       </c>
       <c r="C1138" t="n">
-        <v>-0.242783035491205</v>
+        <v>-0.305889418007306</v>
       </c>
     </row>
     <row r="1139">
@@ -13530,7 +13524,7 @@
         <v>16</v>
       </c>
       <c r="C1139" t="n">
-        <v>-0.17811317577201</v>
+        <v>-0.165301197489583</v>
       </c>
     </row>
     <row r="1140">
@@ -13541,7 +13535,7 @@
         <v>16</v>
       </c>
       <c r="C1140" t="n">
-        <v>-0.362658300883295</v>
+        <v>-1.26725147562629</v>
       </c>
     </row>
     <row r="1141">
@@ -13552,7 +13546,7 @@
         <v>16</v>
       </c>
       <c r="C1141" t="n">
-        <v>-0.657352289584914</v>
+        <v>-0.211508646699372</v>
       </c>
     </row>
     <row r="1142">
@@ -13563,7 +13557,7 @@
         <v>16</v>
       </c>
       <c r="C1142" t="n">
-        <v>-0.267249070821816</v>
+        <v>0.285039166160849</v>
       </c>
     </row>
     <row r="1143">
@@ -13585,7 +13579,7 @@
         <v>16</v>
       </c>
       <c r="C1144" t="n">
-        <v>-0.351613064730338</v>
+        <v>-0.566366969085681</v>
       </c>
     </row>
     <row r="1145">
@@ -13596,7 +13590,7 @@
         <v>16</v>
       </c>
       <c r="C1145" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.188701510036084</v>
       </c>
     </row>
     <row r="1146">
@@ -13607,7 +13601,7 @@
         <v>16</v>
       </c>
       <c r="C1146" t="n">
-        <v>-0.108382272114269</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1147">
@@ -13629,7 +13623,7 @@
         <v>16</v>
       </c>
       <c r="C1148" t="n">
-        <v>-0.243775912639098</v>
+        <v>-0.204077984030165</v>
       </c>
     </row>
     <row r="1149">
@@ -13640,7 +13634,7 @@
         <v>16</v>
       </c>
       <c r="C1149" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.223318433522026</v>
       </c>
     </row>
     <row r="1150">
@@ -13662,7 +13656,7 @@
         <v>16</v>
       </c>
       <c r="C1151" t="n">
-        <v>-0.244627291657565</v>
+        <v>0.249051704004939</v>
       </c>
     </row>
     <row r="1152">
@@ -13684,7 +13678,7 @@
         <v>16</v>
       </c>
       <c r="C1153" t="n">
-        <v>0.266027550704299</v>
+        <v>0.115742842367625</v>
       </c>
     </row>
     <row r="1154">
@@ -13695,7 +13689,7 @@
         <v>16</v>
       </c>
       <c r="C1154" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.400097416651177</v>
       </c>
     </row>
     <row r="1155">
@@ -13706,7 +13700,7 @@
         <v>16</v>
       </c>
       <c r="C1155" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.177323723075684</v>
       </c>
     </row>
     <row r="1156">
@@ -13717,7 +13711,7 @@
         <v>16</v>
       </c>
       <c r="C1156" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.195943351159117</v>
       </c>
     </row>
     <row r="1157">
@@ -13728,7 +13722,7 @@
         <v>16</v>
       </c>
       <c r="C1157" t="n">
-        <v>-2.42519290592519</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1158">
@@ -13739,7 +13733,7 @@
         <v>16</v>
       </c>
       <c r="C1158" t="n">
-        <v>-0.261046035563273</v>
+        <v>-0.423746126261494</v>
       </c>
     </row>
     <row r="1159">
@@ -13750,7 +13744,7 @@
         <v>16</v>
       </c>
       <c r="C1159" t="n">
-        <v>-0.543095901479252</v>
+        <v>-0.569003482052974</v>
       </c>
     </row>
     <row r="1160">
@@ -13761,7 +13755,7 @@
         <v>16</v>
       </c>
       <c r="C1160" t="n">
-        <v>-0.880324422445583</v>
+        <v>-0.403899380448442</v>
       </c>
     </row>
     <row r="1161">
@@ -13772,7 +13766,7 @@
         <v>16</v>
       </c>
       <c r="C1161" t="n">
-        <v>0.102286998451386</v>
+        <v>-0.166202511021261</v>
       </c>
     </row>
     <row r="1162">
@@ -13794,7 +13788,7 @@
         <v>16</v>
       </c>
       <c r="C1163" t="n">
-        <v>-0.172691454654171</v>
+        <v>-1.27074772930965</v>
       </c>
     </row>
     <row r="1164">
@@ -13805,7 +13799,7 @@
         <v>16</v>
       </c>
       <c r="C1164" t="n">
-        <v>-0.26766382540488</v>
+        <v>-0.788911191043221</v>
       </c>
     </row>
     <row r="1165">
@@ -13827,7 +13821,7 @@
         <v>16</v>
       </c>
       <c r="C1166" t="n">
-        <v>-0.173611111111111</v>
+        <v>-1.47160465275362</v>
       </c>
     </row>
     <row r="1167">
@@ -13838,7 +13832,7 @@
         <v>16</v>
       </c>
       <c r="C1167" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.919794969953826</v>
       </c>
     </row>
     <row r="1168">
@@ -13849,7 +13843,7 @@
         <v>16</v>
       </c>
       <c r="C1168" t="n">
-        <v>-0.20627080455153</v>
+        <v>-0.19337402896072</v>
       </c>
     </row>
     <row r="1169">
@@ -13860,7 +13854,7 @@
         <v>16</v>
       </c>
       <c r="C1169" t="n">
-        <v>-0.285415171805703</v>
+        <v>-4.80995316181956</v>
       </c>
     </row>
     <row r="1170">
@@ -13871,7 +13865,7 @@
         <v>16</v>
       </c>
       <c r="C1170" t="n">
-        <v>-0.0732573754917418</v>
+        <v>-0.215342757849455</v>
       </c>
     </row>
     <row r="1171">
@@ -13882,7 +13876,7 @@
         <v>16</v>
       </c>
       <c r="C1171" t="n">
-        <v>-0.216821185670069</v>
+        <v>-0.174050891839546</v>
       </c>
     </row>
     <row r="1172">
@@ -13893,7 +13887,7 @@
         <v>16</v>
       </c>
       <c r="C1172" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.69615487780283</v>
       </c>
     </row>
     <row r="1173">
@@ -13904,7 +13898,7 @@
         <v>16</v>
       </c>
       <c r="C1173" t="n">
-        <v>-0.636741052898503</v>
+        <v>-0.50701611600203</v>
       </c>
     </row>
     <row r="1174">
@@ -13915,7 +13909,7 @@
         <v>16</v>
       </c>
       <c r="C1174" t="n">
-        <v>0.195144895780485</v>
+        <v>-0.0642411362160118</v>
       </c>
     </row>
     <row r="1175">
@@ -13926,7 +13920,7 @@
         <v>16</v>
       </c>
       <c r="C1175" t="n">
-        <v>-0.52181705404335</v>
+        <v>-3.0680899131056</v>
       </c>
     </row>
     <row r="1176">
@@ -13937,7 +13931,7 @@
         <v>16</v>
       </c>
       <c r="C1176" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.688829940141861</v>
       </c>
     </row>
     <row r="1177">
@@ -13948,7 +13942,7 @@
         <v>16</v>
       </c>
       <c r="C1177" t="n">
-        <v>-0.478772080279487</v>
+        <v>-0.387851483897998</v>
       </c>
     </row>
     <row r="1178">
@@ -13981,7 +13975,7 @@
         <v>16</v>
       </c>
       <c r="C1180" t="n">
-        <v>-1.06804583534964</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1181">
@@ -13992,7 +13986,7 @@
         <v>16</v>
       </c>
       <c r="C1181" t="n">
-        <v>-0.542634919787724</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1182">
@@ -14003,7 +13997,7 @@
         <v>16</v>
       </c>
       <c r="C1182" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.679661929177938</v>
       </c>
     </row>
     <row r="1183">
@@ -14014,7 +14008,7 @@
         <v>16</v>
       </c>
       <c r="C1183" t="n">
-        <v>-0.189993186139137</v>
+        <v>-0.154479513843222</v>
       </c>
     </row>
     <row r="1184">
@@ -14025,7 +14019,7 @@
         <v>16</v>
       </c>
       <c r="C1184" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.22469924250154</v>
       </c>
     </row>
     <row r="1185">
@@ -14036,7 +14030,7 @@
         <v>16</v>
       </c>
       <c r="C1185" t="n">
-        <v>-0.173611111111111</v>
+        <v>-1.1603677385475</v>
       </c>
     </row>
     <row r="1186">
@@ -14047,7 +14041,7 @@
         <v>16</v>
       </c>
       <c r="C1186" t="n">
-        <v>-0.187681219626566</v>
+        <v>-0.702973581910767</v>
       </c>
     </row>
     <row r="1187">
@@ -14058,7 +14052,7 @@
         <v>16</v>
       </c>
       <c r="C1187" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.360498848211048</v>
       </c>
     </row>
     <row r="1188">
@@ -14069,7 +14063,7 @@
         <v>16</v>
       </c>
       <c r="C1188" t="n">
-        <v>-0.261438201630564</v>
+        <v>-0.674415110388673</v>
       </c>
     </row>
     <row r="1189">
@@ -14080,7 +14074,7 @@
         <v>16</v>
       </c>
       <c r="C1189" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.437291313028543</v>
       </c>
     </row>
     <row r="1190">
@@ -14091,7 +14085,7 @@
         <v>16</v>
       </c>
       <c r="C1190" t="n">
-        <v>-0.199040284738378</v>
+        <v>-0.212549478561656</v>
       </c>
     </row>
     <row r="1191">
@@ -14102,7 +14096,7 @@
         <v>16</v>
       </c>
       <c r="C1191" t="n">
-        <v>-0.597219176774481</v>
+        <v>-0.589195342233808</v>
       </c>
     </row>
     <row r="1192">
@@ -14113,7 +14107,7 @@
         <v>16</v>
       </c>
       <c r="C1192" t="n">
-        <v>-1.06319333131762</v>
+        <v>-0.795981523138357</v>
       </c>
     </row>
     <row r="1193">
@@ -14124,7 +14118,7 @@
         <v>16</v>
       </c>
       <c r="C1193" t="n">
-        <v>-0.220685248183485</v>
+        <v>-0.873898722139117</v>
       </c>
     </row>
     <row r="1194">
@@ -14146,7 +14140,7 @@
         <v>16</v>
       </c>
       <c r="C1195" t="n">
-        <v>-0.287781581472171</v>
+        <v>-0.754183019811485</v>
       </c>
     </row>
     <row r="1196">
@@ -14157,7 +14151,7 @@
         <v>16</v>
       </c>
       <c r="C1196" t="n">
-        <v>-0.543370191811714</v>
+        <v>-0.471577987175775</v>
       </c>
     </row>
     <row r="1197">
@@ -14168,7 +14162,7 @@
         <v>16</v>
       </c>
       <c r="C1197" t="n">
-        <v>-0.441884153818797</v>
+        <v>-0.456801519105767</v>
       </c>
     </row>
     <row r="1198">
@@ -14179,7 +14173,7 @@
         <v>16</v>
       </c>
       <c r="C1198" t="n">
-        <v>-0.814341067173715</v>
+        <v>-1.26964123367072</v>
       </c>
     </row>
     <row r="1199">
@@ -14190,7 +14184,7 @@
         <v>16</v>
       </c>
       <c r="C1199" t="n">
-        <v>-0.454436579401345</v>
+        <v>-0.522077371130314</v>
       </c>
     </row>
     <row r="1200">
@@ -14201,7 +14195,7 @@
         <v>16</v>
       </c>
       <c r="C1200" t="n">
-        <v>-0.722113272409825</v>
+        <v>-0.806054854225896</v>
       </c>
     </row>
     <row r="1201">
@@ -14212,7 +14206,7 @@
         <v>16</v>
       </c>
       <c r="C1201" t="n">
-        <v>-0.703238200349192</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
   </sheetData>
@@ -14767,7 +14761,7 @@
         <v>2790.83</v>
       </c>
       <c r="E32" t="n">
-        <v>-418.8533560693</v>
+        <v>-179.339230769231</v>
       </c>
     </row>
     <row r="33">
@@ -14937,7 +14931,7 @@
         <v>-1491.94</v>
       </c>
       <c r="E42" t="n">
-        <v>2812.56292445541</v>
+        <v>1429.36651886434</v>
       </c>
     </row>
     <row r="43">
@@ -15090,7 +15084,7 @@
         <v>-1.918</v>
       </c>
       <c r="E51" t="n">
-        <v>2.44617847760395</v>
+        <v>2.12738461538462</v>
       </c>
     </row>
     <row r="52">
@@ -15226,7 +15220,7 @@
         <v>83</v>
       </c>
       <c r="E59" t="n">
-        <v>39.3846153846154</v>
+        <v>14.2394916994521</v>
       </c>
     </row>
     <row r="60">
@@ -15345,7 +15339,7 @@
         <v>5</v>
       </c>
       <c r="E66" t="n">
-        <v>47.8933345622273</v>
+        <v>45.3846153846154</v>
       </c>
     </row>
     <row r="67">
@@ -15413,7 +15407,7 @@
         <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>120.602745524001</v>
+        <v>114.96485815965</v>
       </c>
     </row>
     <row r="71">
@@ -15447,7 +15441,7 @@
         <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>9.25</v>
+        <v>-9.38232738994054</v>
       </c>
     </row>
     <row r="73">
@@ -15583,7 +15577,7 @@
         <v>6</v>
       </c>
       <c r="E80" t="n">
-        <v>9.64775215345196</v>
+        <v>10.4295800595053</v>
       </c>
     </row>
     <row r="81">
@@ -15634,7 +15628,7 @@
         <v>15</v>
       </c>
       <c r="E83" t="n">
-        <v>6.04652784503396</v>
+        <v>8.41666666666667</v>
       </c>
     </row>
     <row r="84">
@@ -15775,13 +15769,13 @@
         <v>47</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -15789,16 +15783,16 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -15806,16 +15800,16 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -15823,16 +15817,16 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -15840,16 +15834,16 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -15857,16 +15851,16 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -15874,7 +15868,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
@@ -15883,7 +15877,7 @@
         <v>0.0714285714285714</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -15891,7 +15885,7 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -15900,7 +15894,7 @@
         <v>0.0714285714285714</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -15908,7 +15902,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
@@ -15917,7 +15911,7 @@
         <v>0.0714285714285714</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -15934,7 +15928,7 @@
         <v>0.0714285714285714</v>
       </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -15945,10 +15939,10 @@
         <v>52</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="E17" t="s">
         <v>20</v>
@@ -15959,16 +15953,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.153846153846154</v>
       </c>
       <c r="E18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -15976,16 +15970,16 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.153846153846154</v>
       </c>
       <c r="E19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
@@ -15993,16 +15987,16 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.153846153846154</v>
       </c>
       <c r="E20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -16010,16 +16004,16 @@
         <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.153846153846154</v>
       </c>
       <c r="E21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
@@ -16027,16 +16021,16 @@
         <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="E22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -16044,16 +16038,16 @@
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="E23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -16061,16 +16055,16 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="E24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -16078,117 +16072,15 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.153846153846154</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="E25" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.153846153846154</v>
-      </c>
-      <c r="E26" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.153846153846154</v>
-      </c>
-      <c r="E27" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>16</v>
-      </c>
-      <c r="B28" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="E28" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>16</v>
-      </c>
-      <c r="B29" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="E29" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>16</v>
-      </c>
-      <c r="B30" t="s">
-        <v>50</v>
-      </c>
-      <c r="C30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="E30" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>16</v>
-      </c>
-      <c r="B31" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="E31" t="s">
         <v>21</v>
       </c>
     </row>
